--- a/map/city/regions.xlsx
+++ b/map/city/regions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Unida\Documents\VSC\Python\EpidemicSimulation\map\city\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75ABA5F-5BD3-4C44-B2D9-93550956D18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530CBBA4-0774-45EB-A007-CF14F4E8BB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B03016EF-FA4B-4206-80C1-0600DFDF6CE4}"/>
+    <workbookView xWindow="24300" yWindow="588" windowWidth="21600" windowHeight="11232" xr2:uid="{B03016EF-FA4B-4206-80C1-0600DFDF6CE4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="1028">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="1027">
   <si>
     <t>Map edge nodes within the region</t>
   </si>
@@ -1674,9 +1674,6 @@
   </si>
   <si>
     <t>22821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   </t>
   </si>
   <si>
     <t>323,325,328,329,330,331,332</t>
@@ -3126,7 +3123,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3150,6 +3147,19 @@
       <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="&quot;Helvetica Neue&quot;"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -3178,7 +3188,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -3186,11 +3196,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3206,6 +3231,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3526,7 +3557,7 @@
     <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="76.5">
+    <row r="1" spans="1:7" ht="77.25" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3539,22 +3570,22 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="39">
+    <row r="2" spans="1:7" ht="39.75" thickBot="1">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
@@ -3562,11 +3593,15 @@
       <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="E2" s="8">
+        <v>6813</v>
+      </c>
+      <c r="F2" s="8">
+        <v>738</v>
+      </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" ht="15.75" thickBot="1">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -3577,16 +3612,20 @@
       <c r="D3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="E3" s="8">
+        <v>2054</v>
+      </c>
+      <c r="F3" s="8">
+        <v>222</v>
+      </c>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="51.75">
+    <row r="4" spans="1:7" ht="39.75" thickBot="1">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
@@ -3594,16 +3633,20 @@
       <c r="D4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="E4" s="8">
+        <v>6964</v>
+      </c>
+      <c r="F4" s="8">
+        <v>754</v>
+      </c>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="26.25">
+    <row r="5" spans="1:7" ht="27" thickBot="1">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>16</v>
@@ -3611,11 +3654,15 @@
       <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="E5" s="8">
+        <v>800</v>
+      </c>
+      <c r="F5" s="8">
+        <v>86</v>
+      </c>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" ht="26.25">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -3626,16 +3673,20 @@
       <c r="D6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="E6" s="8">
+        <v>1026</v>
+      </c>
+      <c r="F6" s="8">
+        <v>111</v>
+      </c>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" ht="39">
+    <row r="7" spans="1:7" ht="39.75" thickBot="1">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>22</v>
@@ -3643,16 +3694,20 @@
       <c r="D7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="E7" s="8">
+        <v>10453</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1132</v>
+      </c>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" ht="26.25">
+    <row r="8" spans="1:7" ht="27" thickBot="1">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>25</v>
@@ -3660,11 +3715,15 @@
       <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="E8" s="8">
+        <v>4954</v>
+      </c>
+      <c r="F8" s="8">
+        <v>536</v>
+      </c>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" ht="26.25">
+    <row r="9" spans="1:7" ht="27" thickBot="1">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -3675,11 +3734,15 @@
       <c r="D9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="E9" s="8">
+        <v>2143</v>
+      </c>
+      <c r="F9" s="8">
+        <v>232</v>
+      </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" ht="26.25">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -3690,11 +3753,15 @@
       <c r="D10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
+      <c r="E10" s="8">
+        <v>1818</v>
+      </c>
+      <c r="F10" s="8">
+        <v>197</v>
+      </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="26.25">
+    <row r="11" spans="1:7" ht="27" thickBot="1">
       <c r="A11" s="2" t="s">
         <v>35</v>
       </c>
@@ -3705,11 +3772,15 @@
       <c r="D11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="E11" s="8">
+        <v>844</v>
+      </c>
+      <c r="F11" s="8">
+        <v>91</v>
+      </c>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="39">
+    <row r="12" spans="1:7" ht="27" thickBot="1">
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
@@ -3720,11 +3791,15 @@
       <c r="D12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="E12" s="8">
+        <v>1342</v>
+      </c>
+      <c r="F12" s="8">
+        <v>145</v>
+      </c>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" ht="26.25">
+    <row r="13" spans="1:7" ht="27" thickBot="1">
       <c r="A13" s="2" t="s">
         <v>41</v>
       </c>
@@ -3735,11 +3810,15 @@
       <c r="D13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="E13" s="8">
+        <v>2564</v>
+      </c>
+      <c r="F13" s="8">
+        <v>277</v>
+      </c>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" ht="26.25">
+    <row r="14" spans="1:7" ht="15.75" thickBot="1">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -3750,11 +3829,15 @@
       <c r="D14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
+      <c r="E14" s="8">
+        <v>1349</v>
+      </c>
+      <c r="F14" s="8">
+        <v>146</v>
+      </c>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:7" ht="26.25">
+    <row r="15" spans="1:7" ht="27" thickBot="1">
       <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
@@ -3765,11 +3848,15 @@
       <c r="D15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
+      <c r="E15" s="8">
+        <v>3564</v>
+      </c>
+      <c r="F15" s="8">
+        <v>386</v>
+      </c>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:7" ht="26.25">
+    <row r="16" spans="1:7" ht="27" thickBot="1">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -3780,11 +3867,15 @@
       <c r="D16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="E16" s="8">
+        <v>1373</v>
+      </c>
+      <c r="F16" s="8">
+        <v>148</v>
+      </c>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" ht="39">
+    <row r="17" spans="1:7" ht="27" thickBot="1">
       <c r="A17" s="2" t="s">
         <v>54</v>
       </c>
@@ -3797,11 +3888,15 @@
       <c r="D17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="E17" s="8">
+        <v>1493</v>
+      </c>
+      <c r="F17" s="8">
+        <v>161</v>
+      </c>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" ht="26.25">
+    <row r="18" spans="1:7" ht="27" thickBot="1">
       <c r="A18" s="2" t="s">
         <v>57</v>
       </c>
@@ -3812,11 +3907,15 @@
       <c r="D18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="E18" s="8">
+        <v>1080</v>
+      </c>
+      <c r="F18" s="8">
+        <v>117</v>
+      </c>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="26.25">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1">
       <c r="A19" s="2" t="s">
         <v>60</v>
       </c>
@@ -3827,11 +3926,15 @@
       <c r="D19" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
+      <c r="E19" s="8">
+        <v>216</v>
+      </c>
+      <c r="F19" s="8">
+        <v>23</v>
+      </c>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="26.25">
+    <row r="20" spans="1:7" ht="27" thickBot="1">
       <c r="A20" s="2" t="s">
         <v>63</v>
       </c>
@@ -3842,11 +3945,15 @@
       <c r="D20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="E20" s="8">
+        <v>2936</v>
+      </c>
+      <c r="F20" s="8">
+        <v>318</v>
+      </c>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" ht="39">
+    <row r="21" spans="1:7" ht="27" thickBot="1">
       <c r="A21" s="2" t="s">
         <v>66</v>
       </c>
@@ -3857,11 +3964,15 @@
       <c r="D21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="E21" s="8">
+        <v>3134</v>
+      </c>
+      <c r="F21" s="8">
+        <v>339</v>
+      </c>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" ht="39">
+    <row r="22" spans="1:7" ht="27" thickBot="1">
       <c r="A22" s="2" t="s">
         <v>69</v>
       </c>
@@ -3872,16 +3983,20 @@
       <c r="D22" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
+      <c r="E22" s="8">
+        <v>2146</v>
+      </c>
+      <c r="F22" s="8">
+        <v>232</v>
+      </c>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:7" ht="51.75">
+    <row r="23" spans="1:7" ht="52.5" thickBot="1">
       <c r="A23" s="2" t="s">
         <v>72</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>71</v>
@@ -3889,11 +4004,15 @@
       <c r="D23" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
+      <c r="E23" s="8">
+        <v>5328</v>
+      </c>
+      <c r="F23" s="8">
+        <v>577</v>
+      </c>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:7" ht="26.25">
+    <row r="24" spans="1:7" ht="27" thickBot="1">
       <c r="A24" s="2" t="s">
         <v>75</v>
       </c>
@@ -3904,11 +4023,15 @@
       <c r="D24" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
+      <c r="E24" s="8">
+        <v>1426</v>
+      </c>
+      <c r="F24" s="8">
+        <v>154</v>
+      </c>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" ht="39">
+    <row r="25" spans="1:7" ht="27" thickBot="1">
       <c r="A25" s="2" t="s">
         <v>78</v>
       </c>
@@ -3919,11 +4042,15 @@
       <c r="D25" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
+      <c r="E25" s="8">
+        <v>4266</v>
+      </c>
+      <c r="F25" s="8">
+        <v>462</v>
+      </c>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" ht="15.75" thickBot="1">
       <c r="A26" s="2" t="s">
         <v>81</v>
       </c>
@@ -3934,11 +4061,15 @@
       <c r="D26" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
+      <c r="E26" s="8">
+        <v>493</v>
+      </c>
+      <c r="F26" s="8">
+        <v>53</v>
+      </c>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" spans="1:7" ht="39">
+    <row r="27" spans="1:7" ht="39.75" thickBot="1">
       <c r="A27" s="2" t="s">
         <v>84</v>
       </c>
@@ -3949,11 +4080,15 @@
       <c r="D27" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
+      <c r="E27" s="8">
+        <v>3910</v>
+      </c>
+      <c r="F27" s="8">
+        <v>423</v>
+      </c>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" ht="26.25">
+    <row r="28" spans="1:7" ht="27" thickBot="1">
       <c r="A28" s="2" t="s">
         <v>87</v>
       </c>
@@ -3964,11 +4099,15 @@
       <c r="D28" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
+      <c r="E28" s="8">
+        <v>927</v>
+      </c>
+      <c r="F28" s="8">
+        <v>100</v>
+      </c>
       <c r="G28" s="2"/>
     </row>
-    <row r="29" spans="1:7" ht="26.25">
+    <row r="29" spans="1:7" ht="15.75" thickBot="1">
       <c r="A29" s="2" t="s">
         <v>90</v>
       </c>
@@ -3979,11 +4118,15 @@
       <c r="D29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
+      <c r="E29" s="8">
+        <v>168</v>
+      </c>
+      <c r="F29" s="8">
+        <v>18</v>
+      </c>
       <c r="G29" s="2"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" ht="15.75" thickBot="1">
       <c r="A30" s="2" t="s">
         <v>93</v>
       </c>
@@ -3994,11 +4137,15 @@
       <c r="D30" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
+      <c r="E30" s="8">
+        <v>265</v>
+      </c>
+      <c r="F30" s="8">
+        <v>28</v>
+      </c>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" ht="15.75" thickBot="1">
       <c r="A31" s="2" t="s">
         <v>96</v>
       </c>
@@ -4009,11 +4156,15 @@
       <c r="D31" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
+      <c r="E31" s="8">
+        <v>55</v>
+      </c>
+      <c r="F31" s="8">
+        <v>5</v>
+      </c>
       <c r="G31" s="2"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1">
       <c r="A32" s="2" t="s">
         <v>99</v>
       </c>
@@ -4024,11 +4175,15 @@
       <c r="D32" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
+      <c r="E32" s="8">
+        <v>250</v>
+      </c>
+      <c r="F32" s="8">
+        <v>27</v>
+      </c>
       <c r="G32" s="2"/>
     </row>
-    <row r="33" spans="1:7" ht="26.25">
+    <row r="33" spans="1:7" ht="15.75" thickBot="1">
       <c r="A33" s="2" t="s">
         <v>102</v>
       </c>
@@ -4039,11 +4194,15 @@
       <c r="D33" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
+      <c r="E33" s="8">
+        <v>231</v>
+      </c>
+      <c r="F33" s="8">
+        <v>25</v>
+      </c>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" spans="1:7" ht="26.25">
+    <row r="34" spans="1:7" ht="15.75" thickBot="1">
       <c r="A34" s="2" t="s">
         <v>105</v>
       </c>
@@ -4054,11 +4213,15 @@
       <c r="D34" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
+      <c r="E34" s="8">
+        <v>208</v>
+      </c>
+      <c r="F34" s="8">
+        <v>22</v>
+      </c>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="1:7" ht="26.25">
+    <row r="35" spans="1:7" ht="27" thickBot="1">
       <c r="A35" s="2" t="s">
         <v>108</v>
       </c>
@@ -4069,11 +4232,15 @@
       <c r="D35" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
+      <c r="E35" s="8">
+        <v>475</v>
+      </c>
+      <c r="F35" s="8">
+        <v>51</v>
+      </c>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="1:7" ht="26.25">
+    <row r="36" spans="1:7" ht="15.75" thickBot="1">
       <c r="A36" s="2" t="s">
         <v>111</v>
       </c>
@@ -4084,11 +4251,15 @@
       <c r="D36" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
+      <c r="E36" s="8">
+        <v>742</v>
+      </c>
+      <c r="F36" s="8">
+        <v>80</v>
+      </c>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="1:7" ht="26.25">
+    <row r="37" spans="1:7" ht="15.75" thickBot="1">
       <c r="A37" s="2" t="s">
         <v>114</v>
       </c>
@@ -4099,11 +4270,15 @@
       <c r="D37" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
+      <c r="E37" s="8">
+        <v>729</v>
+      </c>
+      <c r="F37" s="8">
+        <v>79</v>
+      </c>
       <c r="G37" s="2"/>
     </row>
-    <row r="38" spans="1:7" ht="26.25">
+    <row r="38" spans="1:7" ht="15.75" thickBot="1">
       <c r="A38" s="2" t="s">
         <v>117</v>
       </c>
@@ -4114,11 +4289,15 @@
       <c r="D38" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
+      <c r="E38" s="8">
+        <v>474</v>
+      </c>
+      <c r="F38" s="8">
+        <v>51</v>
+      </c>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" spans="1:7" ht="26.25">
+    <row r="39" spans="1:7" ht="15.75" thickBot="1">
       <c r="A39" s="2" t="s">
         <v>120</v>
       </c>
@@ -4129,11 +4308,15 @@
       <c r="D39" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
+      <c r="E39" s="8">
+        <v>444</v>
+      </c>
+      <c r="F39" s="8">
+        <v>48</v>
+      </c>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="1:7" ht="26.25">
+    <row r="40" spans="1:7" ht="15.75" thickBot="1">
       <c r="A40" s="2" t="s">
         <v>123</v>
       </c>
@@ -4144,11 +4327,15 @@
       <c r="D40" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
+      <c r="E40" s="8">
+        <v>423</v>
+      </c>
+      <c r="F40" s="8">
+        <v>45</v>
+      </c>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="1:7" ht="26.25">
+    <row r="41" spans="1:7" ht="15.75" thickBot="1">
       <c r="A41" s="2" t="s">
         <v>126</v>
       </c>
@@ -4159,11 +4346,15 @@
       <c r="D41" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
+      <c r="E41" s="8">
+        <v>1803</v>
+      </c>
+      <c r="F41" s="8">
+        <v>195</v>
+      </c>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="1:7" ht="26.25">
+    <row r="42" spans="1:7" ht="15.75" thickBot="1">
       <c r="A42" s="2" t="s">
         <v>129</v>
       </c>
@@ -4174,11 +4365,15 @@
       <c r="D42" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
+      <c r="E42" s="8">
+        <v>956</v>
+      </c>
+      <c r="F42" s="8">
+        <v>103</v>
+      </c>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="1:7" ht="26.25">
+    <row r="43" spans="1:7" ht="27" thickBot="1">
       <c r="A43" s="2" t="s">
         <v>132</v>
       </c>
@@ -4189,11 +4384,15 @@
       <c r="D43" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
+      <c r="E43" s="8">
+        <v>1213</v>
+      </c>
+      <c r="F43" s="8">
+        <v>131</v>
+      </c>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="1:7" ht="26.25">
+    <row r="44" spans="1:7" ht="15.75" thickBot="1">
       <c r="A44" s="2" t="s">
         <v>135</v>
       </c>
@@ -4204,11 +4403,15 @@
       <c r="D44" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
+      <c r="E44" s="8">
+        <v>1529</v>
+      </c>
+      <c r="F44" s="8">
+        <v>165</v>
+      </c>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="1:7" ht="26.25">
+    <row r="45" spans="1:7" ht="15.75" thickBot="1">
       <c r="A45" s="2" t="s">
         <v>138</v>
       </c>
@@ -4219,11 +4422,15 @@
       <c r="D45" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
+      <c r="E45" s="8">
+        <v>308</v>
+      </c>
+      <c r="F45" s="8">
+        <v>33</v>
+      </c>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="1:7" ht="26.25">
+    <row r="46" spans="1:7" ht="15.75" thickBot="1">
       <c r="A46" s="2" t="s">
         <v>141</v>
       </c>
@@ -4234,11 +4441,15 @@
       <c r="D46" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
+      <c r="E46" s="8">
+        <v>321</v>
+      </c>
+      <c r="F46" s="8">
+        <v>34</v>
+      </c>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="1:7" ht="26.25">
+    <row r="47" spans="1:7" ht="15.75" thickBot="1">
       <c r="A47" s="2" t="s">
         <v>144</v>
       </c>
@@ -4249,11 +4460,15 @@
       <c r="D47" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
+      <c r="E47" s="8">
+        <v>224</v>
+      </c>
+      <c r="F47" s="8">
+        <v>24</v>
+      </c>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="1:7" ht="39">
+    <row r="48" spans="1:7" ht="39.75" thickBot="1">
       <c r="A48" s="2" t="s">
         <v>147</v>
       </c>
@@ -4264,11 +4479,15 @@
       <c r="D48" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
+      <c r="E48" s="8">
+        <v>2593</v>
+      </c>
+      <c r="F48" s="8">
+        <v>281</v>
+      </c>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="1:7" ht="26.25">
+    <row r="49" spans="1:7" ht="27" thickBot="1">
       <c r="A49" s="2" t="s">
         <v>150</v>
       </c>
@@ -4279,11 +4498,15 @@
       <c r="D49" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
+      <c r="E49" s="8">
+        <v>1263</v>
+      </c>
+      <c r="F49" s="8">
+        <v>136</v>
+      </c>
       <c r="G49" s="2"/>
     </row>
-    <row r="50" spans="1:7" ht="26.25">
+    <row r="50" spans="1:7" ht="15.75" thickBot="1">
       <c r="A50" s="2" t="s">
         <v>153</v>
       </c>
@@ -4294,11 +4517,15 @@
       <c r="D50" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
+      <c r="E50" s="8">
+        <v>984</v>
+      </c>
+      <c r="F50" s="8">
+        <v>106</v>
+      </c>
       <c r="G50" s="2"/>
     </row>
-    <row r="51" spans="1:7" ht="26.25">
+    <row r="51" spans="1:7" ht="15.75" thickBot="1">
       <c r="A51" s="2" t="s">
         <v>156</v>
       </c>
@@ -4309,11 +4536,15 @@
       <c r="D51" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
+      <c r="E51" s="8">
+        <v>550</v>
+      </c>
+      <c r="F51" s="8">
+        <v>59</v>
+      </c>
       <c r="G51" s="2"/>
     </row>
-    <row r="52" spans="1:7" ht="26.25">
+    <row r="52" spans="1:7" ht="15.75" thickBot="1">
       <c r="A52" s="2" t="s">
         <v>159</v>
       </c>
@@ -4324,11 +4555,15 @@
       <c r="D52" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
+      <c r="E52" s="8">
+        <v>414</v>
+      </c>
+      <c r="F52" s="8">
+        <v>44</v>
+      </c>
       <c r="G52" s="2"/>
     </row>
-    <row r="53" spans="1:7" ht="26.25">
+    <row r="53" spans="1:7" ht="27" thickBot="1">
       <c r="A53" s="2" t="s">
         <v>162</v>
       </c>
@@ -4339,11 +4574,15 @@
       <c r="D53" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
+      <c r="E53" s="8">
+        <v>681</v>
+      </c>
+      <c r="F53" s="8">
+        <v>73</v>
+      </c>
       <c r="G53" s="2"/>
     </row>
-    <row r="54" spans="1:7" ht="26.25">
+    <row r="54" spans="1:7" ht="27" thickBot="1">
       <c r="A54" s="2" t="s">
         <v>165</v>
       </c>
@@ -4354,11 +4593,15 @@
       <c r="D54" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
+      <c r="E54" s="8">
+        <v>282</v>
+      </c>
+      <c r="F54" s="8">
+        <v>30</v>
+      </c>
       <c r="G54" s="2"/>
     </row>
-    <row r="55" spans="1:7" ht="26.25">
+    <row r="55" spans="1:7" ht="15.75" thickBot="1">
       <c r="A55" s="2" t="s">
         <v>168</v>
       </c>
@@ -4369,11 +4612,15 @@
       <c r="D55" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
+      <c r="E55" s="8">
+        <v>296</v>
+      </c>
+      <c r="F55" s="8">
+        <v>32</v>
+      </c>
       <c r="G55" s="2"/>
     </row>
-    <row r="56" spans="1:7" ht="26.25">
+    <row r="56" spans="1:7" ht="15.75" thickBot="1">
       <c r="A56" s="2" t="s">
         <v>171</v>
       </c>
@@ -4384,11 +4631,15 @@
       <c r="D56" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
+      <c r="E56" s="8">
+        <v>137</v>
+      </c>
+      <c r="F56" s="8">
+        <v>14</v>
+      </c>
       <c r="G56" s="2"/>
     </row>
-    <row r="57" spans="1:7" ht="26.25">
+    <row r="57" spans="1:7" ht="15.75" thickBot="1">
       <c r="A57" s="2" t="s">
         <v>174</v>
       </c>
@@ -4399,11 +4650,15 @@
       <c r="D57" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
+      <c r="E57" s="8">
+        <v>319</v>
+      </c>
+      <c r="F57" s="8">
+        <v>34</v>
+      </c>
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:7" ht="26.25">
+    <row r="58" spans="1:7" ht="27" thickBot="1">
       <c r="A58" s="2" t="s">
         <v>177</v>
       </c>
@@ -4414,11 +4669,15 @@
       <c r="D58" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
+      <c r="E58" s="8">
+        <v>599</v>
+      </c>
+      <c r="F58" s="8">
+        <v>64</v>
+      </c>
       <c r="G58" s="2"/>
     </row>
-    <row r="59" spans="1:7" ht="26.25">
+    <row r="59" spans="1:7" ht="27" thickBot="1">
       <c r="A59" s="2" t="s">
         <v>180</v>
       </c>
@@ -4429,11 +4688,15 @@
       <c r="D59" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
+      <c r="E59" s="8">
+        <v>433</v>
+      </c>
+      <c r="F59" s="8">
+        <v>47</v>
+      </c>
       <c r="G59" s="2"/>
     </row>
-    <row r="60" spans="1:7" ht="26.25">
+    <row r="60" spans="1:7" ht="27" thickBot="1">
       <c r="A60" s="2" t="s">
         <v>183</v>
       </c>
@@ -4444,11 +4707,15 @@
       <c r="D60" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
+      <c r="E60" s="8">
+        <v>318</v>
+      </c>
+      <c r="F60" s="8">
+        <v>34</v>
+      </c>
       <c r="G60" s="2"/>
     </row>
-    <row r="61" spans="1:7" ht="26.25">
+    <row r="61" spans="1:7" ht="27" thickBot="1">
       <c r="A61" s="2" t="s">
         <v>186</v>
       </c>
@@ -4459,11 +4726,15 @@
       <c r="D61" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
+      <c r="E61" s="8">
+        <v>129</v>
+      </c>
+      <c r="F61" s="8">
+        <v>14</v>
+      </c>
       <c r="G61" s="2"/>
     </row>
-    <row r="62" spans="1:7" ht="26.25">
+    <row r="62" spans="1:7" ht="27" thickBot="1">
       <c r="A62" s="2" t="s">
         <v>189</v>
       </c>
@@ -4474,11 +4745,15 @@
       <c r="D62" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
+      <c r="E62" s="8">
+        <v>439</v>
+      </c>
+      <c r="F62" s="8">
+        <v>47</v>
+      </c>
       <c r="G62" s="2"/>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" ht="15.75" thickBot="1">
       <c r="A63" s="2" t="s">
         <v>192</v>
       </c>
@@ -4489,11 +4764,15 @@
       <c r="D63" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
+      <c r="E63" s="8">
+        <v>137</v>
+      </c>
+      <c r="F63" s="8">
+        <v>14</v>
+      </c>
       <c r="G63" s="2"/>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" ht="15.75" thickBot="1">
       <c r="A64" s="2" t="s">
         <v>195</v>
       </c>
@@ -4504,11 +4783,15 @@
       <c r="D64" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
+      <c r="E64" s="8">
+        <v>140</v>
+      </c>
+      <c r="F64" s="8">
+        <v>15</v>
+      </c>
       <c r="G64" s="2"/>
     </row>
-    <row r="65" spans="1:7" ht="39">
+    <row r="65" spans="1:7" ht="27" thickBot="1">
       <c r="A65" s="2" t="s">
         <v>198</v>
       </c>
@@ -4519,11 +4802,15 @@
       <c r="D65" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
+      <c r="E65" s="8">
+        <v>998</v>
+      </c>
+      <c r="F65" s="8">
+        <v>108</v>
+      </c>
       <c r="G65" s="2"/>
     </row>
-    <row r="66" spans="1:7" ht="26.25">
+    <row r="66" spans="1:7" ht="27" thickBot="1">
       <c r="A66" s="2" t="s">
         <v>201</v>
       </c>
@@ -4534,11 +4821,15 @@
       <c r="D66" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
+      <c r="E66" s="8">
+        <v>471</v>
+      </c>
+      <c r="F66" s="8">
+        <v>51</v>
+      </c>
       <c r="G66" s="2"/>
     </row>
-    <row r="67" spans="1:7" ht="26.25">
+    <row r="67" spans="1:7" ht="27" thickBot="1">
       <c r="A67" s="2" t="s">
         <v>204</v>
       </c>
@@ -4549,11 +4840,15 @@
       <c r="D67" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
+      <c r="E67" s="8">
+        <v>450</v>
+      </c>
+      <c r="F67" s="8">
+        <v>48</v>
+      </c>
       <c r="G67" s="2"/>
     </row>
-    <row r="68" spans="1:7" ht="39">
+    <row r="68" spans="1:7" ht="27" thickBot="1">
       <c r="A68" s="2" t="s">
         <v>207</v>
       </c>
@@ -4564,11 +4859,15 @@
       <c r="D68" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
+      <c r="E68" s="8">
+        <v>2473</v>
+      </c>
+      <c r="F68" s="8">
+        <v>268</v>
+      </c>
       <c r="G68" s="2"/>
     </row>
-    <row r="69" spans="1:7" ht="26.25">
+    <row r="69" spans="1:7" ht="27" thickBot="1">
       <c r="A69" s="2" t="s">
         <v>210</v>
       </c>
@@ -4579,11 +4878,15 @@
       <c r="D69" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
+      <c r="E69" s="8">
+        <v>709</v>
+      </c>
+      <c r="F69" s="8">
+        <v>76</v>
+      </c>
       <c r="G69" s="2"/>
     </row>
-    <row r="70" spans="1:7" ht="26.25">
+    <row r="70" spans="1:7" ht="27" thickBot="1">
       <c r="A70" s="2" t="s">
         <v>213</v>
       </c>
@@ -4594,11 +4897,15 @@
       <c r="D70" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
+      <c r="E70" s="8">
+        <v>1674</v>
+      </c>
+      <c r="F70" s="8">
+        <v>181</v>
+      </c>
       <c r="G70" s="2"/>
     </row>
-    <row r="71" spans="1:7" ht="26.25">
+    <row r="71" spans="1:7" ht="27" thickBot="1">
       <c r="A71" s="2" t="s">
         <v>216</v>
       </c>
@@ -4609,11 +4916,15 @@
       <c r="D71" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
+      <c r="E71" s="8">
+        <v>3384</v>
+      </c>
+      <c r="F71" s="8">
+        <v>366</v>
+      </c>
       <c r="G71" s="2"/>
     </row>
-    <row r="72" spans="1:7" ht="26.25">
+    <row r="72" spans="1:7" ht="15.75" thickBot="1">
       <c r="A72" s="2" t="s">
         <v>219</v>
       </c>
@@ -4624,11 +4935,15 @@
       <c r="D72" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
+      <c r="E72" s="8">
+        <v>720</v>
+      </c>
+      <c r="F72" s="8">
+        <v>78</v>
+      </c>
       <c r="G72" s="2"/>
     </row>
-    <row r="73" spans="1:7" ht="26.25">
+    <row r="73" spans="1:7" ht="27" thickBot="1">
       <c r="A73" s="2" t="s">
         <v>222</v>
       </c>
@@ -4639,11 +4954,15 @@
       <c r="D73" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
+      <c r="E73" s="8">
+        <v>4244</v>
+      </c>
+      <c r="F73" s="8">
+        <v>460</v>
+      </c>
       <c r="G73" s="2"/>
     </row>
-    <row r="74" spans="1:7" ht="26.25">
+    <row r="74" spans="1:7" ht="27" thickBot="1">
       <c r="A74" s="2" t="s">
         <v>225</v>
       </c>
@@ -4654,11 +4973,15 @@
       <c r="D74" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
+      <c r="E74" s="8">
+        <v>2116</v>
+      </c>
+      <c r="F74" s="8">
+        <v>229</v>
+      </c>
       <c r="G74" s="2"/>
     </row>
-    <row r="75" spans="1:7" ht="39">
+    <row r="75" spans="1:7" ht="27" thickBot="1">
       <c r="A75" s="2" t="s">
         <v>228</v>
       </c>
@@ -4669,11 +4992,15 @@
       <c r="D75" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
+      <c r="E75" s="8">
+        <v>958</v>
+      </c>
+      <c r="F75" s="8">
+        <v>103</v>
+      </c>
       <c r="G75" s="2"/>
     </row>
-    <row r="76" spans="1:7" ht="26.25">
+    <row r="76" spans="1:7" ht="27" thickBot="1">
       <c r="A76" s="2" t="s">
         <v>231</v>
       </c>
@@ -4684,11 +5011,15 @@
       <c r="D76" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
+      <c r="E76" s="8">
+        <v>142</v>
+      </c>
+      <c r="F76" s="8">
+        <v>15</v>
+      </c>
       <c r="G76" s="2"/>
     </row>
-    <row r="77" spans="1:7" ht="26.25">
+    <row r="77" spans="1:7" ht="27" thickBot="1">
       <c r="A77" s="2" t="s">
         <v>234</v>
       </c>
@@ -4699,11 +5030,15 @@
       <c r="D77" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
+      <c r="E77" s="8">
+        <v>142</v>
+      </c>
+      <c r="F77" s="8">
+        <v>15</v>
+      </c>
       <c r="G77" s="2"/>
     </row>
-    <row r="78" spans="1:7" ht="26.25">
+    <row r="78" spans="1:7" ht="15.75" thickBot="1">
       <c r="A78" s="2" t="s">
         <v>237</v>
       </c>
@@ -4714,11 +5049,15 @@
       <c r="D78" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
+      <c r="E78" s="8">
+        <v>51</v>
+      </c>
+      <c r="F78" s="8">
+        <v>5</v>
+      </c>
       <c r="G78" s="2"/>
     </row>
-    <row r="79" spans="1:7" ht="39">
+    <row r="79" spans="1:7" ht="27" thickBot="1">
       <c r="A79" s="2" t="s">
         <v>240</v>
       </c>
@@ -4729,11 +5068,15 @@
       <c r="D79" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
+      <c r="E79" s="8">
+        <v>1029</v>
+      </c>
+      <c r="F79" s="8">
+        <v>111</v>
+      </c>
       <c r="G79" s="2"/>
     </row>
-    <row r="80" spans="1:7" ht="39">
+    <row r="80" spans="1:7" ht="27" thickBot="1">
       <c r="A80" s="2" t="s">
         <v>243</v>
       </c>
@@ -4744,11 +5087,15 @@
       <c r="D80" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
+      <c r="E80" s="8">
+        <v>354</v>
+      </c>
+      <c r="F80" s="8">
+        <v>38</v>
+      </c>
       <c r="G80" s="2"/>
     </row>
-    <row r="81" spans="1:7" ht="26.25">
+    <row r="81" spans="1:7" ht="27" thickBot="1">
       <c r="A81" s="2" t="s">
         <v>246</v>
       </c>
@@ -4759,11 +5106,15 @@
       <c r="D81" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
+      <c r="E81" s="8">
+        <v>1475</v>
+      </c>
+      <c r="F81" s="8">
+        <v>159</v>
+      </c>
       <c r="G81" s="2"/>
     </row>
-    <row r="82" spans="1:7" ht="39">
+    <row r="82" spans="1:7" ht="27" thickBot="1">
       <c r="A82" s="2" t="s">
         <v>249</v>
       </c>
@@ -4774,11 +5125,15 @@
       <c r="D82" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
+      <c r="E82" s="8">
+        <v>1496</v>
+      </c>
+      <c r="F82" s="8">
+        <v>162</v>
+      </c>
       <c r="G82" s="2"/>
     </row>
-    <row r="83" spans="1:7" ht="51.75">
+    <row r="83" spans="1:7" ht="39.75" thickBot="1">
       <c r="A83" s="2" t="s">
         <v>252</v>
       </c>
@@ -4789,11 +5144,15 @@
       <c r="D83" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
+      <c r="E83" s="8">
+        <v>2297</v>
+      </c>
+      <c r="F83" s="8">
+        <v>248</v>
+      </c>
       <c r="G83" s="2"/>
     </row>
-    <row r="84" spans="1:7" ht="39">
+    <row r="84" spans="1:7" ht="27" thickBot="1">
       <c r="A84" s="2" t="s">
         <v>255</v>
       </c>
@@ -4804,11 +5163,15 @@
       <c r="D84" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
+      <c r="E84" s="8">
+        <v>1010</v>
+      </c>
+      <c r="F84" s="8">
+        <v>109</v>
+      </c>
       <c r="G84" s="2"/>
     </row>
-    <row r="85" spans="1:7" ht="39">
+    <row r="85" spans="1:7" ht="27" thickBot="1">
       <c r="A85" s="2" t="s">
         <v>258</v>
       </c>
@@ -4819,11 +5182,15 @@
       <c r="D85" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
+      <c r="E85" s="8">
+        <v>900</v>
+      </c>
+      <c r="F85" s="8">
+        <v>97</v>
+      </c>
       <c r="G85" s="2"/>
     </row>
-    <row r="86" spans="1:7" ht="26.25">
+    <row r="86" spans="1:7" ht="27" thickBot="1">
       <c r="A86" s="2" t="s">
         <v>261</v>
       </c>
@@ -4834,11 +5201,15 @@
       <c r="D86" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
+      <c r="E86" s="8">
+        <v>522</v>
+      </c>
+      <c r="F86" s="8">
+        <v>56</v>
+      </c>
       <c r="G86" s="2"/>
     </row>
-    <row r="87" spans="1:7" ht="39">
+    <row r="87" spans="1:7" ht="27" thickBot="1">
       <c r="A87" s="2" t="s">
         <v>264</v>
       </c>
@@ -4849,11 +5220,15 @@
       <c r="D87" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
+      <c r="E87" s="8">
+        <v>770</v>
+      </c>
+      <c r="F87" s="8">
+        <v>83</v>
+      </c>
       <c r="G87" s="2"/>
     </row>
-    <row r="88" spans="1:7" ht="39">
+    <row r="88" spans="1:7" ht="27" thickBot="1">
       <c r="A88" s="2" t="s">
         <v>267</v>
       </c>
@@ -4864,11 +5239,15 @@
       <c r="D88" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
+      <c r="E88" s="8">
+        <v>678</v>
+      </c>
+      <c r="F88" s="8">
+        <v>73</v>
+      </c>
       <c r="G88" s="2"/>
     </row>
-    <row r="89" spans="1:7" ht="26.25">
+    <row r="89" spans="1:7" ht="27" thickBot="1">
       <c r="A89" s="2" t="s">
         <v>270</v>
       </c>
@@ -4879,11 +5258,15 @@
       <c r="D89" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
+      <c r="E89" s="8">
+        <v>236</v>
+      </c>
+      <c r="F89" s="8">
+        <v>25</v>
+      </c>
       <c r="G89" s="2"/>
     </row>
-    <row r="90" spans="1:7" ht="26.25">
+    <row r="90" spans="1:7" ht="27" thickBot="1">
       <c r="A90" s="2" t="s">
         <v>273</v>
       </c>
@@ -4894,11 +5277,15 @@
       <c r="D90" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
+      <c r="E90" s="8">
+        <v>253</v>
+      </c>
+      <c r="F90" s="8">
+        <v>27</v>
+      </c>
       <c r="G90" s="2"/>
     </row>
-    <row r="91" spans="1:7" ht="39">
+    <row r="91" spans="1:7" ht="27" thickBot="1">
       <c r="A91" s="2" t="s">
         <v>276</v>
       </c>
@@ -4909,11 +5296,15 @@
       <c r="D91" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
+      <c r="E91" s="8">
+        <v>531</v>
+      </c>
+      <c r="F91" s="8">
+        <v>57</v>
+      </c>
       <c r="G91" s="2"/>
     </row>
-    <row r="92" spans="1:7" ht="26.25">
+    <row r="92" spans="1:7" ht="27" thickBot="1">
       <c r="A92" s="2" t="s">
         <v>279</v>
       </c>
@@ -4924,11 +5315,15 @@
       <c r="D92" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
+      <c r="E92" s="8">
+        <v>437</v>
+      </c>
+      <c r="F92" s="8">
+        <v>47</v>
+      </c>
       <c r="G92" s="2"/>
     </row>
-    <row r="93" spans="1:7" ht="39">
+    <row r="93" spans="1:7" ht="27" thickBot="1">
       <c r="A93" s="2" t="s">
         <v>282</v>
       </c>
@@ -4939,11 +5334,15 @@
       <c r="D93" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
+      <c r="E93" s="8">
+        <v>724</v>
+      </c>
+      <c r="F93" s="8">
+        <v>78</v>
+      </c>
       <c r="G93" s="2"/>
     </row>
-    <row r="94" spans="1:7" ht="26.25">
+    <row r="94" spans="1:7" ht="27" thickBot="1">
       <c r="A94" s="2" t="s">
         <v>285</v>
       </c>
@@ -4954,11 +5353,15 @@
       <c r="D94" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
+      <c r="E94" s="8">
+        <v>449</v>
+      </c>
+      <c r="F94" s="8">
+        <v>48</v>
+      </c>
       <c r="G94" s="2"/>
     </row>
-    <row r="95" spans="1:7" ht="26.25">
+    <row r="95" spans="1:7" ht="27" thickBot="1">
       <c r="A95" s="2" t="s">
         <v>288</v>
       </c>
@@ -4969,11 +5372,15 @@
       <c r="D95" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
+      <c r="E95" s="8">
+        <v>133</v>
+      </c>
+      <c r="F95" s="8">
+        <v>14</v>
+      </c>
       <c r="G95" s="2"/>
     </row>
-    <row r="96" spans="1:7" ht="26.25">
+    <row r="96" spans="1:7" ht="27" thickBot="1">
       <c r="A96" s="2" t="s">
         <v>291</v>
       </c>
@@ -4984,11 +5391,15 @@
       <c r="D96" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
+      <c r="E96" s="8">
+        <v>329</v>
+      </c>
+      <c r="F96" s="8">
+        <v>35</v>
+      </c>
       <c r="G96" s="2"/>
     </row>
-    <row r="97" spans="1:7" ht="26.25">
+    <row r="97" spans="1:7" ht="27" thickBot="1">
       <c r="A97" s="2" t="s">
         <v>294</v>
       </c>
@@ -4999,11 +5410,15 @@
       <c r="D97" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
+      <c r="E97" s="8">
+        <v>409</v>
+      </c>
+      <c r="F97" s="8">
+        <v>44</v>
+      </c>
       <c r="G97" s="2"/>
     </row>
-    <row r="98" spans="1:7" ht="26.25">
+    <row r="98" spans="1:7" ht="27" thickBot="1">
       <c r="A98" s="2" t="s">
         <v>297</v>
       </c>
@@ -5014,11 +5429,15 @@
       <c r="D98" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
+      <c r="E98" s="8">
+        <v>595</v>
+      </c>
+      <c r="F98" s="8">
+        <v>64</v>
+      </c>
       <c r="G98" s="2"/>
     </row>
-    <row r="99" spans="1:7" ht="26.25">
+    <row r="99" spans="1:7" ht="27" thickBot="1">
       <c r="A99" s="2" t="s">
         <v>300</v>
       </c>
@@ -5029,11 +5448,15 @@
       <c r="D99" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
+      <c r="E99" s="8">
+        <v>482</v>
+      </c>
+      <c r="F99" s="8">
+        <v>52</v>
+      </c>
       <c r="G99" s="2"/>
     </row>
-    <row r="100" spans="1:7" ht="26.25">
+    <row r="100" spans="1:7" ht="27" thickBot="1">
       <c r="A100" s="2" t="s">
         <v>303</v>
       </c>
@@ -5044,11 +5467,15 @@
       <c r="D100" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
+      <c r="E100" s="8">
+        <v>404</v>
+      </c>
+      <c r="F100" s="8">
+        <v>43</v>
+      </c>
       <c r="G100" s="2"/>
     </row>
-    <row r="101" spans="1:7" ht="26.25">
+    <row r="101" spans="1:7" ht="27" thickBot="1">
       <c r="A101" s="2" t="s">
         <v>306</v>
       </c>
@@ -5059,11 +5486,15 @@
       <c r="D101" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
+      <c r="E101" s="8">
+        <v>334</v>
+      </c>
+      <c r="F101" s="8">
+        <v>36</v>
+      </c>
       <c r="G101" s="2"/>
     </row>
-    <row r="102" spans="1:7" ht="26.25">
+    <row r="102" spans="1:7" ht="27" thickBot="1">
       <c r="A102" s="2" t="s">
         <v>309</v>
       </c>
@@ -5074,11 +5505,15 @@
       <c r="D102" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
+      <c r="E102" s="8">
+        <v>134</v>
+      </c>
+      <c r="F102" s="8">
+        <v>14</v>
+      </c>
       <c r="G102" s="2"/>
     </row>
-    <row r="103" spans="1:7" ht="26.25">
+    <row r="103" spans="1:7" ht="27" thickBot="1">
       <c r="A103" s="2" t="s">
         <v>312</v>
       </c>
@@ -5089,11 +5524,15 @@
       <c r="D103" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
+      <c r="E103" s="8">
+        <v>423</v>
+      </c>
+      <c r="F103" s="8">
+        <v>45</v>
+      </c>
       <c r="G103" s="2"/>
     </row>
-    <row r="104" spans="1:7" ht="39">
+    <row r="104" spans="1:7" ht="27" thickBot="1">
       <c r="A104" s="2" t="s">
         <v>315</v>
       </c>
@@ -5104,11 +5543,15 @@
       <c r="D104" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
+      <c r="E104" s="8">
+        <v>2664</v>
+      </c>
+      <c r="F104" s="8">
+        <v>288</v>
+      </c>
       <c r="G104" s="2"/>
     </row>
-    <row r="105" spans="1:7" ht="39">
+    <row r="105" spans="1:7" ht="27" thickBot="1">
       <c r="A105" s="2" t="s">
         <v>318</v>
       </c>
@@ -5119,11 +5562,15 @@
       <c r="D105" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
+      <c r="E105" s="8">
+        <v>783</v>
+      </c>
+      <c r="F105" s="8">
+        <v>84</v>
+      </c>
       <c r="G105" s="2"/>
     </row>
-    <row r="106" spans="1:7" ht="26.25">
+    <row r="106" spans="1:7" ht="27" thickBot="1">
       <c r="A106" s="2" t="s">
         <v>321</v>
       </c>
@@ -5134,11 +5581,15 @@
       <c r="D106" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
+      <c r="E106" s="8">
+        <v>413</v>
+      </c>
+      <c r="F106" s="8">
+        <v>44</v>
+      </c>
       <c r="G106" s="2"/>
     </row>
-    <row r="107" spans="1:7" ht="26.25">
+    <row r="107" spans="1:7" ht="27" thickBot="1">
       <c r="A107" s="2" t="s">
         <v>324</v>
       </c>
@@ -5149,11 +5600,15 @@
       <c r="D107" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
+      <c r="E107" s="8">
+        <v>334</v>
+      </c>
+      <c r="F107" s="8">
+        <v>36</v>
+      </c>
       <c r="G107" s="2"/>
     </row>
-    <row r="108" spans="1:7" ht="26.25">
+    <row r="108" spans="1:7" ht="27" thickBot="1">
       <c r="A108" s="2" t="s">
         <v>327</v>
       </c>
@@ -5164,11 +5619,15 @@
       <c r="D108" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
+      <c r="E108" s="8">
+        <v>432</v>
+      </c>
+      <c r="F108" s="8">
+        <v>46</v>
+      </c>
       <c r="G108" s="2"/>
     </row>
-    <row r="109" spans="1:7" ht="26.25">
+    <row r="109" spans="1:7" ht="27" thickBot="1">
       <c r="A109" s="2" t="s">
         <v>330</v>
       </c>
@@ -5179,11 +5638,15 @@
       <c r="D109" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
+      <c r="E109" s="8">
+        <v>265</v>
+      </c>
+      <c r="F109" s="8">
+        <v>28</v>
+      </c>
       <c r="G109" s="2"/>
     </row>
-    <row r="110" spans="1:7" ht="39">
+    <row r="110" spans="1:7" ht="27" thickBot="1">
       <c r="A110" s="2" t="s">
         <v>333</v>
       </c>
@@ -5194,11 +5657,15 @@
       <c r="D110" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
+      <c r="E110" s="8">
+        <v>1450</v>
+      </c>
+      <c r="F110" s="8">
+        <v>157</v>
+      </c>
       <c r="G110" s="2"/>
     </row>
-    <row r="111" spans="1:7" ht="39">
+    <row r="111" spans="1:7" ht="27" thickBot="1">
       <c r="A111" s="2" t="s">
         <v>336</v>
       </c>
@@ -5209,11 +5676,15 @@
       <c r="D111" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
+      <c r="E111" s="8">
+        <v>2694</v>
+      </c>
+      <c r="F111" s="8">
+        <v>292</v>
+      </c>
       <c r="G111" s="2"/>
     </row>
-    <row r="112" spans="1:7" ht="26.25">
+    <row r="112" spans="1:7" ht="15.75" thickBot="1">
       <c r="A112" s="2" t="s">
         <v>339</v>
       </c>
@@ -5224,11 +5695,15 @@
       <c r="D112" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
+      <c r="E112" s="8">
+        <v>187</v>
+      </c>
+      <c r="F112" s="8">
+        <v>20</v>
+      </c>
       <c r="G112" s="2"/>
     </row>
-    <row r="113" spans="1:7" ht="26.25">
+    <row r="113" spans="1:7" ht="27" thickBot="1">
       <c r="A113" s="2" t="s">
         <v>342</v>
       </c>
@@ -5239,11 +5714,15 @@
       <c r="D113" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
+      <c r="E113" s="8">
+        <v>301</v>
+      </c>
+      <c r="F113" s="8">
+        <v>32</v>
+      </c>
       <c r="G113" s="2"/>
     </row>
-    <row r="114" spans="1:7" ht="39">
+    <row r="114" spans="1:7" ht="27" thickBot="1">
       <c r="A114" s="2" t="s">
         <v>345</v>
       </c>
@@ -5254,11 +5733,15 @@
       <c r="D114" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
+      <c r="E114" s="8">
+        <v>598</v>
+      </c>
+      <c r="F114" s="8">
+        <v>64</v>
+      </c>
       <c r="G114" s="2"/>
     </row>
-    <row r="115" spans="1:7" ht="39">
+    <row r="115" spans="1:7" ht="27" thickBot="1">
       <c r="A115" s="2" t="s">
         <v>348</v>
       </c>
@@ -5269,11 +5752,15 @@
       <c r="D115" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
+      <c r="E115" s="8">
+        <v>336</v>
+      </c>
+      <c r="F115" s="8">
+        <v>36</v>
+      </c>
       <c r="G115" s="2"/>
     </row>
-    <row r="116" spans="1:7" ht="51.75">
+    <row r="116" spans="1:7" ht="39.75" thickBot="1">
       <c r="A116" s="2" t="s">
         <v>351</v>
       </c>
@@ -5284,11 +5771,15 @@
       <c r="D116" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
+      <c r="E116" s="8">
+        <v>1495</v>
+      </c>
+      <c r="F116" s="8">
+        <v>162</v>
+      </c>
       <c r="G116" s="2"/>
     </row>
-    <row r="117" spans="1:7" ht="39">
+    <row r="117" spans="1:7" ht="27" thickBot="1">
       <c r="A117" s="2" t="s">
         <v>354</v>
       </c>
@@ -5299,11 +5790,15 @@
       <c r="D117" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
+      <c r="E117" s="8">
+        <v>606</v>
+      </c>
+      <c r="F117" s="8">
+        <v>65</v>
+      </c>
       <c r="G117" s="2"/>
     </row>
-    <row r="118" spans="1:7" ht="26.25">
+    <row r="118" spans="1:7" ht="27" thickBot="1">
       <c r="A118" s="2" t="s">
         <v>357</v>
       </c>
@@ -5314,11 +5809,15 @@
       <c r="D118" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
+      <c r="E118" s="8">
+        <v>785</v>
+      </c>
+      <c r="F118" s="8">
+        <v>85</v>
+      </c>
       <c r="G118" s="2"/>
     </row>
-    <row r="119" spans="1:7" ht="39">
+    <row r="119" spans="1:7" ht="27" thickBot="1">
       <c r="A119" s="2" t="s">
         <v>360</v>
       </c>
@@ -5329,11 +5828,15 @@
       <c r="D119" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
+      <c r="E119" s="8">
+        <v>793</v>
+      </c>
+      <c r="F119" s="8">
+        <v>86</v>
+      </c>
       <c r="G119" s="2"/>
     </row>
-    <row r="120" spans="1:7" ht="26.25">
+    <row r="120" spans="1:7" ht="15.75" thickBot="1">
       <c r="A120" s="2" t="s">
         <v>363</v>
       </c>
@@ -5344,11 +5847,15 @@
       <c r="D120" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="E120" s="2"/>
-      <c r="F120" s="2"/>
+      <c r="E120" s="8">
+        <v>25</v>
+      </c>
+      <c r="F120" s="8">
+        <v>2</v>
+      </c>
       <c r="G120" s="2"/>
     </row>
-    <row r="121" spans="1:7" ht="26.25">
+    <row r="121" spans="1:7" ht="15.75" thickBot="1">
       <c r="A121" s="2" t="s">
         <v>366</v>
       </c>
@@ -5359,11 +5866,15 @@
       <c r="D121" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="E121" s="2"/>
-      <c r="F121" s="2"/>
+      <c r="E121" s="8">
+        <v>58</v>
+      </c>
+      <c r="F121" s="8">
+        <v>6</v>
+      </c>
       <c r="G121" s="2"/>
     </row>
-    <row r="122" spans="1:7" ht="26.25">
+    <row r="122" spans="1:7" ht="15.75" thickBot="1">
       <c r="A122" s="2" t="s">
         <v>369</v>
       </c>
@@ -5374,11 +5885,15 @@
       <c r="D122" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="E122" s="2"/>
-      <c r="F122" s="2"/>
+      <c r="E122" s="8">
+        <v>24</v>
+      </c>
+      <c r="F122" s="8">
+        <v>2</v>
+      </c>
       <c r="G122" s="2"/>
     </row>
-    <row r="123" spans="1:7" ht="39">
+    <row r="123" spans="1:7" ht="27" thickBot="1">
       <c r="A123" s="2" t="s">
         <v>372</v>
       </c>
@@ -5389,11 +5904,15 @@
       <c r="D123" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E123" s="2"/>
-      <c r="F123" s="2"/>
+      <c r="E123" s="8">
+        <v>463</v>
+      </c>
+      <c r="F123" s="8">
+        <v>50</v>
+      </c>
       <c r="G123" s="2"/>
     </row>
-    <row r="124" spans="1:7" ht="26.25">
+    <row r="124" spans="1:7" ht="27" thickBot="1">
       <c r="A124" s="2" t="s">
         <v>375</v>
       </c>
@@ -5404,11 +5923,15 @@
       <c r="D124" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="E124" s="2"/>
-      <c r="F124" s="2"/>
+      <c r="E124" s="8">
+        <v>146</v>
+      </c>
+      <c r="F124" s="8">
+        <v>15</v>
+      </c>
       <c r="G124" s="2"/>
     </row>
-    <row r="125" spans="1:7" ht="26.25">
+    <row r="125" spans="1:7" ht="27" thickBot="1">
       <c r="A125" s="2" t="s">
         <v>378</v>
       </c>
@@ -5419,11 +5942,15 @@
       <c r="D125" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="E125" s="2"/>
-      <c r="F125" s="2"/>
+      <c r="E125" s="8">
+        <v>359</v>
+      </c>
+      <c r="F125" s="8">
+        <v>38</v>
+      </c>
       <c r="G125" s="2"/>
     </row>
-    <row r="126" spans="1:7" ht="26.25">
+    <row r="126" spans="1:7" ht="27" thickBot="1">
       <c r="A126" s="2" t="s">
         <v>381</v>
       </c>
@@ -5434,11 +5961,15 @@
       <c r="D126" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="E126" s="2"/>
-      <c r="F126" s="2"/>
+      <c r="E126" s="8">
+        <v>454</v>
+      </c>
+      <c r="F126" s="8">
+        <v>49</v>
+      </c>
       <c r="G126" s="2"/>
     </row>
-    <row r="127" spans="1:7" ht="26.25">
+    <row r="127" spans="1:7" ht="27" thickBot="1">
       <c r="A127" s="2" t="s">
         <v>384</v>
       </c>
@@ -5449,11 +5980,15 @@
       <c r="D127" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="E127" s="2"/>
-      <c r="F127" s="2"/>
+      <c r="E127" s="8">
+        <v>366</v>
+      </c>
+      <c r="F127" s="8">
+        <v>39</v>
+      </c>
       <c r="G127" s="2"/>
     </row>
-    <row r="128" spans="1:7" ht="39">
+    <row r="128" spans="1:7" ht="27" thickBot="1">
       <c r="A128" s="2" t="s">
         <v>387</v>
       </c>
@@ -5464,11 +5999,15 @@
       <c r="D128" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="E128" s="2"/>
-      <c r="F128" s="2"/>
+      <c r="E128" s="8">
+        <v>470</v>
+      </c>
+      <c r="F128" s="8">
+        <v>51</v>
+      </c>
       <c r="G128" s="2"/>
     </row>
-    <row r="129" spans="1:7" ht="26.25">
+    <row r="129" spans="1:7" ht="27" thickBot="1">
       <c r="A129" s="2" t="s">
         <v>390</v>
       </c>
@@ -5479,11 +6018,15 @@
       <c r="D129" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="E129" s="2"/>
-      <c r="F129" s="2"/>
+      <c r="E129" s="8">
+        <v>427</v>
+      </c>
+      <c r="F129" s="8">
+        <v>46</v>
+      </c>
       <c r="G129" s="2"/>
     </row>
-    <row r="130" spans="1:7" ht="26.25">
+    <row r="130" spans="1:7" ht="27" thickBot="1">
       <c r="A130" s="2" t="s">
         <v>393</v>
       </c>
@@ -5494,11 +6037,15 @@
       <c r="D130" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="E130" s="2"/>
-      <c r="F130" s="2"/>
+      <c r="E130" s="8">
+        <v>350</v>
+      </c>
+      <c r="F130" s="8">
+        <v>38</v>
+      </c>
       <c r="G130" s="2"/>
     </row>
-    <row r="131" spans="1:7" ht="26.25">
+    <row r="131" spans="1:7" ht="27" thickBot="1">
       <c r="A131" s="2" t="s">
         <v>396</v>
       </c>
@@ -5509,11 +6056,15 @@
       <c r="D131" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="E131" s="2"/>
-      <c r="F131" s="2"/>
+      <c r="E131" s="8">
+        <v>142</v>
+      </c>
+      <c r="F131" s="8">
+        <v>15</v>
+      </c>
       <c r="G131" s="2"/>
     </row>
-    <row r="132" spans="1:7" ht="39">
+    <row r="132" spans="1:7" ht="27" thickBot="1">
       <c r="A132" s="2" t="s">
         <v>399</v>
       </c>
@@ -5524,11 +6075,15 @@
       <c r="D132" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="E132" s="2"/>
-      <c r="F132" s="2"/>
+      <c r="E132" s="8">
+        <v>429</v>
+      </c>
+      <c r="F132" s="8">
+        <v>46</v>
+      </c>
       <c r="G132" s="2"/>
     </row>
-    <row r="133" spans="1:7" ht="39">
+    <row r="133" spans="1:7" ht="27" thickBot="1">
       <c r="A133" s="2" t="s">
         <v>402</v>
       </c>
@@ -5539,11 +6094,15 @@
       <c r="D133" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="E133" s="2"/>
-      <c r="F133" s="2"/>
+      <c r="E133" s="8">
+        <v>287</v>
+      </c>
+      <c r="F133" s="8">
+        <v>31</v>
+      </c>
       <c r="G133" s="2"/>
     </row>
-    <row r="134" spans="1:7" ht="26.25">
+    <row r="134" spans="1:7" ht="27" thickBot="1">
       <c r="A134" s="2" t="s">
         <v>405</v>
       </c>
@@ -5554,11 +6113,15 @@
       <c r="D134" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="E134" s="2"/>
-      <c r="F134" s="2"/>
+      <c r="E134" s="8">
+        <v>412</v>
+      </c>
+      <c r="F134" s="8">
+        <v>44</v>
+      </c>
       <c r="G134" s="2"/>
     </row>
-    <row r="135" spans="1:7" ht="26.25">
+    <row r="135" spans="1:7" ht="27" thickBot="1">
       <c r="A135" s="2" t="s">
         <v>408</v>
       </c>
@@ -5569,11 +6132,15 @@
       <c r="D135" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="E135" s="2"/>
-      <c r="F135" s="2"/>
+      <c r="E135" s="8">
+        <v>141</v>
+      </c>
+      <c r="F135" s="8">
+        <v>15</v>
+      </c>
       <c r="G135" s="2"/>
     </row>
-    <row r="136" spans="1:7" ht="26.25">
+    <row r="136" spans="1:7" ht="27" thickBot="1">
       <c r="A136" s="2" t="s">
         <v>411</v>
       </c>
@@ -5584,11 +6151,15 @@
       <c r="D136" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="E136" s="2"/>
-      <c r="F136" s="2"/>
+      <c r="E136" s="8">
+        <v>324</v>
+      </c>
+      <c r="F136" s="8">
+        <v>35</v>
+      </c>
       <c r="G136" s="2"/>
     </row>
-    <row r="137" spans="1:7" ht="39">
+    <row r="137" spans="1:7" ht="27" thickBot="1">
       <c r="A137" s="2" t="s">
         <v>414</v>
       </c>
@@ -5599,11 +6170,15 @@
       <c r="D137" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="E137" s="2"/>
-      <c r="F137" s="2"/>
+      <c r="E137" s="8">
+        <v>388</v>
+      </c>
+      <c r="F137" s="8">
+        <v>42</v>
+      </c>
       <c r="G137" s="2"/>
     </row>
-    <row r="138" spans="1:7" ht="39">
+    <row r="138" spans="1:7" ht="27" thickBot="1">
       <c r="A138" s="2" t="s">
         <v>417</v>
       </c>
@@ -5614,11 +6189,15 @@
       <c r="D138" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="E138" s="2"/>
-      <c r="F138" s="2"/>
+      <c r="E138" s="8">
+        <v>301</v>
+      </c>
+      <c r="F138" s="8">
+        <v>32</v>
+      </c>
       <c r="G138" s="2"/>
     </row>
-    <row r="139" spans="1:7" ht="26.25">
+    <row r="139" spans="1:7" ht="15.75" thickBot="1">
       <c r="A139" s="2" t="s">
         <v>420</v>
       </c>
@@ -5629,11 +6208,15 @@
       <c r="D139" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="E139" s="2"/>
-      <c r="F139" s="2"/>
+      <c r="E139" s="8">
+        <v>128</v>
+      </c>
+      <c r="F139" s="8">
+        <v>13</v>
+      </c>
       <c r="G139" s="2"/>
     </row>
-    <row r="140" spans="1:7" ht="39">
+    <row r="140" spans="1:7" ht="27" thickBot="1">
       <c r="A140" s="2" t="s">
         <v>423</v>
       </c>
@@ -5644,11 +6227,15 @@
       <c r="D140" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="E140" s="2"/>
-      <c r="F140" s="2"/>
+      <c r="E140" s="8">
+        <v>928</v>
+      </c>
+      <c r="F140" s="8">
+        <v>100</v>
+      </c>
       <c r="G140" s="2"/>
     </row>
-    <row r="141" spans="1:7" ht="39">
+    <row r="141" spans="1:7" ht="27" thickBot="1">
       <c r="A141" s="2" t="s">
         <v>426</v>
       </c>
@@ -5659,11 +6246,15 @@
       <c r="D141" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="E141" s="2"/>
-      <c r="F141" s="2"/>
+      <c r="E141" s="8">
+        <v>668</v>
+      </c>
+      <c r="F141" s="8">
+        <v>72</v>
+      </c>
       <c r="G141" s="2"/>
     </row>
-    <row r="142" spans="1:7" ht="39">
+    <row r="142" spans="1:7" ht="27" thickBot="1">
       <c r="A142" s="2" t="s">
         <v>429</v>
       </c>
@@ -5674,11 +6265,15 @@
       <c r="D142" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="E142" s="2"/>
-      <c r="F142" s="2"/>
+      <c r="E142" s="8">
+        <v>1919</v>
+      </c>
+      <c r="F142" s="8">
+        <v>208</v>
+      </c>
       <c r="G142" s="2"/>
     </row>
-    <row r="143" spans="1:7" ht="26.25">
+    <row r="143" spans="1:7" ht="27" thickBot="1">
       <c r="A143" s="2" t="s">
         <v>432</v>
       </c>
@@ -5689,11 +6284,15 @@
       <c r="D143" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="E143" s="2"/>
-      <c r="F143" s="2"/>
+      <c r="E143" s="8">
+        <v>1279</v>
+      </c>
+      <c r="F143" s="8">
+        <v>138</v>
+      </c>
       <c r="G143" s="2"/>
     </row>
-    <row r="144" spans="1:7" ht="26.25">
+    <row r="144" spans="1:7" ht="27" thickBot="1">
       <c r="A144" s="2" t="s">
         <v>435</v>
       </c>
@@ -5704,11 +6303,15 @@
       <c r="D144" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="E144" s="2"/>
-      <c r="F144" s="2"/>
+      <c r="E144" s="8">
+        <v>519</v>
+      </c>
+      <c r="F144" s="8">
+        <v>56</v>
+      </c>
       <c r="G144" s="2"/>
     </row>
-    <row r="145" spans="1:7" ht="26.25">
+    <row r="145" spans="1:7" ht="27" thickBot="1">
       <c r="A145" s="2" t="s">
         <v>438</v>
       </c>
@@ -5719,11 +6322,15 @@
       <c r="D145" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="E145" s="2"/>
-      <c r="F145" s="2"/>
+      <c r="E145" s="8">
+        <v>1527</v>
+      </c>
+      <c r="F145" s="8">
+        <v>165</v>
+      </c>
       <c r="G145" s="2"/>
     </row>
-    <row r="146" spans="1:7" ht="26.25">
+    <row r="146" spans="1:7" ht="27" thickBot="1">
       <c r="A146" s="2" t="s">
         <v>441</v>
       </c>
@@ -5734,11 +6341,15 @@
       <c r="D146" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E146" s="2"/>
-      <c r="F146" s="2"/>
+      <c r="E146" s="8">
+        <v>832</v>
+      </c>
+      <c r="F146" s="8">
+        <v>90</v>
+      </c>
       <c r="G146" s="2"/>
     </row>
-    <row r="147" spans="1:7" ht="39">
+    <row r="147" spans="1:7" ht="39.75" thickBot="1">
       <c r="A147" s="2" t="s">
         <v>444</v>
       </c>
@@ -5749,11 +6360,15 @@
       <c r="D147" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="E147" s="2"/>
-      <c r="F147" s="2"/>
+      <c r="E147" s="8">
+        <v>860</v>
+      </c>
+      <c r="F147" s="8">
+        <v>93</v>
+      </c>
       <c r="G147" s="2"/>
     </row>
-    <row r="148" spans="1:7" ht="51.75">
+    <row r="148" spans="1:7" ht="39.75" thickBot="1">
       <c r="A148" s="2" t="s">
         <v>447</v>
       </c>
@@ -5764,11 +6379,15 @@
       <c r="D148" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="E148" s="2"/>
-      <c r="F148" s="2"/>
+      <c r="E148" s="8">
+        <v>2631</v>
+      </c>
+      <c r="F148" s="8">
+        <v>285</v>
+      </c>
       <c r="G148" s="2"/>
     </row>
-    <row r="149" spans="1:7" ht="39">
+    <row r="149" spans="1:7" ht="27" thickBot="1">
       <c r="A149" s="2" t="s">
         <v>450</v>
       </c>
@@ -5779,11 +6398,15 @@
       <c r="D149" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="E149" s="2"/>
-      <c r="F149" s="2"/>
+      <c r="E149" s="8">
+        <v>916</v>
+      </c>
+      <c r="F149" s="8">
+        <v>99</v>
+      </c>
       <c r="G149" s="2"/>
     </row>
-    <row r="150" spans="1:7" ht="26.25">
+    <row r="150" spans="1:7" ht="27" thickBot="1">
       <c r="A150" s="2" t="s">
         <v>453</v>
       </c>
@@ -5794,11 +6417,15 @@
       <c r="D150" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="E150" s="2"/>
-      <c r="F150" s="2"/>
+      <c r="E150" s="8">
+        <v>691</v>
+      </c>
+      <c r="F150" s="8">
+        <v>74</v>
+      </c>
       <c r="G150" s="2"/>
     </row>
-    <row r="151" spans="1:7" ht="64.5">
+    <row r="151" spans="1:7" ht="52.5" thickBot="1">
       <c r="A151" s="2" t="s">
         <v>456</v>
       </c>
@@ -5809,11 +6436,15 @@
       <c r="D151" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="E151" s="2"/>
-      <c r="F151" s="2"/>
+      <c r="E151" s="8">
+        <v>2295</v>
+      </c>
+      <c r="F151" s="8">
+        <v>248</v>
+      </c>
       <c r="G151" s="2"/>
     </row>
-    <row r="152" spans="1:7" ht="90">
+    <row r="152" spans="1:7" ht="65.25" thickBot="1">
       <c r="A152" s="2" t="s">
         <v>459</v>
       </c>
@@ -5824,11 +6455,15 @@
       <c r="D152" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="E152" s="2"/>
-      <c r="F152" s="2"/>
+      <c r="E152" s="8">
+        <v>5565</v>
+      </c>
+      <c r="F152" s="8">
+        <v>603</v>
+      </c>
       <c r="G152" s="2"/>
     </row>
-    <row r="153" spans="1:7" ht="77.25">
+    <row r="153" spans="1:7" ht="65.25" thickBot="1">
       <c r="A153" s="2" t="s">
         <v>462</v>
       </c>
@@ -5839,11 +6474,15 @@
       <c r="D153" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="E153" s="2"/>
-      <c r="F153" s="2"/>
+      <c r="E153" s="8">
+        <v>6318</v>
+      </c>
+      <c r="F153" s="8">
+        <v>684</v>
+      </c>
       <c r="G153" s="2"/>
     </row>
-    <row r="154" spans="1:7" ht="26.25">
+    <row r="154" spans="1:7" ht="27" thickBot="1">
       <c r="A154" s="2" t="s">
         <v>465</v>
       </c>
@@ -5854,11 +6493,15 @@
       <c r="D154" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="E154" s="2"/>
-      <c r="F154" s="2"/>
+      <c r="E154" s="8">
+        <v>755</v>
+      </c>
+      <c r="F154" s="8">
+        <v>81</v>
+      </c>
       <c r="G154" s="2"/>
     </row>
-    <row r="155" spans="1:7" ht="26.25">
+    <row r="155" spans="1:7" ht="27" thickBot="1">
       <c r="A155" s="2" t="s">
         <v>468</v>
       </c>
@@ -5869,16 +6512,20 @@
       <c r="D155" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="E155" s="2"/>
-      <c r="F155" s="2"/>
+      <c r="E155" s="8">
+        <v>746</v>
+      </c>
+      <c r="F155" s="8">
+        <v>80</v>
+      </c>
       <c r="G155" s="2"/>
     </row>
-    <row r="156" spans="1:7" ht="64.5">
+    <row r="156" spans="1:7" ht="65.25" thickBot="1">
       <c r="A156" s="2" t="s">
         <v>471</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>470</v>
@@ -5886,11 +6533,15 @@
       <c r="D156" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="E156" s="2"/>
-      <c r="F156" s="2"/>
+      <c r="E156" s="8">
+        <v>16269</v>
+      </c>
+      <c r="F156" s="8">
+        <v>1763</v>
+      </c>
       <c r="G156" s="2"/>
     </row>
-    <row r="157" spans="1:7" ht="26.25">
+    <row r="157" spans="1:7" ht="15.75" thickBot="1">
       <c r="A157" s="2" t="s">
         <v>474</v>
       </c>
@@ -5901,11 +6552,15 @@
       <c r="D157" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="E157" s="2"/>
-      <c r="F157" s="2"/>
+      <c r="E157" s="8">
+        <v>161</v>
+      </c>
+      <c r="F157" s="8">
+        <v>17</v>
+      </c>
       <c r="G157" s="2"/>
     </row>
-    <row r="158" spans="1:7" ht="26.25">
+    <row r="158" spans="1:7" ht="15.75" thickBot="1">
       <c r="A158" s="2" t="s">
         <v>477</v>
       </c>
@@ -5916,11 +6571,15 @@
       <c r="D158" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="E158" s="2"/>
-      <c r="F158" s="2"/>
+      <c r="E158" s="8">
+        <v>126</v>
+      </c>
+      <c r="F158" s="8">
+        <v>13</v>
+      </c>
       <c r="G158" s="2"/>
     </row>
-    <row r="159" spans="1:7" ht="26.25">
+    <row r="159" spans="1:7" ht="27" thickBot="1">
       <c r="A159" s="2" t="s">
         <v>480</v>
       </c>
@@ -5931,11 +6590,15 @@
       <c r="D159" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="E159" s="2"/>
-      <c r="F159" s="2"/>
+      <c r="E159" s="8">
+        <v>305</v>
+      </c>
+      <c r="F159" s="8">
+        <v>33</v>
+      </c>
       <c r="G159" s="2"/>
     </row>
-    <row r="160" spans="1:7" ht="39">
+    <row r="160" spans="1:7" ht="27" thickBot="1">
       <c r="A160" s="2" t="s">
         <v>483</v>
       </c>
@@ -5946,11 +6609,15 @@
       <c r="D160" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="E160" s="2"/>
-      <c r="F160" s="2"/>
+      <c r="E160" s="8">
+        <v>695</v>
+      </c>
+      <c r="F160" s="8">
+        <v>75</v>
+      </c>
       <c r="G160" s="2"/>
     </row>
-    <row r="161" spans="1:7" ht="39">
+    <row r="161" spans="1:7" ht="27" thickBot="1">
       <c r="A161" s="2" t="s">
         <v>486</v>
       </c>
@@ -5961,11 +6628,15 @@
       <c r="D161" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="E161" s="2"/>
-      <c r="F161" s="2"/>
+      <c r="E161" s="8">
+        <v>1150</v>
+      </c>
+      <c r="F161" s="8">
+        <v>124</v>
+      </c>
       <c r="G161" s="2"/>
     </row>
-    <row r="162" spans="1:7" ht="26.25">
+    <row r="162" spans="1:7" ht="27" thickBot="1">
       <c r="A162" s="2" t="s">
         <v>489</v>
       </c>
@@ -5976,11 +6647,15 @@
       <c r="D162" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="E162" s="2"/>
-      <c r="F162" s="2"/>
+      <c r="E162" s="8">
+        <v>67</v>
+      </c>
+      <c r="F162" s="8">
+        <v>7</v>
+      </c>
       <c r="G162" s="2"/>
     </row>
-    <row r="163" spans="1:7" ht="39">
+    <row r="163" spans="1:7" ht="27" thickBot="1">
       <c r="A163" s="2" t="s">
         <v>492</v>
       </c>
@@ -5991,11 +6666,15 @@
       <c r="D163" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="E163" s="2"/>
-      <c r="F163" s="2"/>
+      <c r="E163" s="8">
+        <v>282</v>
+      </c>
+      <c r="F163" s="8">
+        <v>30</v>
+      </c>
       <c r="G163" s="2"/>
     </row>
-    <row r="164" spans="1:7" ht="39">
+    <row r="164" spans="1:7" ht="27" thickBot="1">
       <c r="A164" s="4" t="s">
         <v>495</v>
       </c>
@@ -6006,11 +6685,15 @@
       <c r="D164" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="E164" s="2"/>
-      <c r="F164" s="2"/>
+      <c r="E164" s="8">
+        <v>331</v>
+      </c>
+      <c r="F164" s="8">
+        <v>35</v>
+      </c>
       <c r="G164" s="2"/>
     </row>
-    <row r="165" spans="1:7" ht="26.25">
+    <row r="165" spans="1:7" ht="27" thickBot="1">
       <c r="A165" s="5" t="s">
         <v>498</v>
       </c>
@@ -6021,11 +6704,15 @@
       <c r="D165" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="E165" s="2"/>
-      <c r="F165" s="2"/>
+      <c r="E165" s="8">
+        <v>50</v>
+      </c>
+      <c r="F165" s="8">
+        <v>5</v>
+      </c>
       <c r="G165" s="2"/>
     </row>
-    <row r="166" spans="1:7" ht="26.25">
+    <row r="166" spans="1:7" ht="27" thickBot="1">
       <c r="A166" s="2" t="s">
         <v>502</v>
       </c>
@@ -6038,11 +6725,15 @@
       <c r="D166" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="E166" s="2"/>
-      <c r="F166" s="2"/>
+      <c r="E166" s="8">
+        <v>107</v>
+      </c>
+      <c r="F166" s="8">
+        <v>11</v>
+      </c>
       <c r="G166" s="2"/>
     </row>
-    <row r="167" spans="1:7" ht="39">
+    <row r="167" spans="1:7" ht="27" thickBot="1">
       <c r="A167" s="2" t="s">
         <v>505</v>
       </c>
@@ -6053,11 +6744,15 @@
       <c r="D167" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="E167" s="2"/>
-      <c r="F167" s="2"/>
+      <c r="E167" s="8">
+        <v>371</v>
+      </c>
+      <c r="F167" s="8">
+        <v>40</v>
+      </c>
       <c r="G167" s="2"/>
     </row>
-    <row r="168" spans="1:7" ht="39">
+    <row r="168" spans="1:7" ht="27" thickBot="1">
       <c r="A168" s="2" t="s">
         <v>508</v>
       </c>
@@ -6068,11 +6763,15 @@
       <c r="D168" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="E168" s="2"/>
-      <c r="F168" s="2"/>
+      <c r="E168" s="8">
+        <v>331</v>
+      </c>
+      <c r="F168" s="8">
+        <v>35</v>
+      </c>
       <c r="G168" s="2"/>
     </row>
-    <row r="169" spans="1:7" ht="39">
+    <row r="169" spans="1:7" ht="27" thickBot="1">
       <c r="A169" s="2" t="s">
         <v>511</v>
       </c>
@@ -6083,11 +6782,15 @@
       <c r="D169" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="E169" s="2"/>
-      <c r="F169" s="2"/>
+      <c r="E169" s="8">
+        <v>319</v>
+      </c>
+      <c r="F169" s="8">
+        <v>34</v>
+      </c>
       <c r="G169" s="2"/>
     </row>
-    <row r="170" spans="1:7" ht="26.25">
+    <row r="170" spans="1:7" ht="27" thickBot="1">
       <c r="A170" s="2" t="s">
         <v>514</v>
       </c>
@@ -6098,11 +6801,15 @@
       <c r="D170" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="E170" s="2"/>
-      <c r="F170" s="2"/>
+      <c r="E170" s="8">
+        <v>123</v>
+      </c>
+      <c r="F170" s="8">
+        <v>13</v>
+      </c>
       <c r="G170" s="2"/>
     </row>
-    <row r="171" spans="1:7" ht="26.25">
+    <row r="171" spans="1:7" ht="27" thickBot="1">
       <c r="A171" s="2" t="s">
         <v>517</v>
       </c>
@@ -6113,11 +6820,15 @@
       <c r="D171" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="E171" s="2"/>
-      <c r="F171" s="2"/>
+      <c r="E171" s="8">
+        <v>618</v>
+      </c>
+      <c r="F171" s="8">
+        <v>67</v>
+      </c>
       <c r="G171" s="2"/>
     </row>
-    <row r="172" spans="1:7" ht="39">
+    <row r="172" spans="1:7" ht="39.75" thickBot="1">
       <c r="A172" s="2" t="s">
         <v>520</v>
       </c>
@@ -6128,11 +6839,15 @@
       <c r="D172" s="6" t="s">
         <v>521</v>
       </c>
-      <c r="E172" s="2"/>
-      <c r="F172" s="2"/>
+      <c r="E172" s="8">
+        <v>1088</v>
+      </c>
+      <c r="F172" s="8">
+        <v>118</v>
+      </c>
       <c r="G172" s="2"/>
     </row>
-    <row r="173" spans="1:7" ht="26.25">
+    <row r="173" spans="1:7" ht="27" thickBot="1">
       <c r="A173" s="2" t="s">
         <v>523</v>
       </c>
@@ -6143,11 +6858,15 @@
       <c r="D173" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="E173" s="2"/>
-      <c r="F173" s="2"/>
+      <c r="E173" s="8">
+        <v>241</v>
+      </c>
+      <c r="F173" s="8">
+        <v>26</v>
+      </c>
       <c r="G173" s="2"/>
     </row>
-    <row r="174" spans="1:7" ht="26.25">
+    <row r="174" spans="1:7" ht="27" thickBot="1">
       <c r="A174" s="2" t="s">
         <v>526</v>
       </c>
@@ -6158,11 +6877,15 @@
       <c r="D174" s="6" t="s">
         <v>527</v>
       </c>
-      <c r="E174" s="2"/>
-      <c r="F174" s="2"/>
+      <c r="E174" s="8">
+        <v>948</v>
+      </c>
+      <c r="F174" s="8">
+        <v>102</v>
+      </c>
       <c r="G174" s="2"/>
     </row>
-    <row r="175" spans="1:7" ht="39">
+    <row r="175" spans="1:7" ht="27" thickBot="1">
       <c r="A175" s="2" t="s">
         <v>529</v>
       </c>
@@ -6173,11 +6896,15 @@
       <c r="D175" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="E175" s="2"/>
-      <c r="F175" s="2"/>
+      <c r="E175" s="8">
+        <v>1089</v>
+      </c>
+      <c r="F175" s="8">
+        <v>118</v>
+      </c>
       <c r="G175" s="2"/>
     </row>
-    <row r="176" spans="1:7" ht="39">
+    <row r="176" spans="1:7" ht="27" thickBot="1">
       <c r="A176" s="2" t="s">
         <v>532</v>
       </c>
@@ -6188,11 +6915,15 @@
       <c r="D176" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="E176" s="2"/>
-      <c r="F176" s="2"/>
+      <c r="E176" s="8">
+        <v>748</v>
+      </c>
+      <c r="F176" s="8">
+        <v>81</v>
+      </c>
       <c r="G176" s="2"/>
     </row>
-    <row r="177" spans="1:7" ht="39">
+    <row r="177" spans="1:7" ht="27" thickBot="1">
       <c r="A177" s="2" t="s">
         <v>535</v>
       </c>
@@ -6203,11 +6934,15 @@
       <c r="D177" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="E177" s="2"/>
-      <c r="F177" s="2"/>
+      <c r="E177" s="8">
+        <v>849</v>
+      </c>
+      <c r="F177" s="8">
+        <v>92</v>
+      </c>
       <c r="G177" s="2"/>
     </row>
-    <row r="178" spans="1:7" ht="39">
+    <row r="178" spans="1:7" ht="27" thickBot="1">
       <c r="A178" s="2" t="s">
         <v>538</v>
       </c>
@@ -6218,11 +6953,15 @@
       <c r="D178" s="6" t="s">
         <v>539</v>
       </c>
-      <c r="E178" s="2"/>
-      <c r="F178" s="2"/>
+      <c r="E178" s="8">
+        <v>1010</v>
+      </c>
+      <c r="F178" s="8">
+        <v>109</v>
+      </c>
       <c r="G178" s="2"/>
     </row>
-    <row r="179" spans="1:7" ht="39">
+    <row r="179" spans="1:7" ht="27" thickBot="1">
       <c r="A179" s="2" t="s">
         <v>541</v>
       </c>
@@ -6233,11 +6972,15 @@
       <c r="D179" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="E179" s="2"/>
-      <c r="F179" s="2"/>
+      <c r="E179" s="8">
+        <v>1067</v>
+      </c>
+      <c r="F179" s="8">
+        <v>115</v>
+      </c>
       <c r="G179" s="2"/>
     </row>
-    <row r="180" spans="1:7" ht="26.25">
+    <row r="180" spans="1:7" ht="27" thickBot="1">
       <c r="A180" s="2" t="s">
         <v>544</v>
       </c>
@@ -6248,2362 +6991,2988 @@
       <c r="D180" s="6" t="s">
         <v>545</v>
       </c>
-      <c r="E180" s="2"/>
-      <c r="F180" s="2" t="s">
-        <v>546</v>
+      <c r="E180" s="8">
+        <v>242</v>
+      </c>
+      <c r="F180" s="8">
+        <v>26</v>
       </c>
       <c r="G180" s="2"/>
     </row>
-    <row r="181" spans="1:7" ht="39">
+    <row r="181" spans="1:7" ht="39.75" thickBot="1">
       <c r="A181" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B181" s="2"/>
       <c r="C181" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>549</v>
-      </c>
-      <c r="E181" s="2"/>
-      <c r="F181" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="E181" s="8">
+        <v>1738</v>
+      </c>
+      <c r="F181" s="8">
+        <v>188</v>
+      </c>
       <c r="G181" s="2"/>
     </row>
-    <row r="182" spans="1:7" ht="39">
+    <row r="182" spans="1:7" ht="27" thickBot="1">
       <c r="A182" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B182" s="2"/>
       <c r="C182" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>552</v>
-      </c>
-      <c r="E182" s="2"/>
-      <c r="F182" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="E182" s="8">
+        <v>2410</v>
+      </c>
+      <c r="F182" s="8">
+        <v>261</v>
+      </c>
       <c r="G182" s="2"/>
     </row>
-    <row r="183" spans="1:7" ht="77.25">
+    <row r="183" spans="1:7" ht="52.5" thickBot="1">
       <c r="A183" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B183" s="2"/>
       <c r="C183" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>555</v>
-      </c>
-      <c r="E183" s="2"/>
-      <c r="F183" s="2"/>
+        <v>554</v>
+      </c>
+      <c r="E183" s="8">
+        <v>5219</v>
+      </c>
+      <c r="F183" s="8">
+        <v>565</v>
+      </c>
       <c r="G183" s="2"/>
     </row>
-    <row r="184" spans="1:7" ht="39">
+    <row r="184" spans="1:7" ht="27" thickBot="1">
       <c r="A184" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B184" s="2"/>
       <c r="C184" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="E184" s="2"/>
-      <c r="F184" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="E184" s="8">
+        <v>785</v>
+      </c>
+      <c r="F184" s="8">
+        <v>85</v>
+      </c>
       <c r="G184" s="2"/>
     </row>
-    <row r="185" spans="1:7" ht="39">
+    <row r="185" spans="1:7" ht="39.75" thickBot="1">
       <c r="A185" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B185" s="2"/>
       <c r="C185" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>561</v>
-      </c>
-      <c r="E185" s="2"/>
-      <c r="F185" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="E185" s="8">
+        <v>2089</v>
+      </c>
+      <c r="F185" s="8">
+        <v>226</v>
+      </c>
       <c r="G185" s="2"/>
     </row>
-    <row r="186" spans="1:7" ht="51.75">
+    <row r="186" spans="1:7" ht="39.75" thickBot="1">
       <c r="A186" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B186" s="2"/>
       <c r="C186" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="E186" s="2"/>
-      <c r="F186" s="2"/>
+        <v>563</v>
+      </c>
+      <c r="E186" s="8">
+        <v>1729</v>
+      </c>
+      <c r="F186" s="8">
+        <v>187</v>
+      </c>
       <c r="G186" s="2"/>
     </row>
-    <row r="187" spans="1:7" ht="39">
+    <row r="187" spans="1:7" ht="39.75" thickBot="1">
       <c r="A187" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B187" s="2"/>
       <c r="C187" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D187" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="E187" s="8">
+        <v>1180</v>
+      </c>
+      <c r="F187" s="8">
+        <v>127</v>
+      </c>
+      <c r="G187" s="2"/>
+    </row>
+    <row r="188" spans="1:7" ht="39.75" thickBot="1">
+      <c r="A188" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C188" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="E187" s="2"/>
-      <c r="F187" s="2"/>
-      <c r="G187" s="2"/>
-    </row>
-    <row r="188" spans="1:7" ht="51.75">
-      <c r="A188" s="2" t="s">
+      <c r="D188" s="6" t="s">
         <v>569</v>
       </c>
-      <c r="B188" s="2" t="s">
+      <c r="E188" s="8">
+        <v>7038</v>
+      </c>
+      <c r="F188" s="8">
+        <v>762</v>
+      </c>
+      <c r="G188" s="2"/>
+    </row>
+    <row r="189" spans="1:7" ht="27" thickBot="1">
+      <c r="A189" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B189" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="C188" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="D188" s="6" t="s">
+      <c r="C189" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E188" s="2"/>
-      <c r="F188" s="2"/>
-      <c r="G188" s="2"/>
-    </row>
-    <row r="189" spans="1:7" ht="39">
-      <c r="A189" s="2" t="s">
+      <c r="D189" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="B189" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="D189" s="6" t="s">
-        <v>573</v>
-      </c>
-      <c r="E189" s="2"/>
-      <c r="F189" s="2"/>
+      <c r="E189" s="8">
+        <v>1071</v>
+      </c>
+      <c r="F189" s="8">
+        <v>116</v>
+      </c>
       <c r="G189" s="2"/>
     </row>
-    <row r="190" spans="1:7" ht="51.75">
+    <row r="190" spans="1:7" ht="39.75" thickBot="1">
       <c r="A190" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B190" s="2"/>
       <c r="C190" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>576</v>
-      </c>
-      <c r="E190" s="2"/>
-      <c r="F190" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="E190" s="8">
+        <v>4611</v>
+      </c>
+      <c r="F190" s="8">
+        <v>499</v>
+      </c>
       <c r="G190" s="2"/>
     </row>
-    <row r="191" spans="1:7" ht="90">
+    <row r="191" spans="1:7" ht="65.25" thickBot="1">
       <c r="A191" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B191" s="2"/>
       <c r="C191" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="E191" s="2"/>
-      <c r="F191" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="E191" s="8">
+        <v>8838</v>
+      </c>
+      <c r="F191" s="8">
+        <v>957</v>
+      </c>
       <c r="G191" s="2"/>
     </row>
-    <row r="192" spans="1:7" ht="26.25">
+    <row r="192" spans="1:7" ht="27" thickBot="1">
       <c r="A192" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B192" s="2"/>
       <c r="C192" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>582</v>
-      </c>
-      <c r="E192" s="2"/>
-      <c r="F192" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="E192" s="8">
+        <v>281</v>
+      </c>
+      <c r="F192" s="8">
+        <v>30</v>
+      </c>
       <c r="G192" s="2"/>
     </row>
-    <row r="193" spans="1:7" ht="39">
+    <row r="193" spans="1:7" ht="27" thickBot="1">
       <c r="A193" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B193" s="2"/>
       <c r="C193" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>585</v>
-      </c>
-      <c r="E193" s="2"/>
-      <c r="F193" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="E193" s="8">
+        <v>501</v>
+      </c>
+      <c r="F193" s="8">
+        <v>54</v>
+      </c>
       <c r="G193" s="2"/>
     </row>
-    <row r="194" spans="1:7" ht="26.25">
+    <row r="194" spans="1:7" ht="27" thickBot="1">
       <c r="A194" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B194" s="2"/>
       <c r="C194" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>588</v>
-      </c>
-      <c r="E194" s="2"/>
-      <c r="F194" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="E194" s="8">
+        <v>520</v>
+      </c>
+      <c r="F194" s="8">
+        <v>56</v>
+      </c>
       <c r="G194" s="2"/>
     </row>
-    <row r="195" spans="1:7" ht="39">
+    <row r="195" spans="1:7" ht="27" thickBot="1">
       <c r="A195" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B195" s="2"/>
       <c r="C195" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>591</v>
-      </c>
-      <c r="E195" s="2"/>
-      <c r="F195" s="2"/>
+        <v>590</v>
+      </c>
+      <c r="E195" s="8">
+        <v>922</v>
+      </c>
+      <c r="F195" s="8">
+        <v>100</v>
+      </c>
       <c r="G195" s="2"/>
     </row>
-    <row r="196" spans="1:7" ht="39">
+    <row r="196" spans="1:7" ht="27" thickBot="1">
       <c r="A196" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B196" s="2"/>
       <c r="C196" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="E196" s="2"/>
-      <c r="F196" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="E196" s="8">
+        <v>1717</v>
+      </c>
+      <c r="F196" s="8">
+        <v>186</v>
+      </c>
       <c r="G196" s="2"/>
     </row>
-    <row r="197" spans="1:7" ht="26.25">
+    <row r="197" spans="1:7" ht="27" thickBot="1">
       <c r="A197" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B197" s="2"/>
       <c r="C197" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="E197" s="2"/>
-      <c r="F197" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="E197" s="8">
+        <v>505</v>
+      </c>
+      <c r="F197" s="8">
+        <v>54</v>
+      </c>
       <c r="G197" s="2"/>
     </row>
-    <row r="198" spans="1:7" ht="26.25">
+    <row r="198" spans="1:7" ht="27" thickBot="1">
       <c r="A198" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B198" s="2"/>
       <c r="C198" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>600</v>
-      </c>
-      <c r="E198" s="2"/>
-      <c r="F198" s="2"/>
+        <v>599</v>
+      </c>
+      <c r="E198" s="8">
+        <v>168</v>
+      </c>
+      <c r="F198" s="8">
+        <v>18</v>
+      </c>
       <c r="G198" s="2"/>
     </row>
-    <row r="199" spans="1:7" ht="39">
+    <row r="199" spans="1:7" ht="27" thickBot="1">
       <c r="A199" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B199" s="2"/>
       <c r="C199" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>603</v>
-      </c>
-      <c r="E199" s="2"/>
-      <c r="F199" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="E199" s="8">
+        <v>2102</v>
+      </c>
+      <c r="F199" s="8">
+        <v>227</v>
+      </c>
       <c r="G199" s="2"/>
     </row>
-    <row r="200" spans="1:7" ht="64.5">
+    <row r="200" spans="1:7" ht="52.5" thickBot="1">
       <c r="A200" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>606</v>
-      </c>
-      <c r="E200" s="2"/>
-      <c r="F200" s="2"/>
+        <v>605</v>
+      </c>
+      <c r="E200" s="8">
+        <v>10095</v>
+      </c>
+      <c r="F200" s="8">
+        <v>1094</v>
+      </c>
       <c r="G200" s="2"/>
     </row>
-    <row r="201" spans="1:7" ht="64.5">
+    <row r="201" spans="1:7" ht="52.5" thickBot="1">
       <c r="A201" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B201" s="2"/>
       <c r="C201" s="2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>609</v>
-      </c>
-      <c r="E201" s="2"/>
-      <c r="F201" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="E201" s="8">
+        <v>10896</v>
+      </c>
+      <c r="F201" s="8">
+        <v>1180</v>
+      </c>
       <c r="G201" s="2"/>
     </row>
-    <row r="202" spans="1:7" ht="39">
+    <row r="202" spans="1:7" ht="27" thickBot="1">
       <c r="A202" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B202" s="2"/>
       <c r="C202" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>612</v>
-      </c>
-      <c r="E202" s="2"/>
-      <c r="F202" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="E202" s="8">
+        <v>1960</v>
+      </c>
+      <c r="F202" s="8">
+        <v>212</v>
+      </c>
       <c r="G202" s="2"/>
     </row>
-    <row r="203" spans="1:7" ht="39">
+    <row r="203" spans="1:7" ht="27" thickBot="1">
       <c r="A203" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B203" s="2"/>
       <c r="C203" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>615</v>
-      </c>
-      <c r="E203" s="2"/>
-      <c r="F203" s="2"/>
+        <v>614</v>
+      </c>
+      <c r="E203" s="8">
+        <v>2135</v>
+      </c>
+      <c r="F203" s="8">
+        <v>231</v>
+      </c>
       <c r="G203" s="2"/>
     </row>
-    <row r="204" spans="1:7" ht="64.5">
+    <row r="204" spans="1:7" ht="52.5" thickBot="1">
       <c r="A204" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B204" s="2"/>
       <c r="C204" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>618</v>
-      </c>
-      <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
+        <v>617</v>
+      </c>
+      <c r="E204" s="8">
+        <v>4038</v>
+      </c>
+      <c r="F204" s="8">
+        <v>437</v>
+      </c>
       <c r="G204" s="2"/>
     </row>
-    <row r="205" spans="1:7" ht="26.25">
+    <row r="205" spans="1:7" ht="15.75" thickBot="1">
       <c r="A205" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B205" s="2"/>
       <c r="C205" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>621</v>
-      </c>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
+        <v>620</v>
+      </c>
+      <c r="E205" s="8">
+        <v>224</v>
+      </c>
+      <c r="F205" s="8">
+        <v>24</v>
+      </c>
       <c r="G205" s="2"/>
     </row>
-    <row r="206" spans="1:7" ht="39">
+    <row r="206" spans="1:7" ht="27" thickBot="1">
       <c r="A206" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B206" s="2"/>
       <c r="C206" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>624</v>
-      </c>
-      <c r="E206" s="2"/>
-      <c r="F206" s="2"/>
+        <v>623</v>
+      </c>
+      <c r="E206" s="8">
+        <v>883</v>
+      </c>
+      <c r="F206" s="8">
+        <v>95</v>
+      </c>
       <c r="G206" s="2"/>
     </row>
-    <row r="207" spans="1:7" ht="26.25">
+    <row r="207" spans="1:7" ht="27" thickBot="1">
       <c r="A207" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B207" s="2"/>
       <c r="C207" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>627</v>
-      </c>
-      <c r="E207" s="2"/>
-      <c r="F207" s="2"/>
+        <v>626</v>
+      </c>
+      <c r="E207" s="8">
+        <v>753</v>
+      </c>
+      <c r="F207" s="8">
+        <v>81</v>
+      </c>
       <c r="G207" s="2"/>
     </row>
-    <row r="208" spans="1:7" ht="26.25">
+    <row r="208" spans="1:7" ht="27" thickBot="1">
       <c r="A208" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B208" s="2"/>
       <c r="C208" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>630</v>
-      </c>
-      <c r="E208" s="2"/>
-      <c r="F208" s="2"/>
+        <v>629</v>
+      </c>
+      <c r="E208" s="8">
+        <v>409</v>
+      </c>
+      <c r="F208" s="8">
+        <v>44</v>
+      </c>
       <c r="G208" s="2"/>
     </row>
-    <row r="209" spans="1:7" ht="64.5">
+    <row r="209" spans="1:7" ht="52.5" thickBot="1">
       <c r="A209" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B209" s="2"/>
       <c r="C209" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>633</v>
-      </c>
-      <c r="E209" s="2"/>
-      <c r="F209" s="2"/>
+        <v>632</v>
+      </c>
+      <c r="E209" s="8">
+        <v>3090</v>
+      </c>
+      <c r="F209" s="8">
+        <v>334</v>
+      </c>
       <c r="G209" s="2"/>
     </row>
-    <row r="210" spans="1:7" ht="26.25">
+    <row r="210" spans="1:7" ht="27" thickBot="1">
       <c r="A210" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B210" s="2"/>
       <c r="C210" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D210" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="E210" s="8">
+        <v>124</v>
+      </c>
+      <c r="F210" s="8">
+        <v>13</v>
+      </c>
+      <c r="G210" s="2"/>
+    </row>
+    <row r="211" spans="1:7" ht="90.75" thickBot="1">
+      <c r="A211" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C211" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="E210" s="2"/>
-      <c r="F210" s="2"/>
-      <c r="G210" s="2"/>
-    </row>
-    <row r="211" spans="1:7" ht="90">
-      <c r="A211" s="2" t="s">
+      <c r="D211" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="B211" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="D211" s="6" t="s">
-        <v>639</v>
-      </c>
-      <c r="E211" s="2"/>
-      <c r="F211" s="2"/>
+      <c r="E211" s="8">
+        <v>15731</v>
+      </c>
+      <c r="F211" s="8">
+        <v>1704</v>
+      </c>
       <c r="G211" s="2"/>
     </row>
-    <row r="212" spans="1:7" ht="64.5">
+    <row r="212" spans="1:7" ht="52.5" thickBot="1">
       <c r="A212" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B212" s="2"/>
       <c r="C212" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>642</v>
-      </c>
-      <c r="E212" s="2"/>
-      <c r="F212" s="2"/>
+        <v>641</v>
+      </c>
+      <c r="E212" s="8">
+        <v>3306</v>
+      </c>
+      <c r="F212" s="8">
+        <v>358</v>
+      </c>
       <c r="G212" s="2"/>
     </row>
-    <row r="213" spans="1:7" ht="26.25">
+    <row r="213" spans="1:7" ht="27" thickBot="1">
       <c r="A213" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B213" s="2"/>
       <c r="C213" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>645</v>
-      </c>
-      <c r="E213" s="2"/>
-      <c r="F213" s="2"/>
+        <v>644</v>
+      </c>
+      <c r="E213" s="8">
+        <v>1588</v>
+      </c>
+      <c r="F213" s="8">
+        <v>172</v>
+      </c>
       <c r="G213" s="2"/>
     </row>
-    <row r="214" spans="1:7" ht="39">
+    <row r="214" spans="1:7" ht="27" thickBot="1">
       <c r="A214" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B214" s="2"/>
       <c r="C214" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>648</v>
-      </c>
-      <c r="E214" s="2"/>
-      <c r="F214" s="2"/>
+        <v>647</v>
+      </c>
+      <c r="E214" s="8">
+        <v>831</v>
+      </c>
+      <c r="F214" s="8">
+        <v>90</v>
+      </c>
       <c r="G214" s="2"/>
     </row>
-    <row r="215" spans="1:7" ht="39">
+    <row r="215" spans="1:7" ht="39.75" thickBot="1">
       <c r="A215" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B215" s="2"/>
       <c r="C215" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>651</v>
-      </c>
-      <c r="E215" s="2"/>
-      <c r="F215" s="2"/>
+        <v>650</v>
+      </c>
+      <c r="E215" s="8">
+        <v>1292</v>
+      </c>
+      <c r="F215" s="8">
+        <v>140</v>
+      </c>
       <c r="G215" s="2"/>
     </row>
-    <row r="216" spans="1:7" ht="39">
+    <row r="216" spans="1:7" ht="27" thickBot="1">
       <c r="A216" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B216" s="2"/>
       <c r="C216" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>654</v>
-      </c>
-      <c r="E216" s="2"/>
-      <c r="F216" s="2"/>
+        <v>653</v>
+      </c>
+      <c r="E216" s="8">
+        <v>932</v>
+      </c>
+      <c r="F216" s="8">
+        <v>101</v>
+      </c>
       <c r="G216" s="2"/>
     </row>
-    <row r="217" spans="1:7" ht="26.25">
+    <row r="217" spans="1:7" ht="15.75" thickBot="1">
       <c r="A217" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B217" s="2"/>
       <c r="C217" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D217" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="E217" s="8">
+        <v>209</v>
+      </c>
+      <c r="F217" s="8">
+        <v>22</v>
+      </c>
+      <c r="G217" s="2"/>
+    </row>
+    <row r="218" spans="1:7" ht="39.75" thickBot="1">
+      <c r="A218" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C218" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="E217" s="2"/>
-      <c r="F217" s="2"/>
-      <c r="G217" s="2"/>
-    </row>
-    <row r="218" spans="1:7" ht="39">
-      <c r="A218" s="2" t="s">
+      <c r="D218" s="6" t="s">
         <v>659</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="D218" s="6" t="s">
-        <v>660</v>
-      </c>
-      <c r="E218" s="2"/>
-      <c r="F218" s="2"/>
+      <c r="E218" s="8">
+        <v>4532</v>
+      </c>
+      <c r="F218" s="8">
+        <v>491</v>
+      </c>
       <c r="G218" s="2"/>
     </row>
-    <row r="219" spans="1:7" ht="51.75">
+    <row r="219" spans="1:7" ht="39.75" thickBot="1">
       <c r="A219" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B219" s="2"/>
       <c r="C219" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>663</v>
-      </c>
-      <c r="E219" s="2"/>
-      <c r="F219" s="2"/>
+        <v>662</v>
+      </c>
+      <c r="E219" s="8">
+        <v>1989</v>
+      </c>
+      <c r="F219" s="8">
+        <v>215</v>
+      </c>
       <c r="G219" s="2"/>
     </row>
-    <row r="220" spans="1:7" ht="39">
+    <row r="220" spans="1:7" ht="27" thickBot="1">
       <c r="A220" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B220" s="2"/>
       <c r="C220" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>666</v>
-      </c>
-      <c r="E220" s="2"/>
-      <c r="F220" s="2"/>
+        <v>665</v>
+      </c>
+      <c r="E220" s="8">
+        <v>1574</v>
+      </c>
+      <c r="F220" s="8">
+        <v>170</v>
+      </c>
       <c r="G220" s="2"/>
     </row>
-    <row r="221" spans="1:7" ht="26.25">
+    <row r="221" spans="1:7" ht="27" thickBot="1">
       <c r="A221" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B221" s="2"/>
       <c r="C221" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>669</v>
-      </c>
-      <c r="E221" s="2"/>
-      <c r="F221" s="2"/>
+        <v>668</v>
+      </c>
+      <c r="E221" s="8">
+        <v>1322</v>
+      </c>
+      <c r="F221" s="8">
+        <v>143</v>
+      </c>
       <c r="G221" s="2"/>
     </row>
-    <row r="222" spans="1:7" ht="39">
+    <row r="222" spans="1:7" ht="27" thickBot="1">
       <c r="A222" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B222" s="2"/>
       <c r="C222" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>672</v>
-      </c>
-      <c r="E222" s="2"/>
-      <c r="F222" s="2"/>
+        <v>671</v>
+      </c>
+      <c r="E222" s="8">
+        <v>1281</v>
+      </c>
+      <c r="F222" s="8">
+        <v>138</v>
+      </c>
       <c r="G222" s="2"/>
     </row>
-    <row r="223" spans="1:7" ht="39">
+    <row r="223" spans="1:7" ht="27" thickBot="1">
       <c r="A223" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B223" s="2"/>
       <c r="C223" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>675</v>
-      </c>
-      <c r="E223" s="2"/>
-      <c r="F223" s="2"/>
+        <v>674</v>
+      </c>
+      <c r="E223" s="8">
+        <v>9624</v>
+      </c>
+      <c r="F223" s="8">
+        <v>1043</v>
+      </c>
       <c r="G223" s="2"/>
     </row>
-    <row r="224" spans="1:7" ht="39">
+    <row r="224" spans="1:7" ht="39.75" thickBot="1">
       <c r="A224" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B224" s="2"/>
       <c r="C224" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>678</v>
-      </c>
-      <c r="E224" s="2"/>
-      <c r="F224" s="2"/>
+        <v>677</v>
+      </c>
+      <c r="E224" s="8">
+        <v>5639</v>
+      </c>
+      <c r="F224" s="8">
+        <v>611</v>
+      </c>
       <c r="G224" s="2"/>
     </row>
-    <row r="225" spans="1:7" ht="26.25">
+    <row r="225" spans="1:7" ht="27" thickBot="1">
       <c r="A225" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B225" s="2"/>
       <c r="C225" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>681</v>
-      </c>
-      <c r="E225" s="2"/>
-      <c r="F225" s="2"/>
+        <v>680</v>
+      </c>
+      <c r="E225" s="8">
+        <v>823</v>
+      </c>
+      <c r="F225" s="8">
+        <v>89</v>
+      </c>
       <c r="G225" s="2"/>
     </row>
-    <row r="226" spans="1:7" ht="26.25">
+    <row r="226" spans="1:7" ht="27" thickBot="1">
       <c r="A226" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B226" s="2"/>
       <c r="C226" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>684</v>
-      </c>
-      <c r="E226" s="2"/>
-      <c r="F226" s="2"/>
+        <v>683</v>
+      </c>
+      <c r="E226" s="8">
+        <v>673</v>
+      </c>
+      <c r="F226" s="8">
+        <v>72</v>
+      </c>
       <c r="G226" s="2"/>
     </row>
-    <row r="227" spans="1:7" ht="26.25">
+    <row r="227" spans="1:7" ht="27" thickBot="1">
       <c r="A227" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B227" s="2"/>
       <c r="C227" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>687</v>
-      </c>
-      <c r="E227" s="2"/>
-      <c r="F227" s="2"/>
+        <v>686</v>
+      </c>
+      <c r="E227" s="8">
+        <v>921</v>
+      </c>
+      <c r="F227" s="8">
+        <v>99</v>
+      </c>
       <c r="G227" s="2"/>
     </row>
-    <row r="228" spans="1:7" ht="39">
+    <row r="228" spans="1:7" ht="27" thickBot="1">
       <c r="A228" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B228" s="2"/>
       <c r="C228" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>690</v>
-      </c>
-      <c r="E228" s="2"/>
-      <c r="F228" s="2"/>
+        <v>689</v>
+      </c>
+      <c r="E228" s="8">
+        <v>1734</v>
+      </c>
+      <c r="F228" s="8">
+        <v>187</v>
+      </c>
       <c r="G228" s="2"/>
     </row>
-    <row r="229" spans="1:7" ht="39">
+    <row r="229" spans="1:7" ht="27" thickBot="1">
       <c r="A229" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B229" s="2"/>
       <c r="C229" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>693</v>
-      </c>
-      <c r="E229" s="2"/>
-      <c r="F229" s="2"/>
+        <v>692</v>
+      </c>
+      <c r="E229" s="8">
+        <v>770</v>
+      </c>
+      <c r="F229" s="8">
+        <v>83</v>
+      </c>
       <c r="G229" s="2"/>
     </row>
-    <row r="230" spans="1:7" ht="77.25">
+    <row r="230" spans="1:7" ht="52.5" thickBot="1">
       <c r="A230" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B230" s="2"/>
       <c r="C230" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D230" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="E230" s="8">
+        <v>10152</v>
+      </c>
+      <c r="F230" s="8">
+        <v>1100</v>
+      </c>
+      <c r="G230" s="2"/>
+    </row>
+    <row r="231" spans="1:7" ht="39.75" thickBot="1">
+      <c r="A231" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C231" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="E230" s="2"/>
-      <c r="F230" s="2"/>
-      <c r="G230" s="2"/>
-    </row>
-    <row r="231" spans="1:7" ht="51.75">
-      <c r="A231" s="2" t="s">
+      <c r="D231" s="6" t="s">
         <v>698</v>
       </c>
-      <c r="B231" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="D231" s="6" t="s">
-        <v>699</v>
-      </c>
-      <c r="E231" s="2"/>
-      <c r="F231" s="2"/>
+      <c r="E231" s="8">
+        <v>5283</v>
+      </c>
+      <c r="F231" s="8">
+        <v>572</v>
+      </c>
       <c r="G231" s="2"/>
     </row>
-    <row r="232" spans="1:7" ht="26.25">
+    <row r="232" spans="1:7" ht="27" thickBot="1">
       <c r="A232" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B232" s="2"/>
       <c r="C232" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>702</v>
-      </c>
-      <c r="E232" s="2"/>
-      <c r="F232" s="2"/>
+        <v>701</v>
+      </c>
+      <c r="E232" s="8">
+        <v>1475</v>
+      </c>
+      <c r="F232" s="8">
+        <v>159</v>
+      </c>
       <c r="G232" s="2"/>
     </row>
-    <row r="233" spans="1:7" ht="39">
+    <row r="233" spans="1:7" ht="27" thickBot="1">
       <c r="A233" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B233" s="2"/>
       <c r="C233" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>705</v>
-      </c>
-      <c r="E233" s="2"/>
-      <c r="F233" s="2"/>
+        <v>704</v>
+      </c>
+      <c r="E233" s="8">
+        <v>1237</v>
+      </c>
+      <c r="F233" s="8">
+        <v>134</v>
+      </c>
       <c r="G233" s="2"/>
     </row>
-    <row r="234" spans="1:7" ht="39">
+    <row r="234" spans="1:7" ht="27" thickBot="1">
       <c r="A234" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B234" s="2"/>
       <c r="C234" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>708</v>
-      </c>
-      <c r="E234" s="2"/>
-      <c r="F234" s="2"/>
+        <v>707</v>
+      </c>
+      <c r="E234" s="8">
+        <v>3426</v>
+      </c>
+      <c r="F234" s="8">
+        <v>371</v>
+      </c>
       <c r="G234" s="2"/>
     </row>
-    <row r="235" spans="1:7" ht="39">
+    <row r="235" spans="1:7" ht="27" thickBot="1">
       <c r="A235" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B235" s="2"/>
       <c r="C235" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>711</v>
-      </c>
-      <c r="E235" s="2"/>
-      <c r="F235" s="2"/>
+        <v>710</v>
+      </c>
+      <c r="E235" s="8">
+        <v>1552</v>
+      </c>
+      <c r="F235" s="8">
+        <v>168</v>
+      </c>
       <c r="G235" s="2"/>
     </row>
-    <row r="236" spans="1:7" ht="39">
+    <row r="236" spans="1:7" ht="27" thickBot="1">
       <c r="A236" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B236" s="2"/>
       <c r="C236" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>714</v>
-      </c>
-      <c r="E236" s="2"/>
-      <c r="F236" s="2"/>
+        <v>713</v>
+      </c>
+      <c r="E236" s="8">
+        <v>1693</v>
+      </c>
+      <c r="F236" s="8">
+        <v>183</v>
+      </c>
       <c r="G236" s="2"/>
     </row>
-    <row r="237" spans="1:7" ht="39">
+    <row r="237" spans="1:7" ht="27" thickBot="1">
       <c r="A237" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B237" s="2"/>
       <c r="C237" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>717</v>
-      </c>
-      <c r="E237" s="2"/>
-      <c r="F237" s="2"/>
+        <v>716</v>
+      </c>
+      <c r="E237" s="8">
+        <v>469</v>
+      </c>
+      <c r="F237" s="8">
+        <v>50</v>
+      </c>
       <c r="G237" s="2"/>
     </row>
-    <row r="238" spans="1:7" ht="26.25">
+    <row r="238" spans="1:7" ht="15.75" thickBot="1">
       <c r="A238" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B238" s="2"/>
       <c r="C238" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>720</v>
-      </c>
-      <c r="E238" s="2"/>
-      <c r="F238" s="2"/>
+        <v>719</v>
+      </c>
+      <c r="E238" s="8">
+        <v>57</v>
+      </c>
+      <c r="F238" s="8">
+        <v>6</v>
+      </c>
       <c r="G238" s="2"/>
     </row>
-    <row r="239" spans="1:7" ht="39">
+    <row r="239" spans="1:7" ht="27" thickBot="1">
       <c r="A239" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B239" s="2"/>
       <c r="C239" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>723</v>
-      </c>
-      <c r="E239" s="2"/>
-      <c r="F239" s="2"/>
+        <v>722</v>
+      </c>
+      <c r="E239" s="8">
+        <v>628</v>
+      </c>
+      <c r="F239" s="8">
+        <v>68</v>
+      </c>
       <c r="G239" s="2"/>
     </row>
-    <row r="240" spans="1:7" ht="39">
+    <row r="240" spans="1:7" ht="27" thickBot="1">
       <c r="A240" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B240" s="2"/>
       <c r="C240" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>726</v>
-      </c>
-      <c r="E240" s="2"/>
-      <c r="F240" s="2"/>
+        <v>725</v>
+      </c>
+      <c r="E240" s="8">
+        <v>2719</v>
+      </c>
+      <c r="F240" s="8">
+        <v>294</v>
+      </c>
       <c r="G240" s="2"/>
     </row>
-    <row r="241" spans="1:7" ht="26.25">
+    <row r="241" spans="1:7" ht="27" thickBot="1">
       <c r="A241" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B241" s="2"/>
       <c r="C241" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>729</v>
-      </c>
-      <c r="E241" s="2"/>
-      <c r="F241" s="2"/>
+        <v>728</v>
+      </c>
+      <c r="E241" s="8">
+        <v>598</v>
+      </c>
+      <c r="F241" s="8">
+        <v>64</v>
+      </c>
       <c r="G241" s="2"/>
     </row>
-    <row r="242" spans="1:7" ht="64.5">
+    <row r="242" spans="1:7" ht="52.5" thickBot="1">
       <c r="A242" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B242" s="2"/>
       <c r="C242" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>732</v>
-      </c>
-      <c r="E242" s="2"/>
-      <c r="F242" s="2"/>
+        <v>731</v>
+      </c>
+      <c r="E242" s="8">
+        <v>4416</v>
+      </c>
+      <c r="F242" s="8">
+        <v>478</v>
+      </c>
       <c r="G242" s="2"/>
     </row>
-    <row r="243" spans="1:7" ht="26.25">
+    <row r="243" spans="1:7" ht="15.75" thickBot="1">
       <c r="A243" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B243" s="2"/>
       <c r="C243" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>735</v>
-      </c>
-      <c r="E243" s="2"/>
-      <c r="F243" s="2"/>
+        <v>734</v>
+      </c>
+      <c r="E243" s="8">
+        <v>40</v>
+      </c>
+      <c r="F243" s="8">
+        <v>4</v>
+      </c>
       <c r="G243" s="2"/>
     </row>
-    <row r="244" spans="1:7" ht="39">
+    <row r="244" spans="1:7" ht="27" thickBot="1">
       <c r="A244" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B244" s="2"/>
       <c r="C244" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>738</v>
-      </c>
-      <c r="E244" s="2"/>
-      <c r="F244" s="2"/>
+        <v>737</v>
+      </c>
+      <c r="E244" s="8">
+        <v>1708</v>
+      </c>
+      <c r="F244" s="8">
+        <v>185</v>
+      </c>
       <c r="G244" s="2"/>
     </row>
-    <row r="245" spans="1:7" ht="26.25">
+    <row r="245" spans="1:7" ht="15.75" thickBot="1">
       <c r="A245" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B245" s="2"/>
       <c r="C245" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>741</v>
-      </c>
-      <c r="E245" s="2"/>
-      <c r="F245" s="2"/>
+        <v>740</v>
+      </c>
+      <c r="E245" s="8">
+        <v>87</v>
+      </c>
+      <c r="F245" s="8">
+        <v>9</v>
+      </c>
       <c r="G245" s="2"/>
     </row>
-    <row r="246" spans="1:7" ht="26.25">
+    <row r="246" spans="1:7" ht="27" thickBot="1">
       <c r="A246" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B246" s="2"/>
       <c r="C246" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>744</v>
-      </c>
-      <c r="E246" s="2"/>
-      <c r="F246" s="2"/>
+        <v>743</v>
+      </c>
+      <c r="E246" s="8">
+        <v>304</v>
+      </c>
+      <c r="F246" s="8">
+        <v>33</v>
+      </c>
       <c r="G246" s="2"/>
     </row>
-    <row r="247" spans="1:7" ht="26.25">
+    <row r="247" spans="1:7" ht="15.75" thickBot="1">
       <c r="A247" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B247" s="2"/>
       <c r="C247" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>747</v>
-      </c>
-      <c r="E247" s="2"/>
-      <c r="F247" s="2"/>
+        <v>746</v>
+      </c>
+      <c r="E247" s="8">
+        <v>58</v>
+      </c>
+      <c r="F247" s="8">
+        <v>6</v>
+      </c>
       <c r="G247" s="2"/>
     </row>
-    <row r="248" spans="1:7" ht="26.25">
+    <row r="248" spans="1:7" ht="27" thickBot="1">
       <c r="A248" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B248" s="2"/>
       <c r="C248" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>750</v>
-      </c>
-      <c r="E248" s="2"/>
-      <c r="F248" s="2"/>
+        <v>749</v>
+      </c>
+      <c r="E248" s="8">
+        <v>223</v>
+      </c>
+      <c r="F248" s="8">
+        <v>24</v>
+      </c>
       <c r="G248" s="2"/>
     </row>
-    <row r="249" spans="1:7" ht="26.25">
+    <row r="249" spans="1:7" ht="27" thickBot="1">
       <c r="A249" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B249" s="2"/>
       <c r="C249" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>753</v>
-      </c>
-      <c r="E249" s="2"/>
-      <c r="F249" s="2"/>
+        <v>752</v>
+      </c>
+      <c r="E249" s="8">
+        <v>77</v>
+      </c>
+      <c r="F249" s="8">
+        <v>8</v>
+      </c>
       <c r="G249" s="2"/>
     </row>
-    <row r="250" spans="1:7" ht="26.25">
+    <row r="250" spans="1:7" ht="27" thickBot="1">
       <c r="A250" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B250" s="2"/>
       <c r="C250" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>756</v>
-      </c>
-      <c r="E250" s="2"/>
-      <c r="F250" s="2"/>
+        <v>755</v>
+      </c>
+      <c r="E250" s="8">
+        <v>783</v>
+      </c>
+      <c r="F250" s="8">
+        <v>84</v>
+      </c>
       <c r="G250" s="2"/>
     </row>
-    <row r="251" spans="1:7" ht="26.25">
+    <row r="251" spans="1:7" ht="27" thickBot="1">
       <c r="A251" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B251" s="2"/>
       <c r="C251" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>759</v>
-      </c>
-      <c r="E251" s="2"/>
-      <c r="F251" s="2"/>
+        <v>758</v>
+      </c>
+      <c r="E251" s="8">
+        <v>654</v>
+      </c>
+      <c r="F251" s="8">
+        <v>70</v>
+      </c>
       <c r="G251" s="2"/>
     </row>
-    <row r="252" spans="1:7" ht="39">
+    <row r="252" spans="1:7" ht="27" thickBot="1">
       <c r="A252" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B252" s="2"/>
       <c r="C252" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>762</v>
-      </c>
-      <c r="E252" s="2"/>
-      <c r="F252" s="2"/>
+        <v>761</v>
+      </c>
+      <c r="E252" s="8">
+        <v>2511</v>
+      </c>
+      <c r="F252" s="8">
+        <v>272</v>
+      </c>
       <c r="G252" s="2"/>
     </row>
-    <row r="253" spans="1:7" ht="39">
+    <row r="253" spans="1:7" ht="27" thickBot="1">
       <c r="A253" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B253" s="2"/>
       <c r="C253" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>765</v>
-      </c>
-      <c r="E253" s="2"/>
-      <c r="F253" s="2"/>
+        <v>764</v>
+      </c>
+      <c r="E253" s="8">
+        <v>416</v>
+      </c>
+      <c r="F253" s="8">
+        <v>45</v>
+      </c>
       <c r="G253" s="2"/>
     </row>
-    <row r="254" spans="1:7" ht="26.25">
+    <row r="254" spans="1:7" ht="27" thickBot="1">
       <c r="A254" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B254" s="2"/>
       <c r="C254" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>768</v>
-      </c>
-      <c r="E254" s="2"/>
-      <c r="F254" s="2"/>
+        <v>767</v>
+      </c>
+      <c r="E254" s="8">
+        <v>312</v>
+      </c>
+      <c r="F254" s="8">
+        <v>33</v>
+      </c>
       <c r="G254" s="2"/>
     </row>
-    <row r="255" spans="1:7" ht="26.25">
+    <row r="255" spans="1:7" ht="15.75" thickBot="1">
       <c r="A255" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B255" s="2"/>
       <c r="C255" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>771</v>
-      </c>
-      <c r="E255" s="2"/>
-      <c r="F255" s="2"/>
+        <v>770</v>
+      </c>
+      <c r="E255" s="8">
+        <v>405</v>
+      </c>
+      <c r="F255" s="8">
+        <v>43</v>
+      </c>
       <c r="G255" s="2"/>
     </row>
-    <row r="256" spans="1:7" ht="26.25">
+    <row r="256" spans="1:7" ht="27" thickBot="1">
       <c r="A256" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B256" s="2"/>
       <c r="C256" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>774</v>
-      </c>
-      <c r="E256" s="2"/>
-      <c r="F256" s="2"/>
+        <v>773</v>
+      </c>
+      <c r="E256" s="8">
+        <v>434</v>
+      </c>
+      <c r="F256" s="8">
+        <v>47</v>
+      </c>
       <c r="G256" s="2"/>
     </row>
-    <row r="257" spans="1:7" ht="26.25">
+    <row r="257" spans="1:7" ht="27" thickBot="1">
       <c r="A257" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B257" s="2"/>
       <c r="C257" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="E257" s="2"/>
-      <c r="F257" s="2"/>
+        <v>776</v>
+      </c>
+      <c r="E257" s="8">
+        <v>477</v>
+      </c>
+      <c r="F257" s="8">
+        <v>51</v>
+      </c>
       <c r="G257" s="2"/>
     </row>
-    <row r="258" spans="1:7" ht="26.25">
+    <row r="258" spans="1:7" ht="27" thickBot="1">
       <c r="A258" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B258" s="2"/>
       <c r="C258" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D258" s="6" t="s">
-        <v>780</v>
-      </c>
-      <c r="E258" s="2"/>
-      <c r="F258" s="2"/>
+        <v>779</v>
+      </c>
+      <c r="E258" s="8">
+        <v>102</v>
+      </c>
+      <c r="F258" s="8">
+        <v>11</v>
+      </c>
       <c r="G258" s="2"/>
     </row>
-    <row r="259" spans="1:7" ht="26.25">
+    <row r="259" spans="1:7" ht="27" thickBot="1">
       <c r="A259" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B259" s="2"/>
       <c r="C259" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>783</v>
-      </c>
-      <c r="E259" s="2"/>
-      <c r="F259" s="2"/>
+        <v>782</v>
+      </c>
+      <c r="E259" s="8">
+        <v>155</v>
+      </c>
+      <c r="F259" s="8">
+        <v>16</v>
+      </c>
       <c r="G259" s="2"/>
     </row>
-    <row r="260" spans="1:7" ht="26.25">
+    <row r="260" spans="1:7" ht="27" thickBot="1">
       <c r="A260" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B260" s="2"/>
       <c r="C260" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>786</v>
-      </c>
-      <c r="E260" s="2"/>
-      <c r="F260" s="2"/>
+        <v>785</v>
+      </c>
+      <c r="E260" s="8">
+        <v>159</v>
+      </c>
+      <c r="F260" s="8">
+        <v>17</v>
+      </c>
       <c r="G260" s="2"/>
     </row>
-    <row r="261" spans="1:7" ht="26.25">
+    <row r="261" spans="1:7" ht="27" thickBot="1">
       <c r="A261" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B261" s="2"/>
       <c r="C261" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>789</v>
-      </c>
-      <c r="E261" s="2"/>
-      <c r="F261" s="2"/>
+        <v>788</v>
+      </c>
+      <c r="E261" s="8">
+        <v>219</v>
+      </c>
+      <c r="F261" s="8">
+        <v>23</v>
+      </c>
       <c r="G261" s="2"/>
     </row>
-    <row r="262" spans="1:7" ht="26.25">
+    <row r="262" spans="1:7" ht="27" thickBot="1">
       <c r="A262" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B262" s="2"/>
       <c r="C262" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D262" s="6" t="s">
-        <v>792</v>
-      </c>
-      <c r="E262" s="2"/>
-      <c r="F262" s="2"/>
+        <v>791</v>
+      </c>
+      <c r="E262" s="8">
+        <v>509</v>
+      </c>
+      <c r="F262" s="8">
+        <v>55</v>
+      </c>
       <c r="G262" s="2"/>
     </row>
-    <row r="263" spans="1:7" ht="26.25">
+    <row r="263" spans="1:7" ht="27" thickBot="1">
       <c r="A263" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B263" s="2"/>
       <c r="C263" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>795</v>
-      </c>
-      <c r="E263" s="2"/>
-      <c r="F263" s="2"/>
+        <v>794</v>
+      </c>
+      <c r="E263" s="8">
+        <v>375</v>
+      </c>
+      <c r="F263" s="8">
+        <v>40</v>
+      </c>
       <c r="G263" s="2"/>
     </row>
-    <row r="264" spans="1:7" ht="39">
+    <row r="264" spans="1:7" ht="27" thickBot="1">
       <c r="A264" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B264" s="2"/>
       <c r="C264" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D264" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="E264" s="2"/>
-      <c r="F264" s="2"/>
+        <v>797</v>
+      </c>
+      <c r="E264" s="8">
+        <v>443</v>
+      </c>
+      <c r="F264" s="8">
+        <v>48</v>
+      </c>
       <c r="G264" s="2"/>
     </row>
-    <row r="265" spans="1:7" ht="26.25">
+    <row r="265" spans="1:7" ht="27" thickBot="1">
       <c r="A265" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B265" s="2"/>
       <c r="C265" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>801</v>
-      </c>
-      <c r="E265" s="2"/>
-      <c r="F265" s="2"/>
+        <v>800</v>
+      </c>
+      <c r="E265" s="8">
+        <v>294</v>
+      </c>
+      <c r="F265" s="8">
+        <v>31</v>
+      </c>
       <c r="G265" s="2"/>
     </row>
-    <row r="266" spans="1:7" ht="26.25">
+    <row r="266" spans="1:7" ht="27" thickBot="1">
       <c r="A266" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B266" s="2"/>
       <c r="C266" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>804</v>
-      </c>
-      <c r="E266" s="2"/>
-      <c r="F266" s="2"/>
+        <v>803</v>
+      </c>
+      <c r="E266" s="8">
+        <v>1179</v>
+      </c>
+      <c r="F266" s="8">
+        <v>127</v>
+      </c>
       <c r="G266" s="2"/>
     </row>
-    <row r="267" spans="1:7" ht="26.25">
+    <row r="267" spans="1:7" ht="27" thickBot="1">
       <c r="A267" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B267" s="2"/>
       <c r="C267" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>807</v>
-      </c>
-      <c r="E267" s="2"/>
-      <c r="F267" s="2"/>
+        <v>806</v>
+      </c>
+      <c r="E267" s="8">
+        <v>452</v>
+      </c>
+      <c r="F267" s="8">
+        <v>49</v>
+      </c>
       <c r="G267" s="2"/>
     </row>
-    <row r="268" spans="1:7" ht="26.25">
+    <row r="268" spans="1:7" ht="27" thickBot="1">
       <c r="A268" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B268" s="2"/>
       <c r="C268" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>810</v>
-      </c>
-      <c r="E268" s="2"/>
-      <c r="F268" s="2"/>
+        <v>809</v>
+      </c>
+      <c r="E268" s="8">
+        <v>160</v>
+      </c>
+      <c r="F268" s="8">
+        <v>17</v>
+      </c>
       <c r="G268" s="2"/>
     </row>
-    <row r="269" spans="1:7" ht="26.25">
+    <row r="269" spans="1:7" ht="15.75" thickBot="1">
       <c r="A269" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B269" s="2"/>
       <c r="C269" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="E269" s="2"/>
-      <c r="F269" s="2"/>
+        <v>812</v>
+      </c>
+      <c r="E269" s="8">
+        <v>142</v>
+      </c>
+      <c r="F269" s="8">
+        <v>15</v>
+      </c>
       <c r="G269" s="2"/>
     </row>
-    <row r="270" spans="1:7" ht="39">
+    <row r="270" spans="1:7" ht="27" thickBot="1">
       <c r="A270" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B270" s="2"/>
       <c r="C270" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>816</v>
-      </c>
-      <c r="E270" s="2"/>
-      <c r="F270" s="2"/>
+        <v>815</v>
+      </c>
+      <c r="E270" s="8">
+        <v>249</v>
+      </c>
+      <c r="F270" s="8">
+        <v>27</v>
+      </c>
       <c r="G270" s="2"/>
     </row>
-    <row r="271" spans="1:7" ht="26.25">
+    <row r="271" spans="1:7" ht="27" thickBot="1">
       <c r="A271" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B271" s="2"/>
       <c r="C271" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>819</v>
-      </c>
-      <c r="E271" s="2"/>
-      <c r="F271" s="2"/>
+        <v>818</v>
+      </c>
+      <c r="E271" s="8">
+        <v>169</v>
+      </c>
+      <c r="F271" s="8">
+        <v>18</v>
+      </c>
       <c r="G271" s="2"/>
     </row>
-    <row r="272" spans="1:7" ht="26.25">
+    <row r="272" spans="1:7" ht="27" thickBot="1">
       <c r="A272" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B272" s="2"/>
       <c r="C272" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D272" s="6" t="s">
-        <v>822</v>
-      </c>
-      <c r="E272" s="2"/>
-      <c r="F272" s="2"/>
+        <v>821</v>
+      </c>
+      <c r="E272" s="8">
+        <v>533</v>
+      </c>
+      <c r="F272" s="8">
+        <v>57</v>
+      </c>
       <c r="G272" s="2"/>
     </row>
-    <row r="273" spans="1:7" ht="26.25">
+    <row r="273" spans="1:7" ht="27" thickBot="1">
       <c r="A273" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B273" s="2"/>
       <c r="C273" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>825</v>
-      </c>
-      <c r="E273" s="2"/>
-      <c r="F273" s="2"/>
+        <v>824</v>
+      </c>
+      <c r="E273" s="8">
+        <v>464</v>
+      </c>
+      <c r="F273" s="8">
+        <v>50</v>
+      </c>
       <c r="G273" s="2"/>
     </row>
-    <row r="274" spans="1:7" ht="26.25">
+    <row r="274" spans="1:7" ht="27" thickBot="1">
       <c r="A274" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B274" s="2"/>
       <c r="C274" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>828</v>
-      </c>
-      <c r="E274" s="2"/>
-      <c r="F274" s="2"/>
+        <v>827</v>
+      </c>
+      <c r="E274" s="8">
+        <v>420</v>
+      </c>
+      <c r="F274" s="8">
+        <v>45</v>
+      </c>
       <c r="G274" s="2"/>
     </row>
-    <row r="275" spans="1:7" ht="51.75">
+    <row r="275" spans="1:7" ht="39.75" thickBot="1">
       <c r="A275" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B275" s="2"/>
       <c r="C275" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>831</v>
-      </c>
-      <c r="E275" s="2"/>
-      <c r="F275" s="2"/>
+        <v>830</v>
+      </c>
+      <c r="E275" s="8">
+        <v>2611</v>
+      </c>
+      <c r="F275" s="8">
+        <v>283</v>
+      </c>
       <c r="G275" s="2"/>
     </row>
-    <row r="276" spans="1:7" ht="26.25">
+    <row r="276" spans="1:7" ht="27" thickBot="1">
       <c r="A276" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B276" s="2"/>
       <c r="C276" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>834</v>
-      </c>
-      <c r="E276" s="2"/>
-      <c r="F276" s="2"/>
+        <v>833</v>
+      </c>
+      <c r="E276" s="8">
+        <v>328</v>
+      </c>
+      <c r="F276" s="8">
+        <v>35</v>
+      </c>
       <c r="G276" s="2"/>
     </row>
-    <row r="277" spans="1:7" ht="26.25">
+    <row r="277" spans="1:7" ht="27" thickBot="1">
       <c r="A277" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B277" s="2"/>
       <c r="C277" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D277" s="6" t="s">
-        <v>837</v>
-      </c>
-      <c r="E277" s="2"/>
-      <c r="F277" s="2"/>
+        <v>836</v>
+      </c>
+      <c r="E277" s="8">
+        <v>592</v>
+      </c>
+      <c r="F277" s="8">
+        <v>64</v>
+      </c>
       <c r="G277" s="2"/>
     </row>
-    <row r="278" spans="1:7" ht="26.25">
+    <row r="278" spans="1:7" ht="15.75" thickBot="1">
       <c r="A278" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B278" s="2"/>
       <c r="C278" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D278" s="6" t="s">
-        <v>840</v>
-      </c>
-      <c r="E278" s="2"/>
-      <c r="F278" s="2"/>
+        <v>839</v>
+      </c>
+      <c r="E278" s="8">
+        <v>112</v>
+      </c>
+      <c r="F278" s="8">
+        <v>12</v>
+      </c>
       <c r="G278" s="2"/>
     </row>
-    <row r="279" spans="1:7" ht="39">
+    <row r="279" spans="1:7" ht="27" thickBot="1">
       <c r="A279" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B279" s="2"/>
       <c r="C279" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D279" s="6" t="s">
-        <v>843</v>
-      </c>
-      <c r="E279" s="2"/>
-      <c r="F279" s="2"/>
+        <v>842</v>
+      </c>
+      <c r="E279" s="8">
+        <v>712</v>
+      </c>
+      <c r="F279" s="8">
+        <v>77</v>
+      </c>
       <c r="G279" s="2"/>
     </row>
-    <row r="280" spans="1:7" ht="39">
+    <row r="280" spans="1:7" ht="27" thickBot="1">
       <c r="A280" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B280" s="2"/>
       <c r="C280" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D280" s="6" t="s">
-        <v>846</v>
-      </c>
-      <c r="E280" s="2"/>
-      <c r="F280" s="2"/>
+        <v>845</v>
+      </c>
+      <c r="E280" s="8">
+        <v>1280</v>
+      </c>
+      <c r="F280" s="8">
+        <v>138</v>
+      </c>
       <c r="G280" s="2"/>
     </row>
-    <row r="281" spans="1:7" ht="39">
+    <row r="281" spans="1:7" ht="27" thickBot="1">
       <c r="A281" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B281" s="2"/>
       <c r="C281" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D281" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="E281" s="2"/>
-      <c r="F281" s="2"/>
+        <v>848</v>
+      </c>
+      <c r="E281" s="8">
+        <v>1511</v>
+      </c>
+      <c r="F281" s="8">
+        <v>163</v>
+      </c>
       <c r="G281" s="2"/>
     </row>
-    <row r="282" spans="1:7" ht="39">
+    <row r="282" spans="1:7" ht="27" thickBot="1">
       <c r="A282" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B282" s="2"/>
       <c r="C282" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>852</v>
-      </c>
-      <c r="E282" s="2"/>
-      <c r="F282" s="2"/>
+        <v>851</v>
+      </c>
+      <c r="E282" s="8">
+        <v>2447</v>
+      </c>
+      <c r="F282" s="8">
+        <v>265</v>
+      </c>
       <c r="G282" s="2"/>
     </row>
-    <row r="283" spans="1:7" ht="26.25">
+    <row r="283" spans="1:7" ht="27" thickBot="1">
       <c r="A283" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B283" s="2"/>
       <c r="C283" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D283" s="6" t="s">
-        <v>855</v>
-      </c>
-      <c r="E283" s="2"/>
-      <c r="F283" s="2"/>
+        <v>854</v>
+      </c>
+      <c r="E283" s="8">
+        <v>1691</v>
+      </c>
+      <c r="F283" s="8">
+        <v>183</v>
+      </c>
       <c r="G283" s="2"/>
     </row>
-    <row r="284" spans="1:7" ht="39">
+    <row r="284" spans="1:7" ht="27" thickBot="1">
       <c r="A284" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B284" s="2"/>
       <c r="C284" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D284" s="6" t="s">
-        <v>858</v>
-      </c>
-      <c r="E284" s="2"/>
-      <c r="F284" s="2"/>
+        <v>857</v>
+      </c>
+      <c r="E284" s="8">
+        <v>1760</v>
+      </c>
+      <c r="F284" s="8">
+        <v>190</v>
+      </c>
       <c r="G284" s="2"/>
     </row>
-    <row r="285" spans="1:7" ht="26.25">
+    <row r="285" spans="1:7" ht="27" thickBot="1">
       <c r="A285" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B285" s="2"/>
       <c r="C285" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>861</v>
-      </c>
-      <c r="E285" s="2"/>
-      <c r="F285" s="2"/>
+        <v>860</v>
+      </c>
+      <c r="E285" s="8">
+        <v>558</v>
+      </c>
+      <c r="F285" s="8">
+        <v>60</v>
+      </c>
       <c r="G285" s="2"/>
     </row>
-    <row r="286" spans="1:7" ht="26.25">
+    <row r="286" spans="1:7" ht="27" thickBot="1">
       <c r="A286" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B286" s="2"/>
       <c r="C286" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>864</v>
-      </c>
-      <c r="E286" s="2"/>
-      <c r="F286" s="2"/>
+        <v>863</v>
+      </c>
+      <c r="E286" s="8">
+        <v>443</v>
+      </c>
+      <c r="F286" s="8">
+        <v>48</v>
+      </c>
       <c r="G286" s="2"/>
     </row>
-    <row r="287" spans="1:7" ht="39">
+    <row r="287" spans="1:7" ht="27" thickBot="1">
       <c r="A287" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B287" s="2"/>
       <c r="C287" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D287" s="6" t="s">
-        <v>867</v>
-      </c>
-      <c r="E287" s="2"/>
-      <c r="F287" s="2"/>
+        <v>866</v>
+      </c>
+      <c r="E287" s="8">
+        <v>585</v>
+      </c>
+      <c r="F287" s="8">
+        <v>63</v>
+      </c>
       <c r="G287" s="2"/>
     </row>
-    <row r="288" spans="1:7" ht="26.25">
+    <row r="288" spans="1:7" ht="27" thickBot="1">
       <c r="A288" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B288" s="2"/>
       <c r="C288" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D288" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="E288" s="2"/>
-      <c r="F288" s="2"/>
+        <v>869</v>
+      </c>
+      <c r="E288" s="8">
+        <v>472</v>
+      </c>
+      <c r="F288" s="8">
+        <v>51</v>
+      </c>
       <c r="G288" s="2"/>
     </row>
-    <row r="289" spans="1:7" ht="26.25">
+    <row r="289" spans="1:7" ht="27" thickBot="1">
       <c r="A289" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B289" s="2"/>
       <c r="C289" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D289" s="6" t="s">
-        <v>873</v>
-      </c>
-      <c r="E289" s="2"/>
-      <c r="F289" s="2"/>
+        <v>872</v>
+      </c>
+      <c r="E289" s="8">
+        <v>233</v>
+      </c>
+      <c r="F289" s="8">
+        <v>25</v>
+      </c>
       <c r="G289" s="2"/>
     </row>
-    <row r="290" spans="1:7" ht="39">
+    <row r="290" spans="1:7" ht="27" thickBot="1">
       <c r="A290" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B290" s="2"/>
       <c r="C290" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D290" s="6" t="s">
+        <v>875</v>
+      </c>
+      <c r="E290" s="8">
+        <v>1692</v>
+      </c>
+      <c r="F290" s="8">
+        <v>183</v>
+      </c>
+      <c r="G290" s="2"/>
+    </row>
+    <row r="291" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A291" s="2" t="s">
         <v>876</v>
-      </c>
-      <c r="E290" s="2"/>
-      <c r="F290" s="2"/>
-      <c r="G290" s="2"/>
-    </row>
-    <row r="291" spans="1:7">
-      <c r="A291" s="2" t="s">
-        <v>877</v>
       </c>
       <c r="B291" s="2"/>
       <c r="C291" s="6" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="D291" s="6" t="s">
-        <v>878</v>
-      </c>
-      <c r="E291" s="2"/>
-      <c r="F291" s="2"/>
+        <v>877</v>
+      </c>
+      <c r="E291" s="8">
+        <v>376</v>
+      </c>
+      <c r="F291" s="8">
+        <v>40</v>
+      </c>
       <c r="G291" s="2"/>
     </row>
-    <row r="292" spans="1:7" ht="39">
+    <row r="292" spans="1:7" ht="27" thickBot="1">
       <c r="A292" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B292" s="2"/>
       <c r="C292" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D292" s="6" t="s">
-        <v>881</v>
-      </c>
-      <c r="E292" s="2"/>
-      <c r="F292" s="2"/>
+        <v>880</v>
+      </c>
+      <c r="E292" s="8">
+        <v>606</v>
+      </c>
+      <c r="F292" s="8">
+        <v>65</v>
+      </c>
       <c r="G292" s="2"/>
     </row>
-    <row r="293" spans="1:7" ht="39">
+    <row r="293" spans="1:7" ht="27" thickBot="1">
       <c r="A293" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B293" s="2"/>
       <c r="C293" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D293" s="6" t="s">
-        <v>884</v>
-      </c>
-      <c r="E293" s="2"/>
-      <c r="F293" s="2"/>
+        <v>883</v>
+      </c>
+      <c r="E293" s="8">
+        <v>765</v>
+      </c>
+      <c r="F293" s="8">
+        <v>82</v>
+      </c>
       <c r="G293" s="2"/>
     </row>
-    <row r="294" spans="1:7" ht="26.25">
+    <row r="294" spans="1:7" ht="27" thickBot="1">
       <c r="A294" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B294" s="2"/>
       <c r="C294" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D294" s="6" t="s">
-        <v>887</v>
-      </c>
-      <c r="E294" s="2"/>
-      <c r="F294" s="2"/>
+        <v>886</v>
+      </c>
+      <c r="E294" s="8">
+        <v>874</v>
+      </c>
+      <c r="F294" s="8">
+        <v>94</v>
+      </c>
       <c r="G294" s="2"/>
     </row>
-    <row r="295" spans="1:7" ht="26.25">
+    <row r="295" spans="1:7" ht="27" thickBot="1">
       <c r="A295" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B295" s="2"/>
       <c r="C295" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>890</v>
-      </c>
-      <c r="E295" s="2"/>
-      <c r="F295" s="2"/>
+        <v>889</v>
+      </c>
+      <c r="E295" s="8">
+        <v>479</v>
+      </c>
+      <c r="F295" s="8">
+        <v>51</v>
+      </c>
       <c r="G295" s="2"/>
     </row>
-    <row r="296" spans="1:7" ht="26.25">
+    <row r="296" spans="1:7" ht="27" thickBot="1">
       <c r="A296" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B296" s="2"/>
       <c r="C296" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D296" s="6" t="s">
-        <v>893</v>
-      </c>
-      <c r="E296" s="2"/>
-      <c r="F296" s="2"/>
+        <v>892</v>
+      </c>
+      <c r="E296" s="8">
+        <v>276</v>
+      </c>
+      <c r="F296" s="8">
+        <v>30</v>
+      </c>
       <c r="G296" s="2"/>
     </row>
-    <row r="297" spans="1:7" ht="26.25">
+    <row r="297" spans="1:7" ht="27" thickBot="1">
       <c r="A297" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B297" s="2"/>
       <c r="C297" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>896</v>
-      </c>
-      <c r="E297" s="2"/>
-      <c r="F297" s="2"/>
+        <v>895</v>
+      </c>
+      <c r="E297" s="8">
+        <v>1510</v>
+      </c>
+      <c r="F297" s="8">
+        <v>163</v>
+      </c>
       <c r="G297" s="2"/>
     </row>
-    <row r="298" spans="1:7" ht="26.25">
+    <row r="298" spans="1:7" ht="27" thickBot="1">
       <c r="A298" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B298" s="2"/>
       <c r="C298" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>899</v>
-      </c>
-      <c r="E298" s="2"/>
-      <c r="F298" s="2"/>
+        <v>898</v>
+      </c>
+      <c r="E298" s="8">
+        <v>291</v>
+      </c>
+      <c r="F298" s="8">
+        <v>31</v>
+      </c>
       <c r="G298" s="2"/>
     </row>
-    <row r="299" spans="1:7" ht="39">
+    <row r="299" spans="1:7" ht="27" thickBot="1">
       <c r="A299" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B299" s="2"/>
       <c r="C299" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>902</v>
-      </c>
-      <c r="E299" s="2"/>
-      <c r="F299" s="2"/>
+        <v>901</v>
+      </c>
+      <c r="E299" s="8">
+        <v>630</v>
+      </c>
+      <c r="F299" s="8">
+        <v>68</v>
+      </c>
       <c r="G299" s="2"/>
     </row>
-    <row r="300" spans="1:7" ht="26.25">
+    <row r="300" spans="1:7" ht="27" thickBot="1">
       <c r="A300" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B300" s="2"/>
       <c r="C300" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D300" s="6" t="s">
-        <v>905</v>
-      </c>
-      <c r="E300" s="2"/>
-      <c r="F300" s="2"/>
+        <v>904</v>
+      </c>
+      <c r="E300" s="8">
+        <v>535</v>
+      </c>
+      <c r="F300" s="8">
+        <v>58</v>
+      </c>
       <c r="G300" s="2"/>
     </row>
-    <row r="301" spans="1:7" ht="26.25">
+    <row r="301" spans="1:7" ht="27" thickBot="1">
       <c r="A301" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B301" s="2"/>
       <c r="C301" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>908</v>
-      </c>
-      <c r="E301" s="2"/>
-      <c r="F301" s="2"/>
+        <v>907</v>
+      </c>
+      <c r="E301" s="8">
+        <v>675</v>
+      </c>
+      <c r="F301" s="8">
+        <v>73</v>
+      </c>
       <c r="G301" s="2"/>
     </row>
-    <row r="302" spans="1:7" ht="26.25">
+    <row r="302" spans="1:7" ht="27" thickBot="1">
       <c r="A302" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B302" s="2"/>
       <c r="C302" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="D302" s="6" t="s">
-        <v>911</v>
-      </c>
-      <c r="E302" s="2"/>
-      <c r="F302" s="2"/>
+        <v>910</v>
+      </c>
+      <c r="E302" s="8">
+        <v>110</v>
+      </c>
+      <c r="F302" s="8">
+        <v>11</v>
+      </c>
       <c r="G302" s="2"/>
     </row>
-    <row r="303" spans="1:7" ht="26.25">
+    <row r="303" spans="1:7" ht="27" thickBot="1">
       <c r="A303" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B303" s="2"/>
       <c r="C303" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D303" s="6" t="s">
-        <v>914</v>
-      </c>
-      <c r="E303" s="2"/>
-      <c r="F303" s="2"/>
+        <v>913</v>
+      </c>
+      <c r="E303" s="8">
+        <v>81</v>
+      </c>
+      <c r="F303" s="8">
+        <v>8</v>
+      </c>
       <c r="G303" s="2"/>
     </row>
-    <row r="304" spans="1:7" ht="26.25">
+    <row r="304" spans="1:7" ht="27" thickBot="1">
       <c r="A304" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B304" s="2"/>
       <c r="C304" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D304" s="6" t="s">
-        <v>917</v>
-      </c>
-      <c r="E304" s="2"/>
-      <c r="F304" s="2"/>
+        <v>916</v>
+      </c>
+      <c r="E304" s="8">
+        <v>194</v>
+      </c>
+      <c r="F304" s="8">
+        <v>21</v>
+      </c>
       <c r="G304" s="2"/>
     </row>
-    <row r="305" spans="1:7" ht="26.25">
+    <row r="305" spans="1:7" ht="27" thickBot="1">
       <c r="A305" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B305" s="2"/>
       <c r="C305" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>920</v>
-      </c>
-      <c r="E305" s="2"/>
-      <c r="F305" s="2"/>
+        <v>919</v>
+      </c>
+      <c r="E305" s="8">
+        <v>115</v>
+      </c>
+      <c r="F305" s="8">
+        <v>12</v>
+      </c>
       <c r="G305" s="2"/>
     </row>
-    <row r="306" spans="1:7" ht="26.25">
+    <row r="306" spans="1:7" ht="27" thickBot="1">
       <c r="A306" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B306" s="2"/>
       <c r="C306" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D306" s="6" t="s">
-        <v>923</v>
-      </c>
-      <c r="E306" s="2"/>
-      <c r="F306" s="2"/>
+        <v>922</v>
+      </c>
+      <c r="E306" s="8">
+        <v>116</v>
+      </c>
+      <c r="F306" s="8">
+        <v>12</v>
+      </c>
       <c r="G306" s="2"/>
     </row>
-    <row r="307" spans="1:7" ht="26.25">
+    <row r="307" spans="1:7" ht="27" thickBot="1">
       <c r="A307" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B307" s="2"/>
       <c r="C307" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D307" s="6" t="s">
-        <v>926</v>
-      </c>
-      <c r="E307" s="2"/>
-      <c r="F307" s="2"/>
+        <v>925</v>
+      </c>
+      <c r="E307" s="8">
+        <v>795</v>
+      </c>
+      <c r="F307" s="8">
+        <v>86</v>
+      </c>
       <c r="G307" s="2"/>
     </row>
-    <row r="308" spans="1:7" ht="39">
+    <row r="308" spans="1:7" ht="27" thickBot="1">
       <c r="A308" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B308" s="2"/>
       <c r="C308" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D308" s="6" t="s">
-        <v>929</v>
-      </c>
-      <c r="E308" s="2"/>
-      <c r="F308" s="2"/>
+        <v>928</v>
+      </c>
+      <c r="E308" s="8">
+        <v>922</v>
+      </c>
+      <c r="F308" s="8">
+        <v>100</v>
+      </c>
       <c r="G308" s="2"/>
     </row>
-    <row r="309" spans="1:7" ht="26.25">
+    <row r="309" spans="1:7" ht="27" thickBot="1">
       <c r="A309" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B309" s="2"/>
       <c r="C309" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D309" s="6" t="s">
-        <v>932</v>
-      </c>
-      <c r="E309" s="2"/>
-      <c r="F309" s="2"/>
+        <v>931</v>
+      </c>
+      <c r="E309" s="8">
+        <v>179</v>
+      </c>
+      <c r="F309" s="8">
+        <v>19</v>
+      </c>
       <c r="G309" s="2"/>
     </row>
-    <row r="310" spans="1:7" ht="26.25">
+    <row r="310" spans="1:7" ht="27" thickBot="1">
       <c r="A310" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B310" s="2"/>
       <c r="C310" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D310" s="6" t="s">
-        <v>935</v>
-      </c>
-      <c r="E310" s="2"/>
-      <c r="F310" s="2"/>
+        <v>934</v>
+      </c>
+      <c r="E310" s="8">
+        <v>275</v>
+      </c>
+      <c r="F310" s="8">
+        <v>29</v>
+      </c>
       <c r="G310" s="2"/>
     </row>
-    <row r="311" spans="1:7" ht="26.25">
+    <row r="311" spans="1:7" ht="27" thickBot="1">
       <c r="A311" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B311" s="2"/>
       <c r="C311" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D311" s="6" t="s">
-        <v>938</v>
-      </c>
-      <c r="E311" s="2"/>
-      <c r="F311" s="2"/>
+        <v>937</v>
+      </c>
+      <c r="E311" s="8">
+        <v>283</v>
+      </c>
+      <c r="F311" s="8">
+        <v>30</v>
+      </c>
       <c r="G311" s="2"/>
     </row>
-    <row r="312" spans="1:7" ht="26.25">
+    <row r="312" spans="1:7" ht="27" thickBot="1">
       <c r="A312" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B312" s="2"/>
       <c r="C312" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D312" s="6" t="s">
-        <v>941</v>
-      </c>
-      <c r="E312" s="2"/>
-      <c r="F312" s="2"/>
+        <v>940</v>
+      </c>
+      <c r="E312" s="8">
+        <v>320</v>
+      </c>
+      <c r="F312" s="8">
+        <v>34</v>
+      </c>
       <c r="G312" s="2"/>
     </row>
-    <row r="313" spans="1:7" ht="26.25">
+    <row r="313" spans="1:7" ht="27" thickBot="1">
       <c r="A313" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B313" s="2"/>
       <c r="C313" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D313" s="6" t="s">
-        <v>944</v>
-      </c>
-      <c r="E313" s="2"/>
-      <c r="F313" s="2"/>
+        <v>943</v>
+      </c>
+      <c r="E313" s="8">
+        <v>190</v>
+      </c>
+      <c r="F313" s="8">
+        <v>20</v>
+      </c>
       <c r="G313" s="2"/>
     </row>
-    <row r="314" spans="1:7" ht="39">
+    <row r="314" spans="1:7" ht="27" thickBot="1">
       <c r="A314" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B314" s="2"/>
       <c r="C314" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D314" s="6" t="s">
-        <v>947</v>
-      </c>
-      <c r="E314" s="2"/>
-      <c r="F314" s="2"/>
+        <v>946</v>
+      </c>
+      <c r="E314" s="8">
+        <v>1086</v>
+      </c>
+      <c r="F314" s="8">
+        <v>117</v>
+      </c>
       <c r="G314" s="2"/>
     </row>
-    <row r="315" spans="1:7" ht="26.25">
+    <row r="315" spans="1:7" ht="27" thickBot="1">
       <c r="A315" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B315" s="2"/>
       <c r="C315" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="D315" s="6" t="s">
-        <v>950</v>
-      </c>
-      <c r="E315" s="2"/>
-      <c r="F315" s="2"/>
+        <v>949</v>
+      </c>
+      <c r="E315" s="8">
+        <v>808</v>
+      </c>
+      <c r="F315" s="8">
+        <v>87</v>
+      </c>
       <c r="G315" s="2"/>
     </row>
-    <row r="316" spans="1:7" ht="26.25">
+    <row r="316" spans="1:7" ht="27" thickBot="1">
       <c r="A316" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B316" s="2"/>
       <c r="C316" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="D316" s="6" t="s">
-        <v>953</v>
-      </c>
-      <c r="E316" s="2"/>
-      <c r="F316" s="2"/>
+        <v>952</v>
+      </c>
+      <c r="E316" s="8">
+        <v>335</v>
+      </c>
+      <c r="F316" s="8">
+        <v>36</v>
+      </c>
       <c r="G316" s="2"/>
     </row>
-    <row r="317" spans="1:7" ht="26.25">
+    <row r="317" spans="1:7" ht="27" thickBot="1">
       <c r="A317" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B317" s="2"/>
       <c r="C317" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D317" s="6" t="s">
-        <v>956</v>
-      </c>
-      <c r="E317" s="2"/>
-      <c r="F317" s="2"/>
+        <v>955</v>
+      </c>
+      <c r="E317" s="8">
+        <v>741</v>
+      </c>
+      <c r="F317" s="8">
+        <v>80</v>
+      </c>
       <c r="G317" s="2"/>
     </row>
-    <row r="318" spans="1:7" ht="39">
+    <row r="318" spans="1:7" ht="27" thickBot="1">
       <c r="A318" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B318" s="2"/>
       <c r="C318" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="D318" s="6" t="s">
-        <v>959</v>
-      </c>
-      <c r="E318" s="2"/>
-      <c r="F318" s="2"/>
+        <v>958</v>
+      </c>
+      <c r="E318" s="8">
+        <v>1443</v>
+      </c>
+      <c r="F318" s="8">
+        <v>156</v>
+      </c>
       <c r="G318" s="2"/>
     </row>
-    <row r="319" spans="1:7" ht="39">
+    <row r="319" spans="1:7" ht="27" thickBot="1">
       <c r="A319" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B319" s="2"/>
       <c r="C319" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D319" s="6" t="s">
-        <v>962</v>
-      </c>
-      <c r="E319" s="2"/>
-      <c r="F319" s="2"/>
+        <v>961</v>
+      </c>
+      <c r="E319" s="8">
+        <v>2152</v>
+      </c>
+      <c r="F319" s="8">
+        <v>233</v>
+      </c>
       <c r="G319" s="2"/>
     </row>
-    <row r="320" spans="1:7" ht="26.25">
+    <row r="320" spans="1:7" ht="15.75" thickBot="1">
       <c r="A320" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B320" s="2"/>
       <c r="C320" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="D320" s="6" t="s">
-        <v>965</v>
-      </c>
-      <c r="E320" s="2"/>
-      <c r="F320" s="2"/>
+        <v>964</v>
+      </c>
+      <c r="E320" s="8">
+        <v>177</v>
+      </c>
+      <c r="F320" s="8">
+        <v>19</v>
+      </c>
       <c r="G320" s="2"/>
     </row>
-    <row r="321" spans="1:7" ht="39">
+    <row r="321" spans="1:7" ht="39.75" thickBot="1">
       <c r="A321" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B321" s="2"/>
       <c r="C321" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="D321" s="6" t="s">
-        <v>968</v>
-      </c>
-      <c r="E321" s="2"/>
-      <c r="F321" s="2"/>
+        <v>967</v>
+      </c>
+      <c r="E321" s="8">
+        <v>3456</v>
+      </c>
+      <c r="F321" s="8">
+        <v>374</v>
+      </c>
       <c r="G321" s="2"/>
     </row>
-    <row r="322" spans="1:7" ht="26.25">
+    <row r="322" spans="1:7" ht="27" thickBot="1">
       <c r="A322" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B322" s="2"/>
       <c r="C322" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="D322" s="6" t="s">
-        <v>971</v>
-      </c>
-      <c r="E322" s="2"/>
-      <c r="F322" s="2"/>
+        <v>970</v>
+      </c>
+      <c r="E322" s="8">
+        <v>727</v>
+      </c>
+      <c r="F322" s="8">
+        <v>78</v>
+      </c>
       <c r="G322" s="2"/>
     </row>
-    <row r="323" spans="1:7" ht="39">
+    <row r="323" spans="1:7" ht="27" thickBot="1">
       <c r="A323" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B323" s="2"/>
       <c r="C323" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D323" s="6" t="s">
-        <v>974</v>
-      </c>
-      <c r="E323" s="2"/>
-      <c r="F323" s="2"/>
+        <v>973</v>
+      </c>
+      <c r="E323" s="8">
+        <v>1802</v>
+      </c>
+      <c r="F323" s="8">
+        <v>195</v>
+      </c>
       <c r="G323" s="2"/>
     </row>
-    <row r="324" spans="1:7" ht="26.25">
+    <row r="324" spans="1:7" ht="27" thickBot="1">
       <c r="A324" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B324" s="2"/>
       <c r="C324" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D324" s="6" t="s">
-        <v>977</v>
-      </c>
-      <c r="E324" s="2"/>
-      <c r="F324" s="2"/>
+        <v>976</v>
+      </c>
+      <c r="E324" s="8">
+        <v>445</v>
+      </c>
+      <c r="F324" s="8">
+        <v>48</v>
+      </c>
       <c r="G324" s="2"/>
     </row>
-    <row r="325" spans="1:7" ht="26.25">
+    <row r="325" spans="1:7" ht="27" thickBot="1">
       <c r="A325" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B325" s="2"/>
       <c r="C325" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="D325" s="6" t="s">
+        <v>979</v>
+      </c>
+      <c r="E325" s="8">
+        <v>234</v>
+      </c>
+      <c r="F325" s="8">
+        <v>25</v>
+      </c>
+      <c r="G325" s="2"/>
+    </row>
+    <row r="326" spans="1:7" ht="52.5" thickBot="1">
+      <c r="A326" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C326" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="E325" s="2"/>
-      <c r="F325" s="2"/>
-      <c r="G325" s="2"/>
-    </row>
-    <row r="326" spans="1:7" ht="64.5">
-      <c r="A326" s="2" t="s">
+      <c r="D326" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="B326" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C326" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="D326" s="6" t="s">
-        <v>983</v>
-      </c>
-      <c r="E326" s="2"/>
-      <c r="F326" s="2"/>
+      <c r="E326" s="8">
+        <v>2549</v>
+      </c>
+      <c r="F326" s="8">
+        <v>276</v>
+      </c>
       <c r="G326" s="2"/>
     </row>
-    <row r="327" spans="1:7" ht="39">
+    <row r="327" spans="1:7" ht="27" thickBot="1">
       <c r="A327" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B327" s="2"/>
       <c r="C327" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D327" s="6" t="s">
-        <v>986</v>
-      </c>
-      <c r="E327" s="2"/>
-      <c r="F327" s="2"/>
+        <v>985</v>
+      </c>
+      <c r="E327" s="8">
+        <v>703</v>
+      </c>
+      <c r="F327" s="8">
+        <v>76</v>
+      </c>
       <c r="G327" s="2"/>
     </row>
-    <row r="328" spans="1:7">
+    <row r="328" spans="1:7" ht="15.75" thickBot="1">
       <c r="A328" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B328" s="2"/>
       <c r="C328" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="D328" s="6" t="s">
-        <v>989</v>
-      </c>
-      <c r="E328" s="2"/>
-      <c r="F328" s="2"/>
+        <v>988</v>
+      </c>
+      <c r="E328" s="8">
+        <v>87</v>
+      </c>
+      <c r="F328" s="8">
+        <v>9</v>
+      </c>
       <c r="G328" s="2"/>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" spans="1:7" ht="15.75" thickBot="1">
       <c r="A329" s="2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B329" s="2"/>
       <c r="C329" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D329" s="6" t="s">
-        <v>992</v>
-      </c>
-      <c r="E329" s="2"/>
-      <c r="F329" s="2"/>
+        <v>991</v>
+      </c>
+      <c r="E329" s="8">
+        <v>30</v>
+      </c>
+      <c r="F329" s="8">
+        <v>3</v>
+      </c>
       <c r="G329" s="2"/>
     </row>
-    <row r="330" spans="1:7">
+    <row r="330" spans="1:7" ht="15.75" thickBot="1">
       <c r="A330" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B330" s="2"/>
       <c r="C330" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D330" s="6" t="s">
-        <v>995</v>
-      </c>
-      <c r="E330" s="2"/>
-      <c r="F330" s="2"/>
+        <v>994</v>
+      </c>
+      <c r="E330" s="8">
+        <v>82</v>
+      </c>
+      <c r="F330" s="8">
+        <v>8</v>
+      </c>
       <c r="G330" s="2"/>
     </row>
-    <row r="331" spans="1:7" ht="26.25">
+    <row r="331" spans="1:7" ht="15.75" thickBot="1">
       <c r="A331" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B331" s="2"/>
       <c r="C331" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D331" s="6" t="s">
-        <v>998</v>
-      </c>
-      <c r="E331" s="2"/>
-      <c r="F331" s="2"/>
+        <v>997</v>
+      </c>
+      <c r="E331" s="8">
+        <v>47</v>
+      </c>
+      <c r="F331" s="8">
+        <v>5</v>
+      </c>
       <c r="G331" s="2"/>
     </row>
-    <row r="332" spans="1:7" ht="39">
+    <row r="332" spans="1:7" ht="39.75" thickBot="1">
       <c r="A332" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B332" s="2"/>
       <c r="C332" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D332" s="6" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E332" s="2"/>
-      <c r="F332" s="2"/>
+        <v>1000</v>
+      </c>
+      <c r="E332" s="8">
+        <v>1296</v>
+      </c>
+      <c r="F332" s="8">
+        <v>140</v>
+      </c>
       <c r="G332" s="2"/>
     </row>
-    <row r="333" spans="1:7" ht="26.25">
+    <row r="333" spans="1:7" ht="15.75" thickBot="1">
       <c r="A333" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B333" s="2"/>
       <c r="C333" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D333" s="6" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E333" s="2"/>
-      <c r="F333" s="2"/>
+        <v>1003</v>
+      </c>
+      <c r="E333" s="8">
+        <v>27</v>
+      </c>
+      <c r="F333" s="8">
+        <v>2</v>
+      </c>
       <c r="G333" s="2"/>
     </row>
-    <row r="334" spans="1:7" ht="26.25">
+    <row r="334" spans="1:7" ht="15.75" thickBot="1">
       <c r="A334" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B334" s="2"/>
       <c r="C334" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D334" s="6" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E334" s="2"/>
-      <c r="F334" s="2"/>
+        <v>1006</v>
+      </c>
+      <c r="E334" s="8">
+        <v>83</v>
+      </c>
+      <c r="F334" s="8">
+        <v>9</v>
+      </c>
       <c r="G334" s="2"/>
     </row>
-    <row r="335" spans="1:7" ht="26.25">
+    <row r="335" spans="1:7" ht="15.75" thickBot="1">
       <c r="A335" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B335" s="2"/>
       <c r="C335" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D335" s="6" t="s">
-        <v>1010</v>
-      </c>
-      <c r="E335" s="2"/>
-      <c r="F335" s="2"/>
+        <v>1009</v>
+      </c>
+      <c r="E335" s="8">
+        <v>42</v>
+      </c>
+      <c r="F335" s="8">
+        <v>4</v>
+      </c>
       <c r="G335" s="2"/>
     </row>
-    <row r="336" spans="1:7" ht="39">
+    <row r="336" spans="1:7" ht="27" thickBot="1">
       <c r="A336" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B336" s="2"/>
       <c r="C336" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="D336" s="6" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E336" s="2"/>
-      <c r="F336" s="2"/>
+        <v>1012</v>
+      </c>
+      <c r="E336" s="8">
+        <v>325</v>
+      </c>
+      <c r="F336" s="8">
+        <v>35</v>
+      </c>
       <c r="G336" s="2"/>
     </row>
   </sheetData>

--- a/map/city/regions.xlsx
+++ b/map/city/regions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Unida\Documents\VSC\Python\EpidemicSimulation\map\city\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530CBBA4-0774-45EB-A007-CF14F4E8BB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02B8E2A-A427-4119-9D40-ABF04F7A5403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24300" yWindow="588" windowWidth="21600" windowHeight="11232" xr2:uid="{B03016EF-FA4B-4206-80C1-0600DFDF6CE4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B03016EF-FA4B-4206-80C1-0600DFDF6CE4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3255,9 +3255,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3295,7 +3295,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3401,7 +3401,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3543,7 +3543,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3552,12 +3552,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257F345E-2D8B-488B-B1EA-82B9B5AE8CB7}">
   <dimension ref="A1:G336"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="77.25" thickBot="1">
+    <row r="1" spans="1:7" ht="79.8" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="39.75" thickBot="1">
+    <row r="2" spans="1:7" ht="42" thickBot="1">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -3594,14 +3594,14 @@
         <v>9</v>
       </c>
       <c r="E2" s="8">
-        <v>6813</v>
+        <v>7612</v>
       </c>
       <c r="F2" s="8">
         <v>738</v>
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" thickBot="1">
+    <row r="3" spans="1:7" ht="15" thickBot="1">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -3613,14 +3613,14 @@
         <v>12</v>
       </c>
       <c r="E3" s="8">
-        <v>2054</v>
+        <v>2296</v>
       </c>
       <c r="F3" s="8">
         <v>222</v>
       </c>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="39.75" thickBot="1">
+    <row r="4" spans="1:7" ht="42" thickBot="1">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -3634,14 +3634,14 @@
         <v>15</v>
       </c>
       <c r="E4" s="8">
-        <v>6964</v>
+        <v>7781</v>
       </c>
       <c r="F4" s="8">
         <v>754</v>
       </c>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="27" thickBot="1">
+    <row r="5" spans="1:7" ht="28.2" thickBot="1">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -3655,14 +3655,14 @@
         <v>18</v>
       </c>
       <c r="E5" s="8">
-        <v>800</v>
+        <v>894</v>
       </c>
       <c r="F5" s="8">
         <v>86</v>
       </c>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1">
+    <row r="6" spans="1:7" ht="15" thickBot="1">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -3674,14 +3674,14 @@
         <v>21</v>
       </c>
       <c r="E6" s="8">
-        <v>1026</v>
+        <v>1146</v>
       </c>
       <c r="F6" s="8">
         <v>111</v>
       </c>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" ht="39.75" thickBot="1">
+    <row r="7" spans="1:7" ht="42" thickBot="1">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
@@ -3695,14 +3695,14 @@
         <v>24</v>
       </c>
       <c r="E7" s="8">
-        <v>10453</v>
+        <v>11679</v>
       </c>
       <c r="F7" s="8">
         <v>1132</v>
       </c>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" ht="27" thickBot="1">
+    <row r="8" spans="1:7" ht="28.2" thickBot="1">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
@@ -3716,14 +3716,14 @@
         <v>27</v>
       </c>
       <c r="E8" s="8">
-        <v>4954</v>
+        <v>5535</v>
       </c>
       <c r="F8" s="8">
         <v>536</v>
       </c>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" ht="27" thickBot="1">
+    <row r="9" spans="1:7" ht="28.2" thickBot="1">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -3735,14 +3735,14 @@
         <v>30</v>
       </c>
       <c r="E9" s="8">
-        <v>2143</v>
+        <v>2395</v>
       </c>
       <c r="F9" s="8">
         <v>232</v>
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1">
+    <row r="10" spans="1:7" ht="15" thickBot="1">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -3754,14 +3754,14 @@
         <v>33</v>
       </c>
       <c r="E10" s="8">
-        <v>1818</v>
+        <v>2031</v>
       </c>
       <c r="F10" s="8">
         <v>197</v>
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="27" thickBot="1">
+    <row r="11" spans="1:7" ht="28.2" thickBot="1">
       <c r="A11" s="2" t="s">
         <v>35</v>
       </c>
@@ -3773,14 +3773,14 @@
         <v>36</v>
       </c>
       <c r="E11" s="8">
-        <v>844</v>
+        <v>943</v>
       </c>
       <c r="F11" s="8">
         <v>91</v>
       </c>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="27" thickBot="1">
+    <row r="12" spans="1:7" ht="28.2" thickBot="1">
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
@@ -3792,14 +3792,14 @@
         <v>39</v>
       </c>
       <c r="E12" s="8">
-        <v>1342</v>
+        <v>1500</v>
       </c>
       <c r="F12" s="8">
         <v>145</v>
       </c>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" ht="27" thickBot="1">
+    <row r="13" spans="1:7" ht="28.2" thickBot="1">
       <c r="A13" s="2" t="s">
         <v>41</v>
       </c>
@@ -3811,14 +3811,14 @@
         <v>42</v>
       </c>
       <c r="E13" s="8">
-        <v>2564</v>
+        <v>2865</v>
       </c>
       <c r="F13" s="8">
         <v>277</v>
       </c>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75" thickBot="1">
+    <row r="14" spans="1:7" ht="15" thickBot="1">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -3830,14 +3830,14 @@
         <v>45</v>
       </c>
       <c r="E14" s="8">
-        <v>1349</v>
+        <v>1508</v>
       </c>
       <c r="F14" s="8">
         <v>146</v>
       </c>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:7" ht="27" thickBot="1">
+    <row r="15" spans="1:7" ht="28.2" thickBot="1">
       <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
@@ -3849,14 +3849,14 @@
         <v>48</v>
       </c>
       <c r="E15" s="8">
-        <v>3564</v>
+        <v>3982</v>
       </c>
       <c r="F15" s="8">
         <v>386</v>
       </c>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:7" ht="27" thickBot="1">
+    <row r="16" spans="1:7" ht="28.2" thickBot="1">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -3868,14 +3868,14 @@
         <v>51</v>
       </c>
       <c r="E16" s="8">
-        <v>1373</v>
+        <v>1534</v>
       </c>
       <c r="F16" s="8">
         <v>148</v>
       </c>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" ht="27" thickBot="1">
+    <row r="17" spans="1:7" ht="28.2" thickBot="1">
       <c r="A17" s="2" t="s">
         <v>54</v>
       </c>
@@ -3889,14 +3889,14 @@
         <v>55</v>
       </c>
       <c r="E17" s="8">
-        <v>1493</v>
+        <v>1668</v>
       </c>
       <c r="F17" s="8">
         <v>161</v>
       </c>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" ht="27" thickBot="1">
+    <row r="18" spans="1:7" ht="28.2" thickBot="1">
       <c r="A18" s="2" t="s">
         <v>57</v>
       </c>
@@ -3908,14 +3908,14 @@
         <v>58</v>
       </c>
       <c r="E18" s="8">
-        <v>1080</v>
+        <v>1207</v>
       </c>
       <c r="F18" s="8">
         <v>117</v>
       </c>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" thickBot="1">
+    <row r="19" spans="1:7" ht="15" thickBot="1">
       <c r="A19" s="2" t="s">
         <v>60</v>
       </c>
@@ -3927,14 +3927,14 @@
         <v>61</v>
       </c>
       <c r="E19" s="8">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="F19" s="8">
         <v>23</v>
       </c>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="27" thickBot="1">
+    <row r="20" spans="1:7" ht="28.2" thickBot="1">
       <c r="A20" s="2" t="s">
         <v>63</v>
       </c>
@@ -3946,14 +3946,14 @@
         <v>64</v>
       </c>
       <c r="E20" s="8">
-        <v>2936</v>
+        <v>3280</v>
       </c>
       <c r="F20" s="8">
         <v>318</v>
       </c>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" ht="27" thickBot="1">
+    <row r="21" spans="1:7" ht="28.2" thickBot="1">
       <c r="A21" s="2" t="s">
         <v>66</v>
       </c>
@@ -3965,14 +3965,14 @@
         <v>67</v>
       </c>
       <c r="E21" s="8">
-        <v>3134</v>
+        <v>3501</v>
       </c>
       <c r="F21" s="8">
         <v>339</v>
       </c>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" ht="27" thickBot="1">
+    <row r="22" spans="1:7" ht="28.2" thickBot="1">
       <c r="A22" s="2" t="s">
         <v>69</v>
       </c>
@@ -3984,14 +3984,14 @@
         <v>70</v>
       </c>
       <c r="E22" s="8">
-        <v>2146</v>
+        <v>2397</v>
       </c>
       <c r="F22" s="8">
         <v>232</v>
       </c>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:7" ht="52.5" thickBot="1">
+    <row r="23" spans="1:7" ht="55.8" thickBot="1">
       <c r="A23" s="2" t="s">
         <v>72</v>
       </c>
@@ -4005,14 +4005,14 @@
         <v>73</v>
       </c>
       <c r="E23" s="8">
-        <v>5328</v>
+        <v>5953</v>
       </c>
       <c r="F23" s="8">
         <v>577</v>
       </c>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:7" ht="27" thickBot="1">
+    <row r="24" spans="1:7" ht="28.2" thickBot="1">
       <c r="A24" s="2" t="s">
         <v>75</v>
       </c>
@@ -4024,14 +4024,14 @@
         <v>76</v>
       </c>
       <c r="E24" s="8">
-        <v>1426</v>
+        <v>1593</v>
       </c>
       <c r="F24" s="8">
         <v>154</v>
       </c>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" ht="27" thickBot="1">
+    <row r="25" spans="1:7" ht="28.2" thickBot="1">
       <c r="A25" s="2" t="s">
         <v>78</v>
       </c>
@@ -4043,14 +4043,14 @@
         <v>79</v>
       </c>
       <c r="E25" s="8">
-        <v>4266</v>
+        <v>4767</v>
       </c>
       <c r="F25" s="8">
         <v>462</v>
       </c>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" spans="1:7" ht="15.75" thickBot="1">
+    <row r="26" spans="1:7" ht="15" thickBot="1">
       <c r="A26" s="2" t="s">
         <v>81</v>
       </c>
@@ -4062,14 +4062,14 @@
         <v>82</v>
       </c>
       <c r="E26" s="8">
-        <v>493</v>
+        <v>551</v>
       </c>
       <c r="F26" s="8">
         <v>53</v>
       </c>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" spans="1:7" ht="39.75" thickBot="1">
+    <row r="27" spans="1:7" ht="42" thickBot="1">
       <c r="A27" s="2" t="s">
         <v>84</v>
       </c>
@@ -4081,14 +4081,14 @@
         <v>85</v>
       </c>
       <c r="E27" s="8">
-        <v>3910</v>
+        <v>4369</v>
       </c>
       <c r="F27" s="8">
         <v>423</v>
       </c>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" ht="27" thickBot="1">
+    <row r="28" spans="1:7" ht="28.2" thickBot="1">
       <c r="A28" s="2" t="s">
         <v>87</v>
       </c>
@@ -4100,14 +4100,14 @@
         <v>88</v>
       </c>
       <c r="E28" s="8">
-        <v>927</v>
+        <v>1036</v>
       </c>
       <c r="F28" s="8">
         <v>100</v>
       </c>
       <c r="G28" s="2"/>
     </row>
-    <row r="29" spans="1:7" ht="15.75" thickBot="1">
+    <row r="29" spans="1:7" ht="15" thickBot="1">
       <c r="A29" s="2" t="s">
         <v>90</v>
       </c>
@@ -4119,14 +4119,14 @@
         <v>91</v>
       </c>
       <c r="E29" s="8">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="F29" s="8">
         <v>18</v>
       </c>
       <c r="G29" s="2"/>
     </row>
-    <row r="30" spans="1:7" ht="15.75" thickBot="1">
+    <row r="30" spans="1:7" ht="15" thickBot="1">
       <c r="A30" s="2" t="s">
         <v>93</v>
       </c>
@@ -4138,14 +4138,14 @@
         <v>94</v>
       </c>
       <c r="E30" s="8">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="F30" s="8">
         <v>28</v>
       </c>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" ht="15.75" thickBot="1">
+    <row r="31" spans="1:7" ht="15" thickBot="1">
       <c r="A31" s="2" t="s">
         <v>96</v>
       </c>
@@ -4157,14 +4157,14 @@
         <v>97</v>
       </c>
       <c r="E31" s="8">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F31" s="8">
         <v>5</v>
       </c>
       <c r="G31" s="2"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" thickBot="1">
+    <row r="32" spans="1:7" ht="15" thickBot="1">
       <c r="A32" s="2" t="s">
         <v>99</v>
       </c>
@@ -4176,14 +4176,14 @@
         <v>100</v>
       </c>
       <c r="E32" s="8">
-        <v>250</v>
+        <v>279</v>
       </c>
       <c r="F32" s="8">
         <v>27</v>
       </c>
       <c r="G32" s="2"/>
     </row>
-    <row r="33" spans="1:7" ht="15.75" thickBot="1">
+    <row r="33" spans="1:7" ht="15" thickBot="1">
       <c r="A33" s="2" t="s">
         <v>102</v>
       </c>
@@ -4195,14 +4195,14 @@
         <v>103</v>
       </c>
       <c r="E33" s="8">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="F33" s="8">
         <v>25</v>
       </c>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" spans="1:7" ht="15.75" thickBot="1">
+    <row r="34" spans="1:7" ht="15" thickBot="1">
       <c r="A34" s="2" t="s">
         <v>105</v>
       </c>
@@ -4214,14 +4214,14 @@
         <v>106</v>
       </c>
       <c r="E34" s="8">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="F34" s="8">
         <v>22</v>
       </c>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="1:7" ht="27" thickBot="1">
+    <row r="35" spans="1:7" ht="28.2" thickBot="1">
       <c r="A35" s="2" t="s">
         <v>108</v>
       </c>
@@ -4233,14 +4233,14 @@
         <v>109</v>
       </c>
       <c r="E35" s="8">
-        <v>475</v>
+        <v>531</v>
       </c>
       <c r="F35" s="8">
         <v>51</v>
       </c>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="1:7" ht="15.75" thickBot="1">
+    <row r="36" spans="1:7" ht="15" thickBot="1">
       <c r="A36" s="2" t="s">
         <v>111</v>
       </c>
@@ -4252,14 +4252,14 @@
         <v>112</v>
       </c>
       <c r="E36" s="8">
-        <v>742</v>
+        <v>829</v>
       </c>
       <c r="F36" s="8">
         <v>80</v>
       </c>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="1:7" ht="15.75" thickBot="1">
+    <row r="37" spans="1:7" ht="15" thickBot="1">
       <c r="A37" s="2" t="s">
         <v>114</v>
       </c>
@@ -4271,14 +4271,14 @@
         <v>115</v>
       </c>
       <c r="E37" s="8">
-        <v>729</v>
+        <v>815</v>
       </c>
       <c r="F37" s="8">
         <v>79</v>
       </c>
       <c r="G37" s="2"/>
     </row>
-    <row r="38" spans="1:7" ht="15.75" thickBot="1">
+    <row r="38" spans="1:7" ht="15" thickBot="1">
       <c r="A38" s="2" t="s">
         <v>117</v>
       </c>
@@ -4290,14 +4290,14 @@
         <v>118</v>
       </c>
       <c r="E38" s="8">
-        <v>474</v>
+        <v>530</v>
       </c>
       <c r="F38" s="8">
         <v>51</v>
       </c>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" spans="1:7" ht="15.75" thickBot="1">
+    <row r="39" spans="1:7" ht="15" thickBot="1">
       <c r="A39" s="2" t="s">
         <v>120</v>
       </c>
@@ -4309,14 +4309,14 @@
         <v>121</v>
       </c>
       <c r="E39" s="8">
-        <v>444</v>
+        <v>496</v>
       </c>
       <c r="F39" s="8">
         <v>48</v>
       </c>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="1:7" ht="15.75" thickBot="1">
+    <row r="40" spans="1:7" ht="15" thickBot="1">
       <c r="A40" s="2" t="s">
         <v>123</v>
       </c>
@@ -4328,14 +4328,14 @@
         <v>124</v>
       </c>
       <c r="E40" s="8">
-        <v>423</v>
+        <v>472</v>
       </c>
       <c r="F40" s="8">
         <v>45</v>
       </c>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="1:7" ht="15.75" thickBot="1">
+    <row r="41" spans="1:7" ht="15" thickBot="1">
       <c r="A41" s="2" t="s">
         <v>126</v>
       </c>
@@ -4347,14 +4347,14 @@
         <v>127</v>
       </c>
       <c r="E41" s="8">
-        <v>1803</v>
+        <v>2015</v>
       </c>
       <c r="F41" s="8">
         <v>195</v>
       </c>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="1:7" ht="15.75" thickBot="1">
+    <row r="42" spans="1:7" ht="15" thickBot="1">
       <c r="A42" s="2" t="s">
         <v>129</v>
       </c>
@@ -4366,14 +4366,14 @@
         <v>130</v>
       </c>
       <c r="E42" s="8">
-        <v>956</v>
+        <v>1068</v>
       </c>
       <c r="F42" s="8">
         <v>103</v>
       </c>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="1:7" ht="27" thickBot="1">
+    <row r="43" spans="1:7" ht="28.2" thickBot="1">
       <c r="A43" s="2" t="s">
         <v>132</v>
       </c>
@@ -4385,14 +4385,14 @@
         <v>133</v>
       </c>
       <c r="E43" s="8">
-        <v>1213</v>
+        <v>1356</v>
       </c>
       <c r="F43" s="8">
         <v>131</v>
       </c>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="1:7" ht="15.75" thickBot="1">
+    <row r="44" spans="1:7" ht="15" thickBot="1">
       <c r="A44" s="2" t="s">
         <v>135</v>
       </c>
@@ -4404,14 +4404,14 @@
         <v>136</v>
       </c>
       <c r="E44" s="8">
-        <v>1529</v>
+        <v>1709</v>
       </c>
       <c r="F44" s="8">
         <v>165</v>
       </c>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="1:7" ht="15.75" thickBot="1">
+    <row r="45" spans="1:7" ht="15" thickBot="1">
       <c r="A45" s="2" t="s">
         <v>138</v>
       </c>
@@ -4423,14 +4423,14 @@
         <v>139</v>
       </c>
       <c r="E45" s="8">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="F45" s="8">
         <v>33</v>
       </c>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="1:7" ht="15.75" thickBot="1">
+    <row r="46" spans="1:7" ht="15" thickBot="1">
       <c r="A46" s="2" t="s">
         <v>141</v>
       </c>
@@ -4442,14 +4442,14 @@
         <v>142</v>
       </c>
       <c r="E46" s="8">
-        <v>321</v>
+        <v>358</v>
       </c>
       <c r="F46" s="8">
         <v>34</v>
       </c>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="1:7" ht="15.75" thickBot="1">
+    <row r="47" spans="1:7" ht="15" thickBot="1">
       <c r="A47" s="2" t="s">
         <v>144</v>
       </c>
@@ -4461,14 +4461,14 @@
         <v>145</v>
       </c>
       <c r="E47" s="8">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="F47" s="8">
         <v>24</v>
       </c>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="1:7" ht="39.75" thickBot="1">
+    <row r="48" spans="1:7" ht="42" thickBot="1">
       <c r="A48" s="2" t="s">
         <v>147</v>
       </c>
@@ -4480,14 +4480,14 @@
         <v>148</v>
       </c>
       <c r="E48" s="8">
-        <v>2593</v>
+        <v>2897</v>
       </c>
       <c r="F48" s="8">
         <v>281</v>
       </c>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="1:7" ht="27" thickBot="1">
+    <row r="49" spans="1:7" ht="28.2" thickBot="1">
       <c r="A49" s="2" t="s">
         <v>150</v>
       </c>
@@ -4499,14 +4499,14 @@
         <v>151</v>
       </c>
       <c r="E49" s="8">
-        <v>1263</v>
+        <v>1411</v>
       </c>
       <c r="F49" s="8">
         <v>136</v>
       </c>
       <c r="G49" s="2"/>
     </row>
-    <row r="50" spans="1:7" ht="15.75" thickBot="1">
+    <row r="50" spans="1:7" ht="15" thickBot="1">
       <c r="A50" s="2" t="s">
         <v>153</v>
       </c>
@@ -4518,14 +4518,14 @@
         <v>154</v>
       </c>
       <c r="E50" s="8">
-        <v>984</v>
+        <v>1100</v>
       </c>
       <c r="F50" s="8">
         <v>106</v>
       </c>
       <c r="G50" s="2"/>
     </row>
-    <row r="51" spans="1:7" ht="15.75" thickBot="1">
+    <row r="51" spans="1:7" ht="15" thickBot="1">
       <c r="A51" s="2" t="s">
         <v>156</v>
       </c>
@@ -4537,14 +4537,14 @@
         <v>157</v>
       </c>
       <c r="E51" s="8">
-        <v>550</v>
+        <v>614</v>
       </c>
       <c r="F51" s="8">
         <v>59</v>
       </c>
       <c r="G51" s="2"/>
     </row>
-    <row r="52" spans="1:7" ht="15.75" thickBot="1">
+    <row r="52" spans="1:7" ht="15" thickBot="1">
       <c r="A52" s="2" t="s">
         <v>159</v>
       </c>
@@ -4556,14 +4556,14 @@
         <v>160</v>
       </c>
       <c r="E52" s="8">
-        <v>414</v>
+        <v>462</v>
       </c>
       <c r="F52" s="8">
         <v>44</v>
       </c>
       <c r="G52" s="2"/>
     </row>
-    <row r="53" spans="1:7" ht="27" thickBot="1">
+    <row r="53" spans="1:7" ht="28.2" thickBot="1">
       <c r="A53" s="2" t="s">
         <v>162</v>
       </c>
@@ -4575,14 +4575,14 @@
         <v>163</v>
       </c>
       <c r="E53" s="8">
-        <v>681</v>
+        <v>761</v>
       </c>
       <c r="F53" s="8">
         <v>73</v>
       </c>
       <c r="G53" s="2"/>
     </row>
-    <row r="54" spans="1:7" ht="27" thickBot="1">
+    <row r="54" spans="1:7" ht="28.2" thickBot="1">
       <c r="A54" s="2" t="s">
         <v>165</v>
       </c>
@@ -4594,14 +4594,14 @@
         <v>166</v>
       </c>
       <c r="E54" s="8">
-        <v>282</v>
+        <v>315</v>
       </c>
       <c r="F54" s="8">
         <v>30</v>
       </c>
       <c r="G54" s="2"/>
     </row>
-    <row r="55" spans="1:7" ht="15.75" thickBot="1">
+    <row r="55" spans="1:7" ht="15" thickBot="1">
       <c r="A55" s="2" t="s">
         <v>168</v>
       </c>
@@ -4613,14 +4613,14 @@
         <v>169</v>
       </c>
       <c r="E55" s="8">
-        <v>296</v>
+        <v>330</v>
       </c>
       <c r="F55" s="8">
         <v>32</v>
       </c>
       <c r="G55" s="2"/>
     </row>
-    <row r="56" spans="1:7" ht="15.75" thickBot="1">
+    <row r="56" spans="1:7" ht="15" thickBot="1">
       <c r="A56" s="2" t="s">
         <v>171</v>
       </c>
@@ -4632,14 +4632,14 @@
         <v>172</v>
       </c>
       <c r="E56" s="8">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="F56" s="8">
         <v>14</v>
       </c>
       <c r="G56" s="2"/>
     </row>
-    <row r="57" spans="1:7" ht="15.75" thickBot="1">
+    <row r="57" spans="1:7" ht="15" thickBot="1">
       <c r="A57" s="2" t="s">
         <v>174</v>
       </c>
@@ -4651,14 +4651,14 @@
         <v>175</v>
       </c>
       <c r="E57" s="8">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="F57" s="8">
         <v>34</v>
       </c>
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:7" ht="27" thickBot="1">
+    <row r="58" spans="1:7" ht="28.2" thickBot="1">
       <c r="A58" s="2" t="s">
         <v>177</v>
       </c>
@@ -4670,14 +4670,14 @@
         <v>178</v>
       </c>
       <c r="E58" s="8">
-        <v>599</v>
+        <v>669</v>
       </c>
       <c r="F58" s="8">
         <v>64</v>
       </c>
       <c r="G58" s="2"/>
     </row>
-    <row r="59" spans="1:7" ht="27" thickBot="1">
+    <row r="59" spans="1:7" ht="28.2" thickBot="1">
       <c r="A59" s="2" t="s">
         <v>180</v>
       </c>
@@ -4689,14 +4689,14 @@
         <v>181</v>
       </c>
       <c r="E59" s="8">
-        <v>433</v>
+        <v>484</v>
       </c>
       <c r="F59" s="8">
         <v>47</v>
       </c>
       <c r="G59" s="2"/>
     </row>
-    <row r="60" spans="1:7" ht="27" thickBot="1">
+    <row r="60" spans="1:7" ht="28.2" thickBot="1">
       <c r="A60" s="2" t="s">
         <v>183</v>
       </c>
@@ -4708,14 +4708,14 @@
         <v>184</v>
       </c>
       <c r="E60" s="8">
-        <v>318</v>
+        <v>355</v>
       </c>
       <c r="F60" s="8">
         <v>34</v>
       </c>
       <c r="G60" s="2"/>
     </row>
-    <row r="61" spans="1:7" ht="27" thickBot="1">
+    <row r="61" spans="1:7" ht="28.2" thickBot="1">
       <c r="A61" s="2" t="s">
         <v>186</v>
       </c>
@@ -4727,14 +4727,14 @@
         <v>187</v>
       </c>
       <c r="E61" s="8">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="F61" s="8">
         <v>14</v>
       </c>
       <c r="G61" s="2"/>
     </row>
-    <row r="62" spans="1:7" ht="27" thickBot="1">
+    <row r="62" spans="1:7" ht="28.2" thickBot="1">
       <c r="A62" s="2" t="s">
         <v>189</v>
       </c>
@@ -4746,14 +4746,14 @@
         <v>190</v>
       </c>
       <c r="E62" s="8">
-        <v>439</v>
+        <v>490</v>
       </c>
       <c r="F62" s="8">
         <v>47</v>
       </c>
       <c r="G62" s="2"/>
     </row>
-    <row r="63" spans="1:7" ht="15.75" thickBot="1">
+    <row r="63" spans="1:7" ht="15" thickBot="1">
       <c r="A63" s="2" t="s">
         <v>192</v>
       </c>
@@ -4765,14 +4765,14 @@
         <v>193</v>
       </c>
       <c r="E63" s="8">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="F63" s="8">
         <v>14</v>
       </c>
       <c r="G63" s="2"/>
     </row>
-    <row r="64" spans="1:7" ht="15.75" thickBot="1">
+    <row r="64" spans="1:7" ht="15" thickBot="1">
       <c r="A64" s="2" t="s">
         <v>195</v>
       </c>
@@ -4784,14 +4784,14 @@
         <v>196</v>
       </c>
       <c r="E64" s="8">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="F64" s="8">
         <v>15</v>
       </c>
       <c r="G64" s="2"/>
     </row>
-    <row r="65" spans="1:7" ht="27" thickBot="1">
+    <row r="65" spans="1:7" ht="28.2" thickBot="1">
       <c r="A65" s="2" t="s">
         <v>198</v>
       </c>
@@ -4803,14 +4803,14 @@
         <v>199</v>
       </c>
       <c r="E65" s="8">
-        <v>998</v>
+        <v>1115</v>
       </c>
       <c r="F65" s="8">
         <v>108</v>
       </c>
       <c r="G65" s="2"/>
     </row>
-    <row r="66" spans="1:7" ht="27" thickBot="1">
+    <row r="66" spans="1:7" ht="28.2" thickBot="1">
       <c r="A66" s="2" t="s">
         <v>201</v>
       </c>
@@ -4822,14 +4822,14 @@
         <v>202</v>
       </c>
       <c r="E66" s="8">
-        <v>471</v>
+        <v>526</v>
       </c>
       <c r="F66" s="8">
         <v>51</v>
       </c>
       <c r="G66" s="2"/>
     </row>
-    <row r="67" spans="1:7" ht="27" thickBot="1">
+    <row r="67" spans="1:7" ht="28.2" thickBot="1">
       <c r="A67" s="2" t="s">
         <v>204</v>
       </c>
@@ -4841,14 +4841,14 @@
         <v>205</v>
       </c>
       <c r="E67" s="8">
-        <v>450</v>
+        <v>503</v>
       </c>
       <c r="F67" s="8">
         <v>48</v>
       </c>
       <c r="G67" s="2"/>
     </row>
-    <row r="68" spans="1:7" ht="27" thickBot="1">
+    <row r="68" spans="1:7" ht="28.2" thickBot="1">
       <c r="A68" s="2" t="s">
         <v>207</v>
       </c>
@@ -4860,14 +4860,14 @@
         <v>208</v>
       </c>
       <c r="E68" s="8">
-        <v>2473</v>
+        <v>2763</v>
       </c>
       <c r="F68" s="8">
         <v>268</v>
       </c>
       <c r="G68" s="2"/>
     </row>
-    <row r="69" spans="1:7" ht="27" thickBot="1">
+    <row r="69" spans="1:7" ht="28.2" thickBot="1">
       <c r="A69" s="2" t="s">
         <v>210</v>
       </c>
@@ -4879,14 +4879,14 @@
         <v>211</v>
       </c>
       <c r="E69" s="8">
-        <v>709</v>
+        <v>792</v>
       </c>
       <c r="F69" s="8">
         <v>76</v>
       </c>
       <c r="G69" s="2"/>
     </row>
-    <row r="70" spans="1:7" ht="27" thickBot="1">
+    <row r="70" spans="1:7" ht="28.2" thickBot="1">
       <c r="A70" s="2" t="s">
         <v>213</v>
       </c>
@@ -4898,14 +4898,14 @@
         <v>214</v>
       </c>
       <c r="E70" s="8">
-        <v>1674</v>
+        <v>1871</v>
       </c>
       <c r="F70" s="8">
         <v>181</v>
       </c>
       <c r="G70" s="2"/>
     </row>
-    <row r="71" spans="1:7" ht="27" thickBot="1">
+    <row r="71" spans="1:7" ht="28.2" thickBot="1">
       <c r="A71" s="2" t="s">
         <v>216</v>
       </c>
@@ -4917,14 +4917,14 @@
         <v>217</v>
       </c>
       <c r="E71" s="8">
-        <v>3384</v>
+        <v>3782</v>
       </c>
       <c r="F71" s="8">
         <v>366</v>
       </c>
       <c r="G71" s="2"/>
     </row>
-    <row r="72" spans="1:7" ht="15.75" thickBot="1">
+    <row r="72" spans="1:7" ht="15" thickBot="1">
       <c r="A72" s="2" t="s">
         <v>219</v>
       </c>
@@ -4936,14 +4936,14 @@
         <v>220</v>
       </c>
       <c r="E72" s="8">
-        <v>720</v>
+        <v>805</v>
       </c>
       <c r="F72" s="8">
         <v>78</v>
       </c>
       <c r="G72" s="2"/>
     </row>
-    <row r="73" spans="1:7" ht="27" thickBot="1">
+    <row r="73" spans="1:7" ht="28.2" thickBot="1">
       <c r="A73" s="2" t="s">
         <v>222</v>
       </c>
@@ -4955,14 +4955,14 @@
         <v>223</v>
       </c>
       <c r="E73" s="8">
-        <v>4244</v>
+        <v>4742</v>
       </c>
       <c r="F73" s="8">
         <v>460</v>
       </c>
       <c r="G73" s="2"/>
     </row>
-    <row r="74" spans="1:7" ht="27" thickBot="1">
+    <row r="74" spans="1:7" ht="28.2" thickBot="1">
       <c r="A74" s="2" t="s">
         <v>225</v>
       </c>
@@ -4974,14 +4974,14 @@
         <v>226</v>
       </c>
       <c r="E74" s="8">
-        <v>2116</v>
+        <v>2364</v>
       </c>
       <c r="F74" s="8">
         <v>229</v>
       </c>
       <c r="G74" s="2"/>
     </row>
-    <row r="75" spans="1:7" ht="27" thickBot="1">
+    <row r="75" spans="1:7" ht="28.2" thickBot="1">
       <c r="A75" s="2" t="s">
         <v>228</v>
       </c>
@@ -4993,14 +4993,14 @@
         <v>229</v>
       </c>
       <c r="E75" s="8">
-        <v>958</v>
+        <v>1071</v>
       </c>
       <c r="F75" s="8">
         <v>103</v>
       </c>
       <c r="G75" s="2"/>
     </row>
-    <row r="76" spans="1:7" ht="27" thickBot="1">
+    <row r="76" spans="1:7" ht="28.2" thickBot="1">
       <c r="A76" s="2" t="s">
         <v>231</v>
       </c>
@@ -5012,14 +5012,14 @@
         <v>232</v>
       </c>
       <c r="E76" s="8">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="F76" s="8">
         <v>15</v>
       </c>
       <c r="G76" s="2"/>
     </row>
-    <row r="77" spans="1:7" ht="27" thickBot="1">
+    <row r="77" spans="1:7" ht="28.2" thickBot="1">
       <c r="A77" s="2" t="s">
         <v>234</v>
       </c>
@@ -5031,14 +5031,14 @@
         <v>235</v>
       </c>
       <c r="E77" s="8">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="F77" s="8">
         <v>15</v>
       </c>
       <c r="G77" s="2"/>
     </row>
-    <row r="78" spans="1:7" ht="15.75" thickBot="1">
+    <row r="78" spans="1:7" ht="15" thickBot="1">
       <c r="A78" s="2" t="s">
         <v>237</v>
       </c>
@@ -5050,14 +5050,14 @@
         <v>238</v>
       </c>
       <c r="E78" s="8">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F78" s="8">
         <v>5</v>
       </c>
       <c r="G78" s="2"/>
     </row>
-    <row r="79" spans="1:7" ht="27" thickBot="1">
+    <row r="79" spans="1:7" ht="28.2" thickBot="1">
       <c r="A79" s="2" t="s">
         <v>240</v>
       </c>
@@ -5069,14 +5069,14 @@
         <v>241</v>
       </c>
       <c r="E79" s="8">
-        <v>1029</v>
+        <v>1149</v>
       </c>
       <c r="F79" s="8">
         <v>111</v>
       </c>
       <c r="G79" s="2"/>
     </row>
-    <row r="80" spans="1:7" ht="27" thickBot="1">
+    <row r="80" spans="1:7" ht="28.2" thickBot="1">
       <c r="A80" s="2" t="s">
         <v>243</v>
       </c>
@@ -5088,14 +5088,14 @@
         <v>244</v>
       </c>
       <c r="E80" s="8">
-        <v>354</v>
+        <v>395</v>
       </c>
       <c r="F80" s="8">
         <v>38</v>
       </c>
       <c r="G80" s="2"/>
     </row>
-    <row r="81" spans="1:7" ht="27" thickBot="1">
+    <row r="81" spans="1:7" ht="28.2" thickBot="1">
       <c r="A81" s="2" t="s">
         <v>246</v>
       </c>
@@ -5107,14 +5107,14 @@
         <v>247</v>
       </c>
       <c r="E81" s="8">
-        <v>1475</v>
+        <v>1648</v>
       </c>
       <c r="F81" s="8">
         <v>159</v>
       </c>
       <c r="G81" s="2"/>
     </row>
-    <row r="82" spans="1:7" ht="27" thickBot="1">
+    <row r="82" spans="1:7" ht="28.2" thickBot="1">
       <c r="A82" s="2" t="s">
         <v>249</v>
       </c>
@@ -5126,14 +5126,14 @@
         <v>250</v>
       </c>
       <c r="E82" s="8">
-        <v>1496</v>
+        <v>1671</v>
       </c>
       <c r="F82" s="8">
         <v>162</v>
       </c>
       <c r="G82" s="2"/>
     </row>
-    <row r="83" spans="1:7" ht="39.75" thickBot="1">
+    <row r="83" spans="1:7" ht="42" thickBot="1">
       <c r="A83" s="2" t="s">
         <v>252</v>
       </c>
@@ -5145,14 +5145,14 @@
         <v>253</v>
       </c>
       <c r="E83" s="8">
-        <v>2297</v>
+        <v>2566</v>
       </c>
       <c r="F83" s="8">
         <v>248</v>
       </c>
       <c r="G83" s="2"/>
     </row>
-    <row r="84" spans="1:7" ht="27" thickBot="1">
+    <row r="84" spans="1:7" ht="28.2" thickBot="1">
       <c r="A84" s="2" t="s">
         <v>255</v>
       </c>
@@ -5164,14 +5164,14 @@
         <v>256</v>
       </c>
       <c r="E84" s="8">
-        <v>1010</v>
+        <v>1128</v>
       </c>
       <c r="F84" s="8">
         <v>109</v>
       </c>
       <c r="G84" s="2"/>
     </row>
-    <row r="85" spans="1:7" ht="27" thickBot="1">
+    <row r="85" spans="1:7" ht="28.2" thickBot="1">
       <c r="A85" s="2" t="s">
         <v>258</v>
       </c>
@@ -5183,14 +5183,14 @@
         <v>259</v>
       </c>
       <c r="E85" s="8">
-        <v>900</v>
+        <v>1006</v>
       </c>
       <c r="F85" s="8">
         <v>97</v>
       </c>
       <c r="G85" s="2"/>
     </row>
-    <row r="86" spans="1:7" ht="27" thickBot="1">
+    <row r="86" spans="1:7" ht="28.2" thickBot="1">
       <c r="A86" s="2" t="s">
         <v>261</v>
       </c>
@@ -5202,14 +5202,14 @@
         <v>262</v>
       </c>
       <c r="E86" s="8">
-        <v>522</v>
+        <v>583</v>
       </c>
       <c r="F86" s="8">
         <v>56</v>
       </c>
       <c r="G86" s="2"/>
     </row>
-    <row r="87" spans="1:7" ht="27" thickBot="1">
+    <row r="87" spans="1:7" ht="28.2" thickBot="1">
       <c r="A87" s="2" t="s">
         <v>264</v>
       </c>
@@ -5221,14 +5221,14 @@
         <v>265</v>
       </c>
       <c r="E87" s="8">
-        <v>770</v>
+        <v>860</v>
       </c>
       <c r="F87" s="8">
         <v>83</v>
       </c>
       <c r="G87" s="2"/>
     </row>
-    <row r="88" spans="1:7" ht="27" thickBot="1">
+    <row r="88" spans="1:7" ht="28.2" thickBot="1">
       <c r="A88" s="2" t="s">
         <v>267</v>
       </c>
@@ -5240,14 +5240,14 @@
         <v>268</v>
       </c>
       <c r="E88" s="8">
-        <v>678</v>
+        <v>757</v>
       </c>
       <c r="F88" s="8">
         <v>73</v>
       </c>
       <c r="G88" s="2"/>
     </row>
-    <row r="89" spans="1:7" ht="27" thickBot="1">
+    <row r="89" spans="1:7" ht="28.2" thickBot="1">
       <c r="A89" s="2" t="s">
         <v>270</v>
       </c>
@@ -5259,14 +5259,14 @@
         <v>271</v>
       </c>
       <c r="E89" s="8">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="F89" s="8">
         <v>25</v>
       </c>
       <c r="G89" s="2"/>
     </row>
-    <row r="90" spans="1:7" ht="27" thickBot="1">
+    <row r="90" spans="1:7" ht="28.2" thickBot="1">
       <c r="A90" s="2" t="s">
         <v>273</v>
       </c>
@@ -5278,14 +5278,14 @@
         <v>274</v>
       </c>
       <c r="E90" s="8">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="F90" s="8">
         <v>27</v>
       </c>
       <c r="G90" s="2"/>
     </row>
-    <row r="91" spans="1:7" ht="27" thickBot="1">
+    <row r="91" spans="1:7" ht="28.2" thickBot="1">
       <c r="A91" s="2" t="s">
         <v>276</v>
       </c>
@@ -5297,14 +5297,14 @@
         <v>277</v>
       </c>
       <c r="E91" s="8">
-        <v>531</v>
+        <v>594</v>
       </c>
       <c r="F91" s="8">
         <v>57</v>
       </c>
       <c r="G91" s="2"/>
     </row>
-    <row r="92" spans="1:7" ht="27" thickBot="1">
+    <row r="92" spans="1:7" ht="28.2" thickBot="1">
       <c r="A92" s="2" t="s">
         <v>279</v>
       </c>
@@ -5316,14 +5316,14 @@
         <v>280</v>
       </c>
       <c r="E92" s="8">
-        <v>437</v>
+        <v>489</v>
       </c>
       <c r="F92" s="8">
         <v>47</v>
       </c>
       <c r="G92" s="2"/>
     </row>
-    <row r="93" spans="1:7" ht="27" thickBot="1">
+    <row r="93" spans="1:7" ht="28.2" thickBot="1">
       <c r="A93" s="2" t="s">
         <v>282</v>
       </c>
@@ -5335,14 +5335,14 @@
         <v>283</v>
       </c>
       <c r="E93" s="8">
-        <v>724</v>
+        <v>809</v>
       </c>
       <c r="F93" s="8">
         <v>78</v>
       </c>
       <c r="G93" s="2"/>
     </row>
-    <row r="94" spans="1:7" ht="27" thickBot="1">
+    <row r="94" spans="1:7" ht="28.2" thickBot="1">
       <c r="A94" s="2" t="s">
         <v>285</v>
       </c>
@@ -5354,14 +5354,14 @@
         <v>286</v>
       </c>
       <c r="E94" s="8">
-        <v>449</v>
+        <v>501</v>
       </c>
       <c r="F94" s="8">
         <v>48</v>
       </c>
       <c r="G94" s="2"/>
     </row>
-    <row r="95" spans="1:7" ht="27" thickBot="1">
+    <row r="95" spans="1:7" ht="28.2" thickBot="1">
       <c r="A95" s="2" t="s">
         <v>288</v>
       </c>
@@ -5373,14 +5373,14 @@
         <v>289</v>
       </c>
       <c r="E95" s="8">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="F95" s="8">
         <v>14</v>
       </c>
       <c r="G95" s="2"/>
     </row>
-    <row r="96" spans="1:7" ht="27" thickBot="1">
+    <row r="96" spans="1:7" ht="28.2" thickBot="1">
       <c r="A96" s="2" t="s">
         <v>291</v>
       </c>
@@ -5392,14 +5392,14 @@
         <v>292</v>
       </c>
       <c r="E96" s="8">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="F96" s="8">
         <v>35</v>
       </c>
       <c r="G96" s="2"/>
     </row>
-    <row r="97" spans="1:7" ht="27" thickBot="1">
+    <row r="97" spans="1:7" ht="28.2" thickBot="1">
       <c r="A97" s="2" t="s">
         <v>294</v>
       </c>
@@ -5411,14 +5411,14 @@
         <v>295</v>
       </c>
       <c r="E97" s="8">
-        <v>409</v>
+        <v>458</v>
       </c>
       <c r="F97" s="8">
         <v>44</v>
       </c>
       <c r="G97" s="2"/>
     </row>
-    <row r="98" spans="1:7" ht="27" thickBot="1">
+    <row r="98" spans="1:7" ht="28.2" thickBot="1">
       <c r="A98" s="2" t="s">
         <v>297</v>
       </c>
@@ -5430,14 +5430,14 @@
         <v>298</v>
       </c>
       <c r="E98" s="8">
-        <v>595</v>
+        <v>665</v>
       </c>
       <c r="F98" s="8">
         <v>64</v>
       </c>
       <c r="G98" s="2"/>
     </row>
-    <row r="99" spans="1:7" ht="27" thickBot="1">
+    <row r="99" spans="1:7" ht="28.2" thickBot="1">
       <c r="A99" s="2" t="s">
         <v>300</v>
       </c>
@@ -5449,14 +5449,14 @@
         <v>301</v>
       </c>
       <c r="E99" s="8">
-        <v>482</v>
+        <v>538</v>
       </c>
       <c r="F99" s="8">
         <v>52</v>
       </c>
       <c r="G99" s="2"/>
     </row>
-    <row r="100" spans="1:7" ht="27" thickBot="1">
+    <row r="100" spans="1:7" ht="28.2" thickBot="1">
       <c r="A100" s="2" t="s">
         <v>303</v>
       </c>
@@ -5468,14 +5468,14 @@
         <v>304</v>
       </c>
       <c r="E100" s="8">
-        <v>404</v>
+        <v>452</v>
       </c>
       <c r="F100" s="8">
         <v>43</v>
       </c>
       <c r="G100" s="2"/>
     </row>
-    <row r="101" spans="1:7" ht="27" thickBot="1">
+    <row r="101" spans="1:7" ht="28.2" thickBot="1">
       <c r="A101" s="2" t="s">
         <v>306</v>
       </c>
@@ -5487,14 +5487,14 @@
         <v>307</v>
       </c>
       <c r="E101" s="8">
-        <v>334</v>
+        <v>373</v>
       </c>
       <c r="F101" s="8">
         <v>36</v>
       </c>
       <c r="G101" s="2"/>
     </row>
-    <row r="102" spans="1:7" ht="27" thickBot="1">
+    <row r="102" spans="1:7" ht="28.2" thickBot="1">
       <c r="A102" s="2" t="s">
         <v>309</v>
       </c>
@@ -5506,14 +5506,14 @@
         <v>310</v>
       </c>
       <c r="E102" s="8">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="F102" s="8">
         <v>14</v>
       </c>
       <c r="G102" s="2"/>
     </row>
-    <row r="103" spans="1:7" ht="27" thickBot="1">
+    <row r="103" spans="1:7" ht="28.2" thickBot="1">
       <c r="A103" s="2" t="s">
         <v>312</v>
       </c>
@@ -5525,14 +5525,14 @@
         <v>313</v>
       </c>
       <c r="E103" s="8">
-        <v>423</v>
+        <v>472</v>
       </c>
       <c r="F103" s="8">
         <v>45</v>
       </c>
       <c r="G103" s="2"/>
     </row>
-    <row r="104" spans="1:7" ht="27" thickBot="1">
+    <row r="104" spans="1:7" ht="28.2" thickBot="1">
       <c r="A104" s="2" t="s">
         <v>315</v>
       </c>
@@ -5544,14 +5544,14 @@
         <v>316</v>
       </c>
       <c r="E104" s="8">
-        <v>2664</v>
+        <v>2977</v>
       </c>
       <c r="F104" s="8">
         <v>288</v>
       </c>
       <c r="G104" s="2"/>
     </row>
-    <row r="105" spans="1:7" ht="27" thickBot="1">
+    <row r="105" spans="1:7" ht="28.2" thickBot="1">
       <c r="A105" s="2" t="s">
         <v>318</v>
       </c>
@@ -5563,14 +5563,14 @@
         <v>319</v>
       </c>
       <c r="E105" s="8">
-        <v>783</v>
+        <v>875</v>
       </c>
       <c r="F105" s="8">
         <v>84</v>
       </c>
       <c r="G105" s="2"/>
     </row>
-    <row r="106" spans="1:7" ht="27" thickBot="1">
+    <row r="106" spans="1:7" ht="28.2" thickBot="1">
       <c r="A106" s="2" t="s">
         <v>321</v>
       </c>
@@ -5582,14 +5582,14 @@
         <v>322</v>
       </c>
       <c r="E106" s="8">
-        <v>413</v>
+        <v>462</v>
       </c>
       <c r="F106" s="8">
         <v>44</v>
       </c>
       <c r="G106" s="2"/>
     </row>
-    <row r="107" spans="1:7" ht="27" thickBot="1">
+    <row r="107" spans="1:7" ht="28.2" thickBot="1">
       <c r="A107" s="2" t="s">
         <v>324</v>
       </c>
@@ -5601,14 +5601,14 @@
         <v>325</v>
       </c>
       <c r="E107" s="8">
-        <v>334</v>
+        <v>373</v>
       </c>
       <c r="F107" s="8">
         <v>36</v>
       </c>
       <c r="G107" s="2"/>
     </row>
-    <row r="108" spans="1:7" ht="27" thickBot="1">
+    <row r="108" spans="1:7" ht="28.2" thickBot="1">
       <c r="A108" s="2" t="s">
         <v>327</v>
       </c>
@@ -5620,14 +5620,14 @@
         <v>328</v>
       </c>
       <c r="E108" s="8">
-        <v>432</v>
+        <v>483</v>
       </c>
       <c r="F108" s="8">
         <v>46</v>
       </c>
       <c r="G108" s="2"/>
     </row>
-    <row r="109" spans="1:7" ht="27" thickBot="1">
+    <row r="109" spans="1:7" ht="28.2" thickBot="1">
       <c r="A109" s="2" t="s">
         <v>330</v>
       </c>
@@ -5639,14 +5639,14 @@
         <v>331</v>
       </c>
       <c r="E109" s="8">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="F109" s="8">
         <v>28</v>
       </c>
       <c r="G109" s="2"/>
     </row>
-    <row r="110" spans="1:7" ht="27" thickBot="1">
+    <row r="110" spans="1:7" ht="28.2" thickBot="1">
       <c r="A110" s="2" t="s">
         <v>333</v>
       </c>
@@ -5658,14 +5658,14 @@
         <v>334</v>
       </c>
       <c r="E110" s="8">
-        <v>1450</v>
+        <v>1620</v>
       </c>
       <c r="F110" s="8">
         <v>157</v>
       </c>
       <c r="G110" s="2"/>
     </row>
-    <row r="111" spans="1:7" ht="27" thickBot="1">
+    <row r="111" spans="1:7" ht="28.2" thickBot="1">
       <c r="A111" s="2" t="s">
         <v>336</v>
       </c>
@@ -5677,14 +5677,14 @@
         <v>337</v>
       </c>
       <c r="E111" s="8">
-        <v>2694</v>
+        <v>3010</v>
       </c>
       <c r="F111" s="8">
         <v>292</v>
       </c>
       <c r="G111" s="2"/>
     </row>
-    <row r="112" spans="1:7" ht="15.75" thickBot="1">
+    <row r="112" spans="1:7" ht="15" thickBot="1">
       <c r="A112" s="2" t="s">
         <v>339</v>
       </c>
@@ -5696,14 +5696,14 @@
         <v>340</v>
       </c>
       <c r="E112" s="8">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="F112" s="8">
         <v>20</v>
       </c>
       <c r="G112" s="2"/>
     </row>
-    <row r="113" spans="1:7" ht="27" thickBot="1">
+    <row r="113" spans="1:7" ht="28.2" thickBot="1">
       <c r="A113" s="2" t="s">
         <v>342</v>
       </c>
@@ -5715,14 +5715,14 @@
         <v>343</v>
       </c>
       <c r="E113" s="8">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="F113" s="8">
         <v>32</v>
       </c>
       <c r="G113" s="2"/>
     </row>
-    <row r="114" spans="1:7" ht="27" thickBot="1">
+    <row r="114" spans="1:7" ht="28.2" thickBot="1">
       <c r="A114" s="2" t="s">
         <v>345</v>
       </c>
@@ -5734,14 +5734,14 @@
         <v>346</v>
       </c>
       <c r="E114" s="8">
-        <v>598</v>
+        <v>668</v>
       </c>
       <c r="F114" s="8">
         <v>64</v>
       </c>
       <c r="G114" s="2"/>
     </row>
-    <row r="115" spans="1:7" ht="27" thickBot="1">
+    <row r="115" spans="1:7" ht="28.2" thickBot="1">
       <c r="A115" s="2" t="s">
         <v>348</v>
       </c>
@@ -5753,14 +5753,14 @@
         <v>349</v>
       </c>
       <c r="E115" s="8">
-        <v>336</v>
+        <v>376</v>
       </c>
       <c r="F115" s="8">
         <v>36</v>
       </c>
       <c r="G115" s="2"/>
     </row>
-    <row r="116" spans="1:7" ht="39.75" thickBot="1">
+    <row r="116" spans="1:7" ht="42" thickBot="1">
       <c r="A116" s="2" t="s">
         <v>351</v>
       </c>
@@ -5772,14 +5772,14 @@
         <v>352</v>
       </c>
       <c r="E116" s="8">
-        <v>1495</v>
+        <v>1670</v>
       </c>
       <c r="F116" s="8">
         <v>162</v>
       </c>
       <c r="G116" s="2"/>
     </row>
-    <row r="117" spans="1:7" ht="27" thickBot="1">
+    <row r="117" spans="1:7" ht="28.2" thickBot="1">
       <c r="A117" s="2" t="s">
         <v>354</v>
       </c>
@@ -5791,14 +5791,14 @@
         <v>355</v>
       </c>
       <c r="E117" s="8">
-        <v>606</v>
+        <v>677</v>
       </c>
       <c r="F117" s="8">
         <v>65</v>
       </c>
       <c r="G117" s="2"/>
     </row>
-    <row r="118" spans="1:7" ht="27" thickBot="1">
+    <row r="118" spans="1:7" ht="28.2" thickBot="1">
       <c r="A118" s="2" t="s">
         <v>357</v>
       </c>
@@ -5810,14 +5810,14 @@
         <v>358</v>
       </c>
       <c r="E118" s="8">
-        <v>785</v>
+        <v>877</v>
       </c>
       <c r="F118" s="8">
         <v>85</v>
       </c>
       <c r="G118" s="2"/>
     </row>
-    <row r="119" spans="1:7" ht="27" thickBot="1">
+    <row r="119" spans="1:7" ht="28.2" thickBot="1">
       <c r="A119" s="2" t="s">
         <v>360</v>
       </c>
@@ -5829,14 +5829,14 @@
         <v>361</v>
       </c>
       <c r="E119" s="8">
-        <v>793</v>
+        <v>887</v>
       </c>
       <c r="F119" s="8">
         <v>86</v>
       </c>
       <c r="G119" s="2"/>
     </row>
-    <row r="120" spans="1:7" ht="15.75" thickBot="1">
+    <row r="120" spans="1:7" ht="15" thickBot="1">
       <c r="A120" s="2" t="s">
         <v>363</v>
       </c>
@@ -5848,14 +5848,14 @@
         <v>364</v>
       </c>
       <c r="E120" s="8">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F120" s="8">
         <v>2</v>
       </c>
       <c r="G120" s="2"/>
     </row>
-    <row r="121" spans="1:7" ht="15.75" thickBot="1">
+    <row r="121" spans="1:7" ht="15" thickBot="1">
       <c r="A121" s="2" t="s">
         <v>366</v>
       </c>
@@ -5867,14 +5867,14 @@
         <v>367</v>
       </c>
       <c r="E121" s="8">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F121" s="8">
         <v>6</v>
       </c>
       <c r="G121" s="2"/>
     </row>
-    <row r="122" spans="1:7" ht="15.75" thickBot="1">
+    <row r="122" spans="1:7" ht="15" thickBot="1">
       <c r="A122" s="2" t="s">
         <v>369</v>
       </c>
@@ -5886,14 +5886,14 @@
         <v>370</v>
       </c>
       <c r="E122" s="8">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F122" s="8">
         <v>2</v>
       </c>
       <c r="G122" s="2"/>
     </row>
-    <row r="123" spans="1:7" ht="27" thickBot="1">
+    <row r="123" spans="1:7" ht="28.2" thickBot="1">
       <c r="A123" s="2" t="s">
         <v>372</v>
       </c>
@@ -5905,14 +5905,14 @@
         <v>373</v>
       </c>
       <c r="E123" s="8">
-        <v>463</v>
+        <v>517</v>
       </c>
       <c r="F123" s="8">
         <v>50</v>
       </c>
       <c r="G123" s="2"/>
     </row>
-    <row r="124" spans="1:7" ht="27" thickBot="1">
+    <row r="124" spans="1:7" ht="28.2" thickBot="1">
       <c r="A124" s="2" t="s">
         <v>375</v>
       </c>
@@ -5924,14 +5924,14 @@
         <v>376</v>
       </c>
       <c r="E124" s="8">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="F124" s="8">
         <v>15</v>
       </c>
       <c r="G124" s="2"/>
     </row>
-    <row r="125" spans="1:7" ht="27" thickBot="1">
+    <row r="125" spans="1:7" ht="28.2" thickBot="1">
       <c r="A125" s="2" t="s">
         <v>378</v>
       </c>
@@ -5943,14 +5943,14 @@
         <v>379</v>
       </c>
       <c r="E125" s="8">
-        <v>359</v>
+        <v>401</v>
       </c>
       <c r="F125" s="8">
         <v>38</v>
       </c>
       <c r="G125" s="2"/>
     </row>
-    <row r="126" spans="1:7" ht="27" thickBot="1">
+    <row r="126" spans="1:7" ht="28.2" thickBot="1">
       <c r="A126" s="2" t="s">
         <v>381</v>
       </c>
@@ -5962,14 +5962,14 @@
         <v>382</v>
       </c>
       <c r="E126" s="8">
-        <v>454</v>
+        <v>507</v>
       </c>
       <c r="F126" s="8">
         <v>49</v>
       </c>
       <c r="G126" s="2"/>
     </row>
-    <row r="127" spans="1:7" ht="27" thickBot="1">
+    <row r="127" spans="1:7" ht="28.2" thickBot="1">
       <c r="A127" s="2" t="s">
         <v>384</v>
       </c>
@@ -5981,14 +5981,14 @@
         <v>385</v>
       </c>
       <c r="E127" s="8">
-        <v>366</v>
+        <v>409</v>
       </c>
       <c r="F127" s="8">
         <v>39</v>
       </c>
       <c r="G127" s="2"/>
     </row>
-    <row r="128" spans="1:7" ht="27" thickBot="1">
+    <row r="128" spans="1:7" ht="28.2" thickBot="1">
       <c r="A128" s="2" t="s">
         <v>387</v>
       </c>
@@ -6000,14 +6000,14 @@
         <v>388</v>
       </c>
       <c r="E128" s="8">
-        <v>470</v>
+        <v>525</v>
       </c>
       <c r="F128" s="8">
         <v>51</v>
       </c>
       <c r="G128" s="2"/>
     </row>
-    <row r="129" spans="1:7" ht="27" thickBot="1">
+    <row r="129" spans="1:7" ht="28.2" thickBot="1">
       <c r="A129" s="2" t="s">
         <v>390</v>
       </c>
@@ -6019,14 +6019,14 @@
         <v>391</v>
       </c>
       <c r="E129" s="8">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="F129" s="8">
         <v>46</v>
       </c>
       <c r="G129" s="2"/>
     </row>
-    <row r="130" spans="1:7" ht="27" thickBot="1">
+    <row r="130" spans="1:7" ht="28.2" thickBot="1">
       <c r="A130" s="2" t="s">
         <v>393</v>
       </c>
@@ -6038,14 +6038,14 @@
         <v>394</v>
       </c>
       <c r="E130" s="8">
-        <v>350</v>
+        <v>392</v>
       </c>
       <c r="F130" s="8">
         <v>38</v>
       </c>
       <c r="G130" s="2"/>
     </row>
-    <row r="131" spans="1:7" ht="27" thickBot="1">
+    <row r="131" spans="1:7" ht="28.2" thickBot="1">
       <c r="A131" s="2" t="s">
         <v>396</v>
       </c>
@@ -6057,14 +6057,14 @@
         <v>397</v>
       </c>
       <c r="E131" s="8">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="F131" s="8">
         <v>15</v>
       </c>
       <c r="G131" s="2"/>
     </row>
-    <row r="132" spans="1:7" ht="27" thickBot="1">
+    <row r="132" spans="1:7" ht="28.2" thickBot="1">
       <c r="A132" s="2" t="s">
         <v>399</v>
       </c>
@@ -6076,14 +6076,14 @@
         <v>400</v>
       </c>
       <c r="E132" s="8">
-        <v>429</v>
+        <v>480</v>
       </c>
       <c r="F132" s="8">
         <v>46</v>
       </c>
       <c r="G132" s="2"/>
     </row>
-    <row r="133" spans="1:7" ht="27" thickBot="1">
+    <row r="133" spans="1:7" ht="28.2" thickBot="1">
       <c r="A133" s="2" t="s">
         <v>402</v>
       </c>
@@ -6095,14 +6095,14 @@
         <v>403</v>
       </c>
       <c r="E133" s="8">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="F133" s="8">
         <v>31</v>
       </c>
       <c r="G133" s="2"/>
     </row>
-    <row r="134" spans="1:7" ht="27" thickBot="1">
+    <row r="134" spans="1:7" ht="28.2" thickBot="1">
       <c r="A134" s="2" t="s">
         <v>405</v>
       </c>
@@ -6114,14 +6114,14 @@
         <v>406</v>
       </c>
       <c r="E134" s="8">
-        <v>412</v>
+        <v>461</v>
       </c>
       <c r="F134" s="8">
         <v>44</v>
       </c>
       <c r="G134" s="2"/>
     </row>
-    <row r="135" spans="1:7" ht="27" thickBot="1">
+    <row r="135" spans="1:7" ht="28.2" thickBot="1">
       <c r="A135" s="2" t="s">
         <v>408</v>
       </c>
@@ -6133,14 +6133,14 @@
         <v>409</v>
       </c>
       <c r="E135" s="8">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="F135" s="8">
         <v>15</v>
       </c>
       <c r="G135" s="2"/>
     </row>
-    <row r="136" spans="1:7" ht="27" thickBot="1">
+    <row r="136" spans="1:7" ht="28.2" thickBot="1">
       <c r="A136" s="2" t="s">
         <v>411</v>
       </c>
@@ -6152,14 +6152,14 @@
         <v>412</v>
       </c>
       <c r="E136" s="8">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="F136" s="8">
         <v>35</v>
       </c>
       <c r="G136" s="2"/>
     </row>
-    <row r="137" spans="1:7" ht="27" thickBot="1">
+    <row r="137" spans="1:7" ht="28.2" thickBot="1">
       <c r="A137" s="2" t="s">
         <v>414</v>
       </c>
@@ -6171,14 +6171,14 @@
         <v>415</v>
       </c>
       <c r="E137" s="8">
-        <v>388</v>
+        <v>433</v>
       </c>
       <c r="F137" s="8">
         <v>42</v>
       </c>
       <c r="G137" s="2"/>
     </row>
-    <row r="138" spans="1:7" ht="27" thickBot="1">
+    <row r="138" spans="1:7" ht="28.2" thickBot="1">
       <c r="A138" s="2" t="s">
         <v>417</v>
       </c>
@@ -6190,14 +6190,14 @@
         <v>418</v>
       </c>
       <c r="E138" s="8">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="F138" s="8">
         <v>32</v>
       </c>
       <c r="G138" s="2"/>
     </row>
-    <row r="139" spans="1:7" ht="15.75" thickBot="1">
+    <row r="139" spans="1:7" ht="15" thickBot="1">
       <c r="A139" s="2" t="s">
         <v>420</v>
       </c>
@@ -6209,14 +6209,14 @@
         <v>421</v>
       </c>
       <c r="E139" s="8">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="F139" s="8">
         <v>13</v>
       </c>
       <c r="G139" s="2"/>
     </row>
-    <row r="140" spans="1:7" ht="27" thickBot="1">
+    <row r="140" spans="1:7" ht="28.2" thickBot="1">
       <c r="A140" s="2" t="s">
         <v>423</v>
       </c>
@@ -6228,14 +6228,14 @@
         <v>424</v>
       </c>
       <c r="E140" s="8">
-        <v>928</v>
+        <v>1037</v>
       </c>
       <c r="F140" s="8">
         <v>100</v>
       </c>
       <c r="G140" s="2"/>
     </row>
-    <row r="141" spans="1:7" ht="27" thickBot="1">
+    <row r="141" spans="1:7" ht="28.2" thickBot="1">
       <c r="A141" s="2" t="s">
         <v>426</v>
       </c>
@@ -6247,14 +6247,14 @@
         <v>427</v>
       </c>
       <c r="E141" s="8">
-        <v>668</v>
+        <v>747</v>
       </c>
       <c r="F141" s="8">
         <v>72</v>
       </c>
       <c r="G141" s="2"/>
     </row>
-    <row r="142" spans="1:7" ht="27" thickBot="1">
+    <row r="142" spans="1:7" ht="28.2" thickBot="1">
       <c r="A142" s="2" t="s">
         <v>429</v>
       </c>
@@ -6266,14 +6266,14 @@
         <v>430</v>
       </c>
       <c r="E142" s="8">
-        <v>1919</v>
+        <v>2144</v>
       </c>
       <c r="F142" s="8">
         <v>208</v>
       </c>
       <c r="G142" s="2"/>
     </row>
-    <row r="143" spans="1:7" ht="27" thickBot="1">
+    <row r="143" spans="1:7" ht="28.2" thickBot="1">
       <c r="A143" s="2" t="s">
         <v>432</v>
       </c>
@@ -6285,14 +6285,14 @@
         <v>433</v>
       </c>
       <c r="E143" s="8">
-        <v>1279</v>
+        <v>1429</v>
       </c>
       <c r="F143" s="8">
         <v>138</v>
       </c>
       <c r="G143" s="2"/>
     </row>
-    <row r="144" spans="1:7" ht="27" thickBot="1">
+    <row r="144" spans="1:7" ht="28.2" thickBot="1">
       <c r="A144" s="2" t="s">
         <v>435</v>
       </c>
@@ -6304,14 +6304,14 @@
         <v>436</v>
       </c>
       <c r="E144" s="8">
-        <v>519</v>
+        <v>580</v>
       </c>
       <c r="F144" s="8">
         <v>56</v>
       </c>
       <c r="G144" s="2"/>
     </row>
-    <row r="145" spans="1:7" ht="27" thickBot="1">
+    <row r="145" spans="1:7" ht="28.2" thickBot="1">
       <c r="A145" s="2" t="s">
         <v>438</v>
       </c>
@@ -6323,14 +6323,14 @@
         <v>439</v>
       </c>
       <c r="E145" s="8">
-        <v>1527</v>
+        <v>1706</v>
       </c>
       <c r="F145" s="8">
         <v>165</v>
       </c>
       <c r="G145" s="2"/>
     </row>
-    <row r="146" spans="1:7" ht="27" thickBot="1">
+    <row r="146" spans="1:7" ht="28.2" thickBot="1">
       <c r="A146" s="2" t="s">
         <v>441</v>
       </c>
@@ -6342,14 +6342,14 @@
         <v>442</v>
       </c>
       <c r="E146" s="8">
-        <v>832</v>
+        <v>930</v>
       </c>
       <c r="F146" s="8">
         <v>90</v>
       </c>
       <c r="G146" s="2"/>
     </row>
-    <row r="147" spans="1:7" ht="39.75" thickBot="1">
+    <row r="147" spans="1:7" ht="42" thickBot="1">
       <c r="A147" s="2" t="s">
         <v>444</v>
       </c>
@@ -6361,14 +6361,14 @@
         <v>445</v>
       </c>
       <c r="E147" s="8">
-        <v>860</v>
+        <v>960</v>
       </c>
       <c r="F147" s="8">
         <v>93</v>
       </c>
       <c r="G147" s="2"/>
     </row>
-    <row r="148" spans="1:7" ht="39.75" thickBot="1">
+    <row r="148" spans="1:7" ht="42" thickBot="1">
       <c r="A148" s="2" t="s">
         <v>447</v>
       </c>
@@ -6380,14 +6380,14 @@
         <v>448</v>
       </c>
       <c r="E148" s="8">
-        <v>2631</v>
+        <v>2940</v>
       </c>
       <c r="F148" s="8">
         <v>285</v>
       </c>
       <c r="G148" s="2"/>
     </row>
-    <row r="149" spans="1:7" ht="27" thickBot="1">
+    <row r="149" spans="1:7" ht="28.2" thickBot="1">
       <c r="A149" s="2" t="s">
         <v>450</v>
       </c>
@@ -6399,14 +6399,14 @@
         <v>451</v>
       </c>
       <c r="E149" s="8">
-        <v>916</v>
+        <v>1024</v>
       </c>
       <c r="F149" s="8">
         <v>99</v>
       </c>
       <c r="G149" s="2"/>
     </row>
-    <row r="150" spans="1:7" ht="27" thickBot="1">
+    <row r="150" spans="1:7" ht="28.2" thickBot="1">
       <c r="A150" s="2" t="s">
         <v>453</v>
       </c>
@@ -6418,14 +6418,14 @@
         <v>454</v>
       </c>
       <c r="E150" s="8">
-        <v>691</v>
+        <v>772</v>
       </c>
       <c r="F150" s="8">
         <v>74</v>
       </c>
       <c r="G150" s="2"/>
     </row>
-    <row r="151" spans="1:7" ht="52.5" thickBot="1">
+    <row r="151" spans="1:7" ht="55.8" thickBot="1">
       <c r="A151" s="2" t="s">
         <v>456</v>
       </c>
@@ -6437,14 +6437,14 @@
         <v>457</v>
       </c>
       <c r="E151" s="8">
-        <v>2295</v>
+        <v>2565</v>
       </c>
       <c r="F151" s="8">
         <v>248</v>
       </c>
       <c r="G151" s="2"/>
     </row>
-    <row r="152" spans="1:7" ht="65.25" thickBot="1">
+    <row r="152" spans="1:7" ht="69.599999999999994" thickBot="1">
       <c r="A152" s="2" t="s">
         <v>459</v>
       </c>
@@ -6456,14 +6456,14 @@
         <v>460</v>
       </c>
       <c r="E152" s="8">
-        <v>5565</v>
+        <v>6218</v>
       </c>
       <c r="F152" s="8">
         <v>603</v>
       </c>
       <c r="G152" s="2"/>
     </row>
-    <row r="153" spans="1:7" ht="65.25" thickBot="1">
+    <row r="153" spans="1:7" ht="69.599999999999994" thickBot="1">
       <c r="A153" s="2" t="s">
         <v>462</v>
       </c>
@@ -6475,14 +6475,14 @@
         <v>463</v>
       </c>
       <c r="E153" s="8">
-        <v>6318</v>
+        <v>7059</v>
       </c>
       <c r="F153" s="8">
         <v>684</v>
       </c>
       <c r="G153" s="2"/>
     </row>
-    <row r="154" spans="1:7" ht="27" thickBot="1">
+    <row r="154" spans="1:7" ht="28.2" thickBot="1">
       <c r="A154" s="2" t="s">
         <v>465</v>
       </c>
@@ -6494,14 +6494,14 @@
         <v>466</v>
       </c>
       <c r="E154" s="8">
-        <v>755</v>
+        <v>844</v>
       </c>
       <c r="F154" s="8">
         <v>81</v>
       </c>
       <c r="G154" s="2"/>
     </row>
-    <row r="155" spans="1:7" ht="27" thickBot="1">
+    <row r="155" spans="1:7" ht="28.2" thickBot="1">
       <c r="A155" s="2" t="s">
         <v>468</v>
       </c>
@@ -6513,14 +6513,14 @@
         <v>469</v>
       </c>
       <c r="E155" s="8">
-        <v>746</v>
+        <v>833</v>
       </c>
       <c r="F155" s="8">
         <v>80</v>
       </c>
       <c r="G155" s="2"/>
     </row>
-    <row r="156" spans="1:7" ht="65.25" thickBot="1">
+    <row r="156" spans="1:7" ht="69.599999999999994" thickBot="1">
       <c r="A156" s="2" t="s">
         <v>471</v>
       </c>
@@ -6534,14 +6534,14 @@
         <v>472</v>
       </c>
       <c r="E156" s="8">
-        <v>16269</v>
+        <v>18178</v>
       </c>
       <c r="F156" s="8">
         <v>1763</v>
       </c>
       <c r="G156" s="2"/>
     </row>
-    <row r="157" spans="1:7" ht="15.75" thickBot="1">
+    <row r="157" spans="1:7" ht="15" thickBot="1">
       <c r="A157" s="2" t="s">
         <v>474</v>
       </c>
@@ -6553,14 +6553,14 @@
         <v>475</v>
       </c>
       <c r="E157" s="8">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="F157" s="8">
         <v>17</v>
       </c>
       <c r="G157" s="2"/>
     </row>
-    <row r="158" spans="1:7" ht="15.75" thickBot="1">
+    <row r="158" spans="1:7" ht="15" thickBot="1">
       <c r="A158" s="2" t="s">
         <v>477</v>
       </c>
@@ -6572,14 +6572,14 @@
         <v>478</v>
       </c>
       <c r="E158" s="8">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="F158" s="8">
         <v>13</v>
       </c>
       <c r="G158" s="2"/>
     </row>
-    <row r="159" spans="1:7" ht="27" thickBot="1">
+    <row r="159" spans="1:7" ht="28.2" thickBot="1">
       <c r="A159" s="2" t="s">
         <v>480</v>
       </c>
@@ -6591,14 +6591,14 @@
         <v>481</v>
       </c>
       <c r="E159" s="8">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="F159" s="8">
         <v>33</v>
       </c>
       <c r="G159" s="2"/>
     </row>
-    <row r="160" spans="1:7" ht="27" thickBot="1">
+    <row r="160" spans="1:7" ht="28.2" thickBot="1">
       <c r="A160" s="2" t="s">
         <v>483</v>
       </c>
@@ -6610,14 +6610,14 @@
         <v>484</v>
       </c>
       <c r="E160" s="8">
-        <v>695</v>
+        <v>777</v>
       </c>
       <c r="F160" s="8">
         <v>75</v>
       </c>
       <c r="G160" s="2"/>
     </row>
-    <row r="161" spans="1:7" ht="27" thickBot="1">
+    <row r="161" spans="1:7" ht="28.2" thickBot="1">
       <c r="A161" s="2" t="s">
         <v>486</v>
       </c>
@@ -6629,14 +6629,14 @@
         <v>487</v>
       </c>
       <c r="E161" s="8">
-        <v>1150</v>
+        <v>1285</v>
       </c>
       <c r="F161" s="8">
         <v>124</v>
       </c>
       <c r="G161" s="2"/>
     </row>
-    <row r="162" spans="1:7" ht="27" thickBot="1">
+    <row r="162" spans="1:7" ht="28.2" thickBot="1">
       <c r="A162" s="2" t="s">
         <v>489</v>
       </c>
@@ -6648,14 +6648,14 @@
         <v>490</v>
       </c>
       <c r="E162" s="8">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F162" s="8">
         <v>7</v>
       </c>
       <c r="G162" s="2"/>
     </row>
-    <row r="163" spans="1:7" ht="27" thickBot="1">
+    <row r="163" spans="1:7" ht="28.2" thickBot="1">
       <c r="A163" s="2" t="s">
         <v>492</v>
       </c>
@@ -6667,14 +6667,14 @@
         <v>493</v>
       </c>
       <c r="E163" s="8">
-        <v>282</v>
+        <v>315</v>
       </c>
       <c r="F163" s="8">
         <v>30</v>
       </c>
       <c r="G163" s="2"/>
     </row>
-    <row r="164" spans="1:7" ht="27" thickBot="1">
+    <row r="164" spans="1:7" ht="28.2" thickBot="1">
       <c r="A164" s="4" t="s">
         <v>495</v>
       </c>
@@ -6686,14 +6686,14 @@
         <v>496</v>
       </c>
       <c r="E164" s="8">
-        <v>331</v>
+        <v>370</v>
       </c>
       <c r="F164" s="8">
         <v>35</v>
       </c>
       <c r="G164" s="2"/>
     </row>
-    <row r="165" spans="1:7" ht="27" thickBot="1">
+    <row r="165" spans="1:7" ht="28.2" thickBot="1">
       <c r="A165" s="5" t="s">
         <v>498</v>
       </c>
@@ -6705,14 +6705,14 @@
         <v>499</v>
       </c>
       <c r="E165" s="8">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F165" s="8">
         <v>5</v>
       </c>
       <c r="G165" s="2"/>
     </row>
-    <row r="166" spans="1:7" ht="27" thickBot="1">
+    <row r="166" spans="1:7" ht="28.2" thickBot="1">
       <c r="A166" s="2" t="s">
         <v>502</v>
       </c>
@@ -6726,14 +6726,14 @@
         <v>503</v>
       </c>
       <c r="E166" s="8">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="F166" s="8">
         <v>11</v>
       </c>
       <c r="G166" s="2"/>
     </row>
-    <row r="167" spans="1:7" ht="27" thickBot="1">
+    <row r="167" spans="1:7" ht="28.2" thickBot="1">
       <c r="A167" s="2" t="s">
         <v>505</v>
       </c>
@@ -6745,14 +6745,14 @@
         <v>506</v>
       </c>
       <c r="E167" s="8">
-        <v>371</v>
+        <v>414</v>
       </c>
       <c r="F167" s="8">
         <v>40</v>
       </c>
       <c r="G167" s="2"/>
     </row>
-    <row r="168" spans="1:7" ht="27" thickBot="1">
+    <row r="168" spans="1:7" ht="28.2" thickBot="1">
       <c r="A168" s="2" t="s">
         <v>508</v>
       </c>
@@ -6764,14 +6764,14 @@
         <v>509</v>
       </c>
       <c r="E168" s="8">
-        <v>331</v>
+        <v>370</v>
       </c>
       <c r="F168" s="8">
         <v>35</v>
       </c>
       <c r="G168" s="2"/>
     </row>
-    <row r="169" spans="1:7" ht="27" thickBot="1">
+    <row r="169" spans="1:7" ht="28.2" thickBot="1">
       <c r="A169" s="2" t="s">
         <v>511</v>
       </c>
@@ -6783,14 +6783,14 @@
         <v>512</v>
       </c>
       <c r="E169" s="8">
-        <v>319</v>
+        <v>357</v>
       </c>
       <c r="F169" s="8">
         <v>34</v>
       </c>
       <c r="G169" s="2"/>
     </row>
-    <row r="170" spans="1:7" ht="27" thickBot="1">
+    <row r="170" spans="1:7" ht="28.2" thickBot="1">
       <c r="A170" s="2" t="s">
         <v>514</v>
       </c>
@@ -6802,14 +6802,14 @@
         <v>515</v>
       </c>
       <c r="E170" s="8">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="F170" s="8">
         <v>13</v>
       </c>
       <c r="G170" s="2"/>
     </row>
-    <row r="171" spans="1:7" ht="27" thickBot="1">
+    <row r="171" spans="1:7" ht="28.2" thickBot="1">
       <c r="A171" s="2" t="s">
         <v>517</v>
       </c>
@@ -6821,14 +6821,14 @@
         <v>518</v>
       </c>
       <c r="E171" s="8">
-        <v>618</v>
+        <v>691</v>
       </c>
       <c r="F171" s="8">
         <v>67</v>
       </c>
       <c r="G171" s="2"/>
     </row>
-    <row r="172" spans="1:7" ht="39.75" thickBot="1">
+    <row r="172" spans="1:7" ht="42" thickBot="1">
       <c r="A172" s="2" t="s">
         <v>520</v>
       </c>
@@ -6840,14 +6840,14 @@
         <v>521</v>
       </c>
       <c r="E172" s="8">
-        <v>1088</v>
+        <v>1216</v>
       </c>
       <c r="F172" s="8">
         <v>118</v>
       </c>
       <c r="G172" s="2"/>
     </row>
-    <row r="173" spans="1:7" ht="27" thickBot="1">
+    <row r="173" spans="1:7" ht="28.2" thickBot="1">
       <c r="A173" s="2" t="s">
         <v>523</v>
       </c>
@@ -6859,14 +6859,14 @@
         <v>524</v>
       </c>
       <c r="E173" s="8">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="F173" s="8">
         <v>26</v>
       </c>
       <c r="G173" s="2"/>
     </row>
-    <row r="174" spans="1:7" ht="27" thickBot="1">
+    <row r="174" spans="1:7" ht="28.2" thickBot="1">
       <c r="A174" s="2" t="s">
         <v>526</v>
       </c>
@@ -6878,14 +6878,14 @@
         <v>527</v>
       </c>
       <c r="E174" s="8">
-        <v>948</v>
+        <v>1059</v>
       </c>
       <c r="F174" s="8">
         <v>102</v>
       </c>
       <c r="G174" s="2"/>
     </row>
-    <row r="175" spans="1:7" ht="27" thickBot="1">
+    <row r="175" spans="1:7" ht="28.2" thickBot="1">
       <c r="A175" s="2" t="s">
         <v>529</v>
       </c>
@@ -6897,14 +6897,14 @@
         <v>530</v>
       </c>
       <c r="E175" s="8">
-        <v>1089</v>
+        <v>1217</v>
       </c>
       <c r="F175" s="8">
         <v>118</v>
       </c>
       <c r="G175" s="2"/>
     </row>
-    <row r="176" spans="1:7" ht="27" thickBot="1">
+    <row r="176" spans="1:7" ht="28.2" thickBot="1">
       <c r="A176" s="2" t="s">
         <v>532</v>
       </c>
@@ -6916,14 +6916,14 @@
         <v>533</v>
       </c>
       <c r="E176" s="8">
-        <v>748</v>
+        <v>836</v>
       </c>
       <c r="F176" s="8">
         <v>81</v>
       </c>
       <c r="G176" s="2"/>
     </row>
-    <row r="177" spans="1:7" ht="27" thickBot="1">
+    <row r="177" spans="1:7" ht="28.2" thickBot="1">
       <c r="A177" s="2" t="s">
         <v>535</v>
       </c>
@@ -6935,14 +6935,14 @@
         <v>536</v>
       </c>
       <c r="E177" s="8">
-        <v>849</v>
+        <v>949</v>
       </c>
       <c r="F177" s="8">
         <v>92</v>
       </c>
       <c r="G177" s="2"/>
     </row>
-    <row r="178" spans="1:7" ht="27" thickBot="1">
+    <row r="178" spans="1:7" ht="28.2" thickBot="1">
       <c r="A178" s="2" t="s">
         <v>538</v>
       </c>
@@ -6954,14 +6954,14 @@
         <v>539</v>
       </c>
       <c r="E178" s="8">
-        <v>1010</v>
+        <v>1128</v>
       </c>
       <c r="F178" s="8">
         <v>109</v>
       </c>
       <c r="G178" s="2"/>
     </row>
-    <row r="179" spans="1:7" ht="27" thickBot="1">
+    <row r="179" spans="1:7" ht="28.2" thickBot="1">
       <c r="A179" s="2" t="s">
         <v>541</v>
       </c>
@@ -6973,14 +6973,14 @@
         <v>542</v>
       </c>
       <c r="E179" s="8">
-        <v>1067</v>
+        <v>1193</v>
       </c>
       <c r="F179" s="8">
         <v>115</v>
       </c>
       <c r="G179" s="2"/>
     </row>
-    <row r="180" spans="1:7" ht="27" thickBot="1">
+    <row r="180" spans="1:7" ht="28.2" thickBot="1">
       <c r="A180" s="2" t="s">
         <v>544</v>
       </c>
@@ -6992,14 +6992,14 @@
         <v>545</v>
       </c>
       <c r="E180" s="8">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="F180" s="8">
         <v>26</v>
       </c>
       <c r="G180" s="2"/>
     </row>
-    <row r="181" spans="1:7" ht="39.75" thickBot="1">
+    <row r="181" spans="1:7" ht="42" thickBot="1">
       <c r="A181" s="2" t="s">
         <v>547</v>
       </c>
@@ -7011,14 +7011,14 @@
         <v>548</v>
       </c>
       <c r="E181" s="8">
-        <v>1738</v>
+        <v>1942</v>
       </c>
       <c r="F181" s="8">
         <v>188</v>
       </c>
       <c r="G181" s="2"/>
     </row>
-    <row r="182" spans="1:7" ht="27" thickBot="1">
+    <row r="182" spans="1:7" ht="28.2" thickBot="1">
       <c r="A182" s="2" t="s">
         <v>550</v>
       </c>
@@ -7030,14 +7030,14 @@
         <v>551</v>
       </c>
       <c r="E182" s="8">
-        <v>2410</v>
+        <v>2693</v>
       </c>
       <c r="F182" s="8">
         <v>261</v>
       </c>
       <c r="G182" s="2"/>
     </row>
-    <row r="183" spans="1:7" ht="52.5" thickBot="1">
+    <row r="183" spans="1:7" ht="55.8" thickBot="1">
       <c r="A183" s="2" t="s">
         <v>553</v>
       </c>
@@ -7049,14 +7049,14 @@
         <v>554</v>
       </c>
       <c r="E183" s="8">
-        <v>5219</v>
+        <v>5832</v>
       </c>
       <c r="F183" s="8">
         <v>565</v>
       </c>
       <c r="G183" s="2"/>
     </row>
-    <row r="184" spans="1:7" ht="27" thickBot="1">
+    <row r="184" spans="1:7" ht="28.2" thickBot="1">
       <c r="A184" s="2" t="s">
         <v>556</v>
       </c>
@@ -7068,14 +7068,14 @@
         <v>557</v>
       </c>
       <c r="E184" s="8">
-        <v>785</v>
+        <v>877</v>
       </c>
       <c r="F184" s="8">
         <v>85</v>
       </c>
       <c r="G184" s="2"/>
     </row>
-    <row r="185" spans="1:7" ht="39.75" thickBot="1">
+    <row r="185" spans="1:7" ht="42" thickBot="1">
       <c r="A185" s="2" t="s">
         <v>559</v>
       </c>
@@ -7087,14 +7087,14 @@
         <v>560</v>
       </c>
       <c r="E185" s="8">
-        <v>2089</v>
+        <v>2334</v>
       </c>
       <c r="F185" s="8">
         <v>226</v>
       </c>
       <c r="G185" s="2"/>
     </row>
-    <row r="186" spans="1:7" ht="39.75" thickBot="1">
+    <row r="186" spans="1:7" ht="42" thickBot="1">
       <c r="A186" s="2" t="s">
         <v>562</v>
       </c>
@@ -7106,14 +7106,14 @@
         <v>563</v>
       </c>
       <c r="E186" s="8">
-        <v>1729</v>
+        <v>1932</v>
       </c>
       <c r="F186" s="8">
         <v>187</v>
       </c>
       <c r="G186" s="2"/>
     </row>
-    <row r="187" spans="1:7" ht="39.75" thickBot="1">
+    <row r="187" spans="1:7" ht="42" thickBot="1">
       <c r="A187" s="2" t="s">
         <v>565</v>
       </c>
@@ -7125,14 +7125,14 @@
         <v>566</v>
       </c>
       <c r="E187" s="8">
-        <v>1180</v>
+        <v>1319</v>
       </c>
       <c r="F187" s="8">
         <v>127</v>
       </c>
       <c r="G187" s="2"/>
     </row>
-    <row r="188" spans="1:7" ht="39.75" thickBot="1">
+    <row r="188" spans="1:7" ht="42" thickBot="1">
       <c r="A188" s="2" t="s">
         <v>568</v>
       </c>
@@ -7146,14 +7146,14 @@
         <v>569</v>
       </c>
       <c r="E188" s="8">
-        <v>7038</v>
+        <v>7863</v>
       </c>
       <c r="F188" s="8">
         <v>762</v>
       </c>
       <c r="G188" s="2"/>
     </row>
-    <row r="189" spans="1:7" ht="27" thickBot="1">
+    <row r="189" spans="1:7" ht="28.2" thickBot="1">
       <c r="A189" s="2" t="s">
         <v>571</v>
       </c>
@@ -7167,14 +7167,14 @@
         <v>572</v>
       </c>
       <c r="E189" s="8">
-        <v>1071</v>
+        <v>1197</v>
       </c>
       <c r="F189" s="8">
         <v>116</v>
       </c>
       <c r="G189" s="2"/>
     </row>
-    <row r="190" spans="1:7" ht="39.75" thickBot="1">
+    <row r="190" spans="1:7" ht="42" thickBot="1">
       <c r="A190" s="2" t="s">
         <v>574</v>
       </c>
@@ -7186,14 +7186,14 @@
         <v>575</v>
       </c>
       <c r="E190" s="8">
-        <v>4611</v>
+        <v>5152</v>
       </c>
       <c r="F190" s="8">
         <v>499</v>
       </c>
       <c r="G190" s="2"/>
     </row>
-    <row r="191" spans="1:7" ht="65.25" thickBot="1">
+    <row r="191" spans="1:7" ht="69.599999999999994" thickBot="1">
       <c r="A191" s="2" t="s">
         <v>577</v>
       </c>
@@ -7205,14 +7205,14 @@
         <v>578</v>
       </c>
       <c r="E191" s="8">
-        <v>8838</v>
+        <v>9875</v>
       </c>
       <c r="F191" s="8">
         <v>957</v>
       </c>
       <c r="G191" s="2"/>
     </row>
-    <row r="192" spans="1:7" ht="27" thickBot="1">
+    <row r="192" spans="1:7" ht="28.2" thickBot="1">
       <c r="A192" s="2" t="s">
         <v>580</v>
       </c>
@@ -7224,14 +7224,14 @@
         <v>581</v>
       </c>
       <c r="E192" s="8">
-        <v>281</v>
+        <v>314</v>
       </c>
       <c r="F192" s="8">
         <v>30</v>
       </c>
       <c r="G192" s="2"/>
     </row>
-    <row r="193" spans="1:7" ht="27" thickBot="1">
+    <row r="193" spans="1:7" ht="28.2" thickBot="1">
       <c r="A193" s="2" t="s">
         <v>583</v>
       </c>
@@ -7243,14 +7243,14 @@
         <v>584</v>
       </c>
       <c r="E193" s="8">
-        <v>501</v>
+        <v>560</v>
       </c>
       <c r="F193" s="8">
         <v>54</v>
       </c>
       <c r="G193" s="2"/>
     </row>
-    <row r="194" spans="1:7" ht="27" thickBot="1">
+    <row r="194" spans="1:7" ht="28.2" thickBot="1">
       <c r="A194" s="2" t="s">
         <v>586</v>
       </c>
@@ -7262,14 +7262,14 @@
         <v>587</v>
       </c>
       <c r="E194" s="8">
-        <v>520</v>
+        <v>581</v>
       </c>
       <c r="F194" s="8">
         <v>56</v>
       </c>
       <c r="G194" s="2"/>
     </row>
-    <row r="195" spans="1:7" ht="27" thickBot="1">
+    <row r="195" spans="1:7" ht="28.2" thickBot="1">
       <c r="A195" s="2" t="s">
         <v>589</v>
       </c>
@@ -7281,14 +7281,14 @@
         <v>590</v>
       </c>
       <c r="E195" s="8">
-        <v>922</v>
+        <v>1031</v>
       </c>
       <c r="F195" s="8">
         <v>100</v>
       </c>
       <c r="G195" s="2"/>
     </row>
-    <row r="196" spans="1:7" ht="27" thickBot="1">
+    <row r="196" spans="1:7" ht="28.2" thickBot="1">
       <c r="A196" s="2" t="s">
         <v>592</v>
       </c>
@@ -7300,14 +7300,14 @@
         <v>593</v>
       </c>
       <c r="E196" s="8">
-        <v>1717</v>
+        <v>1919</v>
       </c>
       <c r="F196" s="8">
         <v>186</v>
       </c>
       <c r="G196" s="2"/>
     </row>
-    <row r="197" spans="1:7" ht="27" thickBot="1">
+    <row r="197" spans="1:7" ht="28.2" thickBot="1">
       <c r="A197" s="2" t="s">
         <v>595</v>
       </c>
@@ -7319,14 +7319,14 @@
         <v>596</v>
       </c>
       <c r="E197" s="8">
-        <v>505</v>
+        <v>564</v>
       </c>
       <c r="F197" s="8">
         <v>54</v>
       </c>
       <c r="G197" s="2"/>
     </row>
-    <row r="198" spans="1:7" ht="27" thickBot="1">
+    <row r="198" spans="1:7" ht="28.2" thickBot="1">
       <c r="A198" s="2" t="s">
         <v>598</v>
       </c>
@@ -7338,14 +7338,14 @@
         <v>599</v>
       </c>
       <c r="E198" s="8">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="F198" s="8">
         <v>18</v>
       </c>
       <c r="G198" s="2"/>
     </row>
-    <row r="199" spans="1:7" ht="27" thickBot="1">
+    <row r="199" spans="1:7" ht="28.2" thickBot="1">
       <c r="A199" s="2" t="s">
         <v>601</v>
       </c>
@@ -7357,14 +7357,14 @@
         <v>602</v>
       </c>
       <c r="E199" s="8">
-        <v>2102</v>
+        <v>2349</v>
       </c>
       <c r="F199" s="8">
         <v>227</v>
       </c>
       <c r="G199" s="2"/>
     </row>
-    <row r="200" spans="1:7" ht="52.5" thickBot="1">
+    <row r="200" spans="1:7" ht="55.8" thickBot="1">
       <c r="A200" s="2" t="s">
         <v>604</v>
       </c>
@@ -7376,14 +7376,14 @@
         <v>605</v>
       </c>
       <c r="E200" s="8">
-        <v>10095</v>
+        <v>11279</v>
       </c>
       <c r="F200" s="8">
         <v>1094</v>
       </c>
       <c r="G200" s="2"/>
     </row>
-    <row r="201" spans="1:7" ht="52.5" thickBot="1">
+    <row r="201" spans="1:7" ht="55.8" thickBot="1">
       <c r="A201" s="2" t="s">
         <v>607</v>
       </c>
@@ -7395,14 +7395,14 @@
         <v>608</v>
       </c>
       <c r="E201" s="8">
-        <v>10896</v>
+        <v>12175</v>
       </c>
       <c r="F201" s="8">
         <v>1180</v>
       </c>
       <c r="G201" s="2"/>
     </row>
-    <row r="202" spans="1:7" ht="27" thickBot="1">
+    <row r="202" spans="1:7" ht="28.2" thickBot="1">
       <c r="A202" s="2" t="s">
         <v>610</v>
       </c>
@@ -7414,14 +7414,14 @@
         <v>611</v>
       </c>
       <c r="E202" s="8">
-        <v>1960</v>
+        <v>2190</v>
       </c>
       <c r="F202" s="8">
         <v>212</v>
       </c>
       <c r="G202" s="2"/>
     </row>
-    <row r="203" spans="1:7" ht="27" thickBot="1">
+    <row r="203" spans="1:7" ht="28.2" thickBot="1">
       <c r="A203" s="2" t="s">
         <v>613</v>
       </c>
@@ -7433,14 +7433,14 @@
         <v>614</v>
       </c>
       <c r="E203" s="8">
-        <v>2135</v>
+        <v>2385</v>
       </c>
       <c r="F203" s="8">
         <v>231</v>
       </c>
       <c r="G203" s="2"/>
     </row>
-    <row r="204" spans="1:7" ht="52.5" thickBot="1">
+    <row r="204" spans="1:7" ht="55.8" thickBot="1">
       <c r="A204" s="2" t="s">
         <v>616</v>
       </c>
@@ -7452,14 +7452,14 @@
         <v>617</v>
       </c>
       <c r="E204" s="8">
-        <v>4038</v>
+        <v>4512</v>
       </c>
       <c r="F204" s="8">
         <v>437</v>
       </c>
       <c r="G204" s="2"/>
     </row>
-    <row r="205" spans="1:7" ht="15.75" thickBot="1">
+    <row r="205" spans="1:7" ht="15" thickBot="1">
       <c r="A205" s="2" t="s">
         <v>619</v>
       </c>
@@ -7471,14 +7471,14 @@
         <v>620</v>
       </c>
       <c r="E205" s="8">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="F205" s="8">
         <v>24</v>
       </c>
       <c r="G205" s="2"/>
     </row>
-    <row r="206" spans="1:7" ht="27" thickBot="1">
+    <row r="206" spans="1:7" ht="28.2" thickBot="1">
       <c r="A206" s="2" t="s">
         <v>622</v>
       </c>
@@ -7490,14 +7490,14 @@
         <v>623</v>
       </c>
       <c r="E206" s="8">
-        <v>883</v>
+        <v>986</v>
       </c>
       <c r="F206" s="8">
         <v>95</v>
       </c>
       <c r="G206" s="2"/>
     </row>
-    <row r="207" spans="1:7" ht="27" thickBot="1">
+    <row r="207" spans="1:7" ht="28.2" thickBot="1">
       <c r="A207" s="2" t="s">
         <v>625</v>
       </c>
@@ -7509,14 +7509,14 @@
         <v>626</v>
       </c>
       <c r="E207" s="8">
-        <v>753</v>
+        <v>842</v>
       </c>
       <c r="F207" s="8">
         <v>81</v>
       </c>
       <c r="G207" s="2"/>
     </row>
-    <row r="208" spans="1:7" ht="27" thickBot="1">
+    <row r="208" spans="1:7" ht="28.2" thickBot="1">
       <c r="A208" s="2" t="s">
         <v>628</v>
       </c>
@@ -7528,14 +7528,14 @@
         <v>629</v>
       </c>
       <c r="E208" s="8">
-        <v>409</v>
+        <v>457</v>
       </c>
       <c r="F208" s="8">
         <v>44</v>
       </c>
       <c r="G208" s="2"/>
     </row>
-    <row r="209" spans="1:7" ht="52.5" thickBot="1">
+    <row r="209" spans="1:7" ht="55.8" thickBot="1">
       <c r="A209" s="2" t="s">
         <v>631</v>
       </c>
@@ -7547,14 +7547,14 @@
         <v>632</v>
       </c>
       <c r="E209" s="8">
-        <v>3090</v>
+        <v>3453</v>
       </c>
       <c r="F209" s="8">
         <v>334</v>
       </c>
       <c r="G209" s="2"/>
     </row>
-    <row r="210" spans="1:7" ht="27" thickBot="1">
+    <row r="210" spans="1:7" ht="28.2" thickBot="1">
       <c r="A210" s="2" t="s">
         <v>634</v>
       </c>
@@ -7566,14 +7566,14 @@
         <v>635</v>
       </c>
       <c r="E210" s="8">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="F210" s="8">
         <v>13</v>
       </c>
       <c r="G210" s="2"/>
     </row>
-    <row r="211" spans="1:7" ht="90.75" thickBot="1">
+    <row r="211" spans="1:7" ht="97.2" thickBot="1">
       <c r="A211" s="2" t="s">
         <v>637</v>
       </c>
@@ -7587,14 +7587,14 @@
         <v>638</v>
       </c>
       <c r="E211" s="8">
-        <v>15731</v>
+        <v>17576</v>
       </c>
       <c r="F211" s="8">
         <v>1704</v>
       </c>
       <c r="G211" s="2"/>
     </row>
-    <row r="212" spans="1:7" ht="52.5" thickBot="1">
+    <row r="212" spans="1:7" ht="55.8" thickBot="1">
       <c r="A212" s="2" t="s">
         <v>640</v>
       </c>
@@ -7606,14 +7606,14 @@
         <v>641</v>
       </c>
       <c r="E212" s="8">
-        <v>3306</v>
+        <v>3694</v>
       </c>
       <c r="F212" s="8">
         <v>358</v>
       </c>
       <c r="G212" s="2"/>
     </row>
-    <row r="213" spans="1:7" ht="27" thickBot="1">
+    <row r="213" spans="1:7" ht="28.2" thickBot="1">
       <c r="A213" s="2" t="s">
         <v>643</v>
       </c>
@@ -7625,14 +7625,14 @@
         <v>644</v>
       </c>
       <c r="E213" s="8">
-        <v>1588</v>
+        <v>1774</v>
       </c>
       <c r="F213" s="8">
         <v>172</v>
       </c>
       <c r="G213" s="2"/>
     </row>
-    <row r="214" spans="1:7" ht="27" thickBot="1">
+    <row r="214" spans="1:7" ht="28.2" thickBot="1">
       <c r="A214" s="2" t="s">
         <v>646</v>
       </c>
@@ -7644,14 +7644,14 @@
         <v>647</v>
       </c>
       <c r="E214" s="8">
-        <v>831</v>
+        <v>929</v>
       </c>
       <c r="F214" s="8">
         <v>90</v>
       </c>
       <c r="G214" s="2"/>
     </row>
-    <row r="215" spans="1:7" ht="39.75" thickBot="1">
+    <row r="215" spans="1:7" ht="42" thickBot="1">
       <c r="A215" s="2" t="s">
         <v>649</v>
       </c>
@@ -7663,14 +7663,14 @@
         <v>650</v>
       </c>
       <c r="E215" s="8">
-        <v>1292</v>
+        <v>1443</v>
       </c>
       <c r="F215" s="8">
         <v>140</v>
       </c>
       <c r="G215" s="2"/>
     </row>
-    <row r="216" spans="1:7" ht="27" thickBot="1">
+    <row r="216" spans="1:7" ht="28.2" thickBot="1">
       <c r="A216" s="2" t="s">
         <v>652</v>
       </c>
@@ -7682,14 +7682,14 @@
         <v>653</v>
       </c>
       <c r="E216" s="8">
-        <v>932</v>
+        <v>1041</v>
       </c>
       <c r="F216" s="8">
         <v>101</v>
       </c>
       <c r="G216" s="2"/>
     </row>
-    <row r="217" spans="1:7" ht="15.75" thickBot="1">
+    <row r="217" spans="1:7" ht="15" thickBot="1">
       <c r="A217" s="2" t="s">
         <v>655</v>
       </c>
@@ -7701,14 +7701,14 @@
         <v>656</v>
       </c>
       <c r="E217" s="8">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="F217" s="8">
         <v>22</v>
       </c>
       <c r="G217" s="2"/>
     </row>
-    <row r="218" spans="1:7" ht="39.75" thickBot="1">
+    <row r="218" spans="1:7" ht="42" thickBot="1">
       <c r="A218" s="2" t="s">
         <v>658</v>
       </c>
@@ -7722,14 +7722,14 @@
         <v>659</v>
       </c>
       <c r="E218" s="8">
-        <v>4532</v>
+        <v>5063</v>
       </c>
       <c r="F218" s="8">
         <v>491</v>
       </c>
       <c r="G218" s="2"/>
     </row>
-    <row r="219" spans="1:7" ht="39.75" thickBot="1">
+    <row r="219" spans="1:7" ht="42" thickBot="1">
       <c r="A219" s="2" t="s">
         <v>661</v>
       </c>
@@ -7741,14 +7741,14 @@
         <v>662</v>
       </c>
       <c r="E219" s="8">
-        <v>1989</v>
+        <v>2222</v>
       </c>
       <c r="F219" s="8">
         <v>215</v>
       </c>
       <c r="G219" s="2"/>
     </row>
-    <row r="220" spans="1:7" ht="27" thickBot="1">
+    <row r="220" spans="1:7" ht="28.2" thickBot="1">
       <c r="A220" s="2" t="s">
         <v>664</v>
       </c>
@@ -7760,14 +7760,14 @@
         <v>665</v>
       </c>
       <c r="E220" s="8">
-        <v>1574</v>
+        <v>1759</v>
       </c>
       <c r="F220" s="8">
         <v>170</v>
       </c>
       <c r="G220" s="2"/>
     </row>
-    <row r="221" spans="1:7" ht="27" thickBot="1">
+    <row r="221" spans="1:7" ht="28.2" thickBot="1">
       <c r="A221" s="2" t="s">
         <v>667</v>
       </c>
@@ -7779,14 +7779,14 @@
         <v>668</v>
       </c>
       <c r="E221" s="8">
-        <v>1322</v>
+        <v>1477</v>
       </c>
       <c r="F221" s="8">
         <v>143</v>
       </c>
       <c r="G221" s="2"/>
     </row>
-    <row r="222" spans="1:7" ht="27" thickBot="1">
+    <row r="222" spans="1:7" ht="28.2" thickBot="1">
       <c r="A222" s="2" t="s">
         <v>670</v>
       </c>
@@ -7798,14 +7798,14 @@
         <v>671</v>
       </c>
       <c r="E222" s="8">
-        <v>1281</v>
+        <v>1432</v>
       </c>
       <c r="F222" s="8">
         <v>138</v>
       </c>
       <c r="G222" s="2"/>
     </row>
-    <row r="223" spans="1:7" ht="27" thickBot="1">
+    <row r="223" spans="1:7" ht="28.2" thickBot="1">
       <c r="A223" s="2" t="s">
         <v>673</v>
       </c>
@@ -7817,14 +7817,14 @@
         <v>674</v>
       </c>
       <c r="E223" s="8">
-        <v>9624</v>
+        <v>10753</v>
       </c>
       <c r="F223" s="8">
         <v>1043</v>
       </c>
       <c r="G223" s="2"/>
     </row>
-    <row r="224" spans="1:7" ht="39.75" thickBot="1">
+    <row r="224" spans="1:7" ht="42" thickBot="1">
       <c r="A224" s="2" t="s">
         <v>676</v>
       </c>
@@ -7836,14 +7836,14 @@
         <v>677</v>
       </c>
       <c r="E224" s="8">
-        <v>5639</v>
+        <v>6301</v>
       </c>
       <c r="F224" s="8">
         <v>611</v>
       </c>
       <c r="G224" s="2"/>
     </row>
-    <row r="225" spans="1:7" ht="27" thickBot="1">
+    <row r="225" spans="1:7" ht="28.2" thickBot="1">
       <c r="A225" s="2" t="s">
         <v>679</v>
       </c>
@@ -7855,14 +7855,14 @@
         <v>680</v>
       </c>
       <c r="E225" s="8">
-        <v>823</v>
+        <v>919</v>
       </c>
       <c r="F225" s="8">
         <v>89</v>
       </c>
       <c r="G225" s="2"/>
     </row>
-    <row r="226" spans="1:7" ht="27" thickBot="1">
+    <row r="226" spans="1:7" ht="28.2" thickBot="1">
       <c r="A226" s="2" t="s">
         <v>682</v>
       </c>
@@ -7874,14 +7874,14 @@
         <v>683</v>
       </c>
       <c r="E226" s="8">
-        <v>673</v>
+        <v>752</v>
       </c>
       <c r="F226" s="8">
         <v>72</v>
       </c>
       <c r="G226" s="2"/>
     </row>
-    <row r="227" spans="1:7" ht="27" thickBot="1">
+    <row r="227" spans="1:7" ht="28.2" thickBot="1">
       <c r="A227" s="2" t="s">
         <v>685</v>
       </c>
@@ -7893,14 +7893,14 @@
         <v>686</v>
       </c>
       <c r="E227" s="8">
-        <v>921</v>
+        <v>1029</v>
       </c>
       <c r="F227" s="8">
         <v>99</v>
       </c>
       <c r="G227" s="2"/>
     </row>
-    <row r="228" spans="1:7" ht="27" thickBot="1">
+    <row r="228" spans="1:7" ht="28.2" thickBot="1">
       <c r="A228" s="2" t="s">
         <v>688</v>
       </c>
@@ -7912,14 +7912,14 @@
         <v>689</v>
       </c>
       <c r="E228" s="8">
-        <v>1734</v>
+        <v>1937</v>
       </c>
       <c r="F228" s="8">
         <v>187</v>
       </c>
       <c r="G228" s="2"/>
     </row>
-    <row r="229" spans="1:7" ht="27" thickBot="1">
+    <row r="229" spans="1:7" ht="28.2" thickBot="1">
       <c r="A229" s="2" t="s">
         <v>691</v>
       </c>
@@ -7931,14 +7931,14 @@
         <v>692</v>
       </c>
       <c r="E229" s="8">
-        <v>770</v>
+        <v>861</v>
       </c>
       <c r="F229" s="8">
         <v>83</v>
       </c>
       <c r="G229" s="2"/>
     </row>
-    <row r="230" spans="1:7" ht="52.5" thickBot="1">
+    <row r="230" spans="1:7" ht="55.8" thickBot="1">
       <c r="A230" s="2" t="s">
         <v>694</v>
       </c>
@@ -7950,14 +7950,14 @@
         <v>695</v>
       </c>
       <c r="E230" s="8">
-        <v>10152</v>
+        <v>11343</v>
       </c>
       <c r="F230" s="8">
         <v>1100</v>
       </c>
       <c r="G230" s="2"/>
     </row>
-    <row r="231" spans="1:7" ht="39.75" thickBot="1">
+    <row r="231" spans="1:7" ht="42" thickBot="1">
       <c r="A231" s="2" t="s">
         <v>697</v>
       </c>
@@ -7971,14 +7971,14 @@
         <v>698</v>
       </c>
       <c r="E231" s="8">
-        <v>5283</v>
+        <v>5903</v>
       </c>
       <c r="F231" s="8">
         <v>572</v>
       </c>
       <c r="G231" s="2"/>
     </row>
-    <row r="232" spans="1:7" ht="27" thickBot="1">
+    <row r="232" spans="1:7" ht="28.2" thickBot="1">
       <c r="A232" s="2" t="s">
         <v>700</v>
       </c>
@@ -7990,14 +7990,14 @@
         <v>701</v>
       </c>
       <c r="E232" s="8">
-        <v>1475</v>
+        <v>1648</v>
       </c>
       <c r="F232" s="8">
         <v>159</v>
       </c>
       <c r="G232" s="2"/>
     </row>
-    <row r="233" spans="1:7" ht="27" thickBot="1">
+    <row r="233" spans="1:7" ht="28.2" thickBot="1">
       <c r="A233" s="2" t="s">
         <v>703</v>
       </c>
@@ -8009,14 +8009,14 @@
         <v>704</v>
       </c>
       <c r="E233" s="8">
-        <v>1237</v>
+        <v>1382</v>
       </c>
       <c r="F233" s="8">
         <v>134</v>
       </c>
       <c r="G233" s="2"/>
     </row>
-    <row r="234" spans="1:7" ht="27" thickBot="1">
+    <row r="234" spans="1:7" ht="28.2" thickBot="1">
       <c r="A234" s="2" t="s">
         <v>706</v>
       </c>
@@ -8028,14 +8028,14 @@
         <v>707</v>
       </c>
       <c r="E234" s="8">
-        <v>3426</v>
+        <v>3828</v>
       </c>
       <c r="F234" s="8">
         <v>371</v>
       </c>
       <c r="G234" s="2"/>
     </row>
-    <row r="235" spans="1:7" ht="27" thickBot="1">
+    <row r="235" spans="1:7" ht="28.2" thickBot="1">
       <c r="A235" s="2" t="s">
         <v>709</v>
       </c>
@@ -8047,14 +8047,14 @@
         <v>710</v>
       </c>
       <c r="E235" s="8">
-        <v>1552</v>
+        <v>1734</v>
       </c>
       <c r="F235" s="8">
         <v>168</v>
       </c>
       <c r="G235" s="2"/>
     </row>
-    <row r="236" spans="1:7" ht="27" thickBot="1">
+    <row r="236" spans="1:7" ht="28.2" thickBot="1">
       <c r="A236" s="2" t="s">
         <v>712</v>
       </c>
@@ -8066,14 +8066,14 @@
         <v>713</v>
       </c>
       <c r="E236" s="8">
-        <v>1693</v>
+        <v>1891</v>
       </c>
       <c r="F236" s="8">
         <v>183</v>
       </c>
       <c r="G236" s="2"/>
     </row>
-    <row r="237" spans="1:7" ht="27" thickBot="1">
+    <row r="237" spans="1:7" ht="28.2" thickBot="1">
       <c r="A237" s="2" t="s">
         <v>715</v>
       </c>
@@ -8085,14 +8085,14 @@
         <v>716</v>
       </c>
       <c r="E237" s="8">
-        <v>469</v>
+        <v>524</v>
       </c>
       <c r="F237" s="8">
         <v>50</v>
       </c>
       <c r="G237" s="2"/>
     </row>
-    <row r="238" spans="1:7" ht="15.75" thickBot="1">
+    <row r="238" spans="1:7" ht="15" thickBot="1">
       <c r="A238" s="2" t="s">
         <v>718</v>
       </c>
@@ -8104,14 +8104,14 @@
         <v>719</v>
       </c>
       <c r="E238" s="8">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F238" s="8">
         <v>6</v>
       </c>
       <c r="G238" s="2"/>
     </row>
-    <row r="239" spans="1:7" ht="27" thickBot="1">
+    <row r="239" spans="1:7" ht="28.2" thickBot="1">
       <c r="A239" s="2" t="s">
         <v>721</v>
       </c>
@@ -8123,14 +8123,14 @@
         <v>722</v>
       </c>
       <c r="E239" s="8">
-        <v>628</v>
+        <v>702</v>
       </c>
       <c r="F239" s="8">
         <v>68</v>
       </c>
       <c r="G239" s="2"/>
     </row>
-    <row r="240" spans="1:7" ht="27" thickBot="1">
+    <row r="240" spans="1:7" ht="28.2" thickBot="1">
       <c r="A240" s="2" t="s">
         <v>724</v>
       </c>
@@ -8142,14 +8142,14 @@
         <v>725</v>
       </c>
       <c r="E240" s="8">
-        <v>2719</v>
+        <v>3038</v>
       </c>
       <c r="F240" s="8">
         <v>294</v>
       </c>
       <c r="G240" s="2"/>
     </row>
-    <row r="241" spans="1:7" ht="27" thickBot="1">
+    <row r="241" spans="1:7" ht="28.2" thickBot="1">
       <c r="A241" s="2" t="s">
         <v>727</v>
       </c>
@@ -8161,14 +8161,14 @@
         <v>728</v>
       </c>
       <c r="E241" s="8">
-        <v>598</v>
+        <v>669</v>
       </c>
       <c r="F241" s="8">
         <v>64</v>
       </c>
       <c r="G241" s="2"/>
     </row>
-    <row r="242" spans="1:7" ht="52.5" thickBot="1">
+    <row r="242" spans="1:7" ht="55.8" thickBot="1">
       <c r="A242" s="2" t="s">
         <v>730</v>
       </c>
@@ -8180,14 +8180,14 @@
         <v>731</v>
       </c>
       <c r="E242" s="8">
-        <v>4416</v>
+        <v>4934</v>
       </c>
       <c r="F242" s="8">
         <v>478</v>
       </c>
       <c r="G242" s="2"/>
     </row>
-    <row r="243" spans="1:7" ht="15.75" thickBot="1">
+    <row r="243" spans="1:7" ht="15" thickBot="1">
       <c r="A243" s="2" t="s">
         <v>733</v>
       </c>
@@ -8199,14 +8199,14 @@
         <v>734</v>
       </c>
       <c r="E243" s="8">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F243" s="8">
         <v>4</v>
       </c>
       <c r="G243" s="2"/>
     </row>
-    <row r="244" spans="1:7" ht="27" thickBot="1">
+    <row r="244" spans="1:7" ht="28.2" thickBot="1">
       <c r="A244" s="2" t="s">
         <v>736</v>
       </c>
@@ -8218,14 +8218,14 @@
         <v>737</v>
       </c>
       <c r="E244" s="8">
-        <v>1708</v>
+        <v>1909</v>
       </c>
       <c r="F244" s="8">
         <v>185</v>
       </c>
       <c r="G244" s="2"/>
     </row>
-    <row r="245" spans="1:7" ht="15.75" thickBot="1">
+    <row r="245" spans="1:7" ht="15" thickBot="1">
       <c r="A245" s="2" t="s">
         <v>739</v>
       </c>
@@ -8237,14 +8237,14 @@
         <v>740</v>
       </c>
       <c r="E245" s="8">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F245" s="8">
         <v>9</v>
       </c>
       <c r="G245" s="2"/>
     </row>
-    <row r="246" spans="1:7" ht="27" thickBot="1">
+    <row r="246" spans="1:7" ht="28.2" thickBot="1">
       <c r="A246" s="2" t="s">
         <v>742</v>
       </c>
@@ -8256,14 +8256,14 @@
         <v>743</v>
       </c>
       <c r="E246" s="8">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="F246" s="8">
         <v>33</v>
       </c>
       <c r="G246" s="2"/>
     </row>
-    <row r="247" spans="1:7" ht="15.75" thickBot="1">
+    <row r="247" spans="1:7" ht="15" thickBot="1">
       <c r="A247" s="2" t="s">
         <v>745</v>
       </c>
@@ -8275,14 +8275,14 @@
         <v>746</v>
       </c>
       <c r="E247" s="8">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F247" s="8">
         <v>6</v>
       </c>
       <c r="G247" s="2"/>
     </row>
-    <row r="248" spans="1:7" ht="27" thickBot="1">
+    <row r="248" spans="1:7" ht="28.2" thickBot="1">
       <c r="A248" s="2" t="s">
         <v>748</v>
       </c>
@@ -8294,14 +8294,14 @@
         <v>749</v>
       </c>
       <c r="E248" s="8">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="F248" s="8">
         <v>24</v>
       </c>
       <c r="G248" s="2"/>
     </row>
-    <row r="249" spans="1:7" ht="27" thickBot="1">
+    <row r="249" spans="1:7" ht="28.2" thickBot="1">
       <c r="A249" s="2" t="s">
         <v>751</v>
       </c>
@@ -8313,14 +8313,14 @@
         <v>752</v>
       </c>
       <c r="E249" s="8">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F249" s="8">
         <v>8</v>
       </c>
       <c r="G249" s="2"/>
     </row>
-    <row r="250" spans="1:7" ht="27" thickBot="1">
+    <row r="250" spans="1:7" ht="28.2" thickBot="1">
       <c r="A250" s="2" t="s">
         <v>754</v>
       </c>
@@ -8332,14 +8332,14 @@
         <v>755</v>
       </c>
       <c r="E250" s="8">
-        <v>783</v>
+        <v>874</v>
       </c>
       <c r="F250" s="8">
         <v>84</v>
       </c>
       <c r="G250" s="2"/>
     </row>
-    <row r="251" spans="1:7" ht="27" thickBot="1">
+    <row r="251" spans="1:7" ht="28.2" thickBot="1">
       <c r="A251" s="2" t="s">
         <v>757</v>
       </c>
@@ -8351,14 +8351,14 @@
         <v>758</v>
       </c>
       <c r="E251" s="8">
-        <v>654</v>
+        <v>731</v>
       </c>
       <c r="F251" s="8">
         <v>70</v>
       </c>
       <c r="G251" s="2"/>
     </row>
-    <row r="252" spans="1:7" ht="27" thickBot="1">
+    <row r="252" spans="1:7" ht="28.2" thickBot="1">
       <c r="A252" s="2" t="s">
         <v>760</v>
       </c>
@@ -8370,14 +8370,14 @@
         <v>761</v>
       </c>
       <c r="E252" s="8">
-        <v>2511</v>
+        <v>2805</v>
       </c>
       <c r="F252" s="8">
         <v>272</v>
       </c>
       <c r="G252" s="2"/>
     </row>
-    <row r="253" spans="1:7" ht="27" thickBot="1">
+    <row r="253" spans="1:7" ht="28.2" thickBot="1">
       <c r="A253" s="2" t="s">
         <v>763</v>
       </c>
@@ -8389,14 +8389,14 @@
         <v>764</v>
       </c>
       <c r="E253" s="8">
-        <v>416</v>
+        <v>464</v>
       </c>
       <c r="F253" s="8">
         <v>45</v>
       </c>
       <c r="G253" s="2"/>
     </row>
-    <row r="254" spans="1:7" ht="27" thickBot="1">
+    <row r="254" spans="1:7" ht="28.2" thickBot="1">
       <c r="A254" s="2" t="s">
         <v>766</v>
       </c>
@@ -8408,14 +8408,14 @@
         <v>767</v>
       </c>
       <c r="E254" s="8">
-        <v>312</v>
+        <v>349</v>
       </c>
       <c r="F254" s="8">
         <v>33</v>
       </c>
       <c r="G254" s="2"/>
     </row>
-    <row r="255" spans="1:7" ht="15.75" thickBot="1">
+    <row r="255" spans="1:7" ht="15" thickBot="1">
       <c r="A255" s="2" t="s">
         <v>769</v>
       </c>
@@ -8427,14 +8427,14 @@
         <v>770</v>
       </c>
       <c r="E255" s="8">
-        <v>405</v>
+        <v>452</v>
       </c>
       <c r="F255" s="8">
         <v>43</v>
       </c>
       <c r="G255" s="2"/>
     </row>
-    <row r="256" spans="1:7" ht="27" thickBot="1">
+    <row r="256" spans="1:7" ht="28.2" thickBot="1">
       <c r="A256" s="2" t="s">
         <v>772</v>
       </c>
@@ -8446,14 +8446,14 @@
         <v>773</v>
       </c>
       <c r="E256" s="8">
-        <v>434</v>
+        <v>485</v>
       </c>
       <c r="F256" s="8">
         <v>47</v>
       </c>
       <c r="G256" s="2"/>
     </row>
-    <row r="257" spans="1:7" ht="27" thickBot="1">
+    <row r="257" spans="1:7" ht="28.2" thickBot="1">
       <c r="A257" s="2" t="s">
         <v>775</v>
       </c>
@@ -8465,14 +8465,14 @@
         <v>776</v>
       </c>
       <c r="E257" s="8">
-        <v>477</v>
+        <v>532</v>
       </c>
       <c r="F257" s="8">
         <v>51</v>
       </c>
       <c r="G257" s="2"/>
     </row>
-    <row r="258" spans="1:7" ht="27" thickBot="1">
+    <row r="258" spans="1:7" ht="28.2" thickBot="1">
       <c r="A258" s="2" t="s">
         <v>778</v>
       </c>
@@ -8484,14 +8484,14 @@
         <v>779</v>
       </c>
       <c r="E258" s="8">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="F258" s="8">
         <v>11</v>
       </c>
       <c r="G258" s="2"/>
     </row>
-    <row r="259" spans="1:7" ht="27" thickBot="1">
+    <row r="259" spans="1:7" ht="28.2" thickBot="1">
       <c r="A259" s="2" t="s">
         <v>781</v>
       </c>
@@ -8503,14 +8503,14 @@
         <v>782</v>
       </c>
       <c r="E259" s="8">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="F259" s="8">
         <v>16</v>
       </c>
       <c r="G259" s="2"/>
     </row>
-    <row r="260" spans="1:7" ht="27" thickBot="1">
+    <row r="260" spans="1:7" ht="28.2" thickBot="1">
       <c r="A260" s="2" t="s">
         <v>784</v>
       </c>
@@ -8522,14 +8522,14 @@
         <v>785</v>
       </c>
       <c r="E260" s="8">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="F260" s="8">
         <v>17</v>
       </c>
       <c r="G260" s="2"/>
     </row>
-    <row r="261" spans="1:7" ht="27" thickBot="1">
+    <row r="261" spans="1:7" ht="28.2" thickBot="1">
       <c r="A261" s="2" t="s">
         <v>787</v>
       </c>
@@ -8541,14 +8541,14 @@
         <v>788</v>
       </c>
       <c r="E261" s="8">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="F261" s="8">
         <v>23</v>
       </c>
       <c r="G261" s="2"/>
     </row>
-    <row r="262" spans="1:7" ht="27" thickBot="1">
+    <row r="262" spans="1:7" ht="28.2" thickBot="1">
       <c r="A262" s="2" t="s">
         <v>790</v>
       </c>
@@ -8560,14 +8560,14 @@
         <v>791</v>
       </c>
       <c r="E262" s="8">
-        <v>509</v>
+        <v>569</v>
       </c>
       <c r="F262" s="8">
         <v>55</v>
       </c>
       <c r="G262" s="2"/>
     </row>
-    <row r="263" spans="1:7" ht="27" thickBot="1">
+    <row r="263" spans="1:7" ht="28.2" thickBot="1">
       <c r="A263" s="2" t="s">
         <v>793</v>
       </c>
@@ -8579,14 +8579,14 @@
         <v>794</v>
       </c>
       <c r="E263" s="8">
-        <v>375</v>
+        <v>419</v>
       </c>
       <c r="F263" s="8">
         <v>40</v>
       </c>
       <c r="G263" s="2"/>
     </row>
-    <row r="264" spans="1:7" ht="27" thickBot="1">
+    <row r="264" spans="1:7" ht="28.2" thickBot="1">
       <c r="A264" s="2" t="s">
         <v>796</v>
       </c>
@@ -8598,14 +8598,14 @@
         <v>797</v>
       </c>
       <c r="E264" s="8">
-        <v>443</v>
+        <v>495</v>
       </c>
       <c r="F264" s="8">
         <v>48</v>
       </c>
       <c r="G264" s="2"/>
     </row>
-    <row r="265" spans="1:7" ht="27" thickBot="1">
+    <row r="265" spans="1:7" ht="28.2" thickBot="1">
       <c r="A265" s="2" t="s">
         <v>799</v>
       </c>
@@ -8617,14 +8617,14 @@
         <v>800</v>
       </c>
       <c r="E265" s="8">
-        <v>294</v>
+        <v>329</v>
       </c>
       <c r="F265" s="8">
         <v>31</v>
       </c>
       <c r="G265" s="2"/>
     </row>
-    <row r="266" spans="1:7" ht="27" thickBot="1">
+    <row r="266" spans="1:7" ht="28.2" thickBot="1">
       <c r="A266" s="2" t="s">
         <v>802</v>
       </c>
@@ -8636,14 +8636,14 @@
         <v>803</v>
       </c>
       <c r="E266" s="8">
-        <v>1179</v>
+        <v>1317</v>
       </c>
       <c r="F266" s="8">
         <v>127</v>
       </c>
       <c r="G266" s="2"/>
     </row>
-    <row r="267" spans="1:7" ht="27" thickBot="1">
+    <row r="267" spans="1:7" ht="28.2" thickBot="1">
       <c r="A267" s="2" t="s">
         <v>805</v>
       </c>
@@ -8655,14 +8655,14 @@
         <v>806</v>
       </c>
       <c r="E267" s="8">
-        <v>452</v>
+        <v>505</v>
       </c>
       <c r="F267" s="8">
         <v>49</v>
       </c>
       <c r="G267" s="2"/>
     </row>
-    <row r="268" spans="1:7" ht="27" thickBot="1">
+    <row r="268" spans="1:7" ht="28.2" thickBot="1">
       <c r="A268" s="2" t="s">
         <v>808</v>
       </c>
@@ -8674,14 +8674,14 @@
         <v>809</v>
       </c>
       <c r="E268" s="8">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="F268" s="8">
         <v>17</v>
       </c>
       <c r="G268" s="2"/>
     </row>
-    <row r="269" spans="1:7" ht="15.75" thickBot="1">
+    <row r="269" spans="1:7" ht="15" thickBot="1">
       <c r="A269" s="2" t="s">
         <v>811</v>
       </c>
@@ -8693,14 +8693,14 @@
         <v>812</v>
       </c>
       <c r="E269" s="8">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="F269" s="8">
         <v>15</v>
       </c>
       <c r="G269" s="2"/>
     </row>
-    <row r="270" spans="1:7" ht="27" thickBot="1">
+    <row r="270" spans="1:7" ht="28.2" thickBot="1">
       <c r="A270" s="2" t="s">
         <v>814</v>
       </c>
@@ -8712,14 +8712,14 @@
         <v>815</v>
       </c>
       <c r="E270" s="8">
-        <v>249</v>
+        <v>278</v>
       </c>
       <c r="F270" s="8">
         <v>27</v>
       </c>
       <c r="G270" s="2"/>
     </row>
-    <row r="271" spans="1:7" ht="27" thickBot="1">
+    <row r="271" spans="1:7" ht="28.2" thickBot="1">
       <c r="A271" s="2" t="s">
         <v>817</v>
       </c>
@@ -8731,14 +8731,14 @@
         <v>818</v>
       </c>
       <c r="E271" s="8">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="F271" s="8">
         <v>18</v>
       </c>
       <c r="G271" s="2"/>
     </row>
-    <row r="272" spans="1:7" ht="27" thickBot="1">
+    <row r="272" spans="1:7" ht="28.2" thickBot="1">
       <c r="A272" s="2" t="s">
         <v>820</v>
       </c>
@@ -8750,14 +8750,14 @@
         <v>821</v>
       </c>
       <c r="E272" s="8">
-        <v>533</v>
+        <v>595</v>
       </c>
       <c r="F272" s="8">
         <v>57</v>
       </c>
       <c r="G272" s="2"/>
     </row>
-    <row r="273" spans="1:7" ht="27" thickBot="1">
+    <row r="273" spans="1:7" ht="28.2" thickBot="1">
       <c r="A273" s="2" t="s">
         <v>823</v>
       </c>
@@ -8769,14 +8769,14 @@
         <v>824</v>
       </c>
       <c r="E273" s="8">
-        <v>464</v>
+        <v>518</v>
       </c>
       <c r="F273" s="8">
         <v>50</v>
       </c>
       <c r="G273" s="2"/>
     </row>
-    <row r="274" spans="1:7" ht="27" thickBot="1">
+    <row r="274" spans="1:7" ht="28.2" thickBot="1">
       <c r="A274" s="2" t="s">
         <v>826</v>
       </c>
@@ -8788,14 +8788,14 @@
         <v>827</v>
       </c>
       <c r="E274" s="8">
-        <v>420</v>
+        <v>469</v>
       </c>
       <c r="F274" s="8">
         <v>45</v>
       </c>
       <c r="G274" s="2"/>
     </row>
-    <row r="275" spans="1:7" ht="39.75" thickBot="1">
+    <row r="275" spans="1:7" ht="42" thickBot="1">
       <c r="A275" s="2" t="s">
         <v>829</v>
       </c>
@@ -8807,14 +8807,14 @@
         <v>830</v>
       </c>
       <c r="E275" s="8">
-        <v>2611</v>
+        <v>2917</v>
       </c>
       <c r="F275" s="8">
         <v>283</v>
       </c>
       <c r="G275" s="2"/>
     </row>
-    <row r="276" spans="1:7" ht="27" thickBot="1">
+    <row r="276" spans="1:7" ht="28.2" thickBot="1">
       <c r="A276" s="2" t="s">
         <v>832</v>
       </c>
@@ -8826,14 +8826,14 @@
         <v>833</v>
       </c>
       <c r="E276" s="8">
-        <v>328</v>
+        <v>366</v>
       </c>
       <c r="F276" s="8">
         <v>35</v>
       </c>
       <c r="G276" s="2"/>
     </row>
-    <row r="277" spans="1:7" ht="27" thickBot="1">
+    <row r="277" spans="1:7" ht="28.2" thickBot="1">
       <c r="A277" s="2" t="s">
         <v>835</v>
       </c>
@@ -8845,14 +8845,14 @@
         <v>836</v>
       </c>
       <c r="E277" s="8">
-        <v>592</v>
+        <v>661</v>
       </c>
       <c r="F277" s="8">
         <v>64</v>
       </c>
       <c r="G277" s="2"/>
     </row>
-    <row r="278" spans="1:7" ht="15.75" thickBot="1">
+    <row r="278" spans="1:7" ht="15" thickBot="1">
       <c r="A278" s="2" t="s">
         <v>838</v>
       </c>
@@ -8864,14 +8864,14 @@
         <v>839</v>
       </c>
       <c r="E278" s="8">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="F278" s="8">
         <v>12</v>
       </c>
       <c r="G278" s="2"/>
     </row>
-    <row r="279" spans="1:7" ht="27" thickBot="1">
+    <row r="279" spans="1:7" ht="28.2" thickBot="1">
       <c r="A279" s="2" t="s">
         <v>841</v>
       </c>
@@ -8883,14 +8883,14 @@
         <v>842</v>
       </c>
       <c r="E279" s="8">
-        <v>712</v>
+        <v>796</v>
       </c>
       <c r="F279" s="8">
         <v>77</v>
       </c>
       <c r="G279" s="2"/>
     </row>
-    <row r="280" spans="1:7" ht="27" thickBot="1">
+    <row r="280" spans="1:7" ht="28.2" thickBot="1">
       <c r="A280" s="2" t="s">
         <v>844</v>
       </c>
@@ -8902,14 +8902,14 @@
         <v>845</v>
       </c>
       <c r="E280" s="8">
-        <v>1280</v>
+        <v>1430</v>
       </c>
       <c r="F280" s="8">
         <v>138</v>
       </c>
       <c r="G280" s="2"/>
     </row>
-    <row r="281" spans="1:7" ht="27" thickBot="1">
+    <row r="281" spans="1:7" ht="28.2" thickBot="1">
       <c r="A281" s="2" t="s">
         <v>847</v>
       </c>
@@ -8921,14 +8921,14 @@
         <v>848</v>
       </c>
       <c r="E281" s="8">
-        <v>1511</v>
+        <v>1688</v>
       </c>
       <c r="F281" s="8">
         <v>163</v>
       </c>
       <c r="G281" s="2"/>
     </row>
-    <row r="282" spans="1:7" ht="27" thickBot="1">
+    <row r="282" spans="1:7" ht="28.2" thickBot="1">
       <c r="A282" s="2" t="s">
         <v>850</v>
       </c>
@@ -8940,14 +8940,14 @@
         <v>851</v>
       </c>
       <c r="E282" s="8">
-        <v>2447</v>
+        <v>2734</v>
       </c>
       <c r="F282" s="8">
         <v>265</v>
       </c>
       <c r="G282" s="2"/>
     </row>
-    <row r="283" spans="1:7" ht="27" thickBot="1">
+    <row r="283" spans="1:7" ht="28.2" thickBot="1">
       <c r="A283" s="2" t="s">
         <v>853</v>
       </c>
@@ -8959,14 +8959,14 @@
         <v>854</v>
       </c>
       <c r="E283" s="8">
-        <v>1691</v>
+        <v>1890</v>
       </c>
       <c r="F283" s="8">
         <v>183</v>
       </c>
       <c r="G283" s="2"/>
     </row>
-    <row r="284" spans="1:7" ht="27" thickBot="1">
+    <row r="284" spans="1:7" ht="28.2" thickBot="1">
       <c r="A284" s="2" t="s">
         <v>856</v>
       </c>
@@ -8978,14 +8978,14 @@
         <v>857</v>
       </c>
       <c r="E284" s="8">
-        <v>1760</v>
+        <v>1967</v>
       </c>
       <c r="F284" s="8">
         <v>190</v>
       </c>
       <c r="G284" s="2"/>
     </row>
-    <row r="285" spans="1:7" ht="27" thickBot="1">
+    <row r="285" spans="1:7" ht="28.2" thickBot="1">
       <c r="A285" s="2" t="s">
         <v>859</v>
       </c>
@@ -8997,14 +8997,14 @@
         <v>860</v>
       </c>
       <c r="E285" s="8">
-        <v>558</v>
+        <v>623</v>
       </c>
       <c r="F285" s="8">
         <v>60</v>
       </c>
       <c r="G285" s="2"/>
     </row>
-    <row r="286" spans="1:7" ht="27" thickBot="1">
+    <row r="286" spans="1:7" ht="28.2" thickBot="1">
       <c r="A286" s="2" t="s">
         <v>862</v>
       </c>
@@ -9016,14 +9016,14 @@
         <v>863</v>
       </c>
       <c r="E286" s="8">
-        <v>443</v>
+        <v>495</v>
       </c>
       <c r="F286" s="8">
         <v>48</v>
       </c>
       <c r="G286" s="2"/>
     </row>
-    <row r="287" spans="1:7" ht="27" thickBot="1">
+    <row r="287" spans="1:7" ht="28.2" thickBot="1">
       <c r="A287" s="2" t="s">
         <v>865</v>
       </c>
@@ -9035,14 +9035,14 @@
         <v>866</v>
       </c>
       <c r="E287" s="8">
-        <v>585</v>
+        <v>653</v>
       </c>
       <c r="F287" s="8">
         <v>63</v>
       </c>
       <c r="G287" s="2"/>
     </row>
-    <row r="288" spans="1:7" ht="27" thickBot="1">
+    <row r="288" spans="1:7" ht="28.2" thickBot="1">
       <c r="A288" s="2" t="s">
         <v>868</v>
       </c>
@@ -9054,14 +9054,14 @@
         <v>869</v>
       </c>
       <c r="E288" s="8">
-        <v>472</v>
+        <v>528</v>
       </c>
       <c r="F288" s="8">
         <v>51</v>
       </c>
       <c r="G288" s="2"/>
     </row>
-    <row r="289" spans="1:7" ht="27" thickBot="1">
+    <row r="289" spans="1:7" ht="28.2" thickBot="1">
       <c r="A289" s="2" t="s">
         <v>871</v>
       </c>
@@ -9073,14 +9073,14 @@
         <v>872</v>
       </c>
       <c r="E289" s="8">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="F289" s="8">
         <v>25</v>
       </c>
       <c r="G289" s="2"/>
     </row>
-    <row r="290" spans="1:7" ht="27" thickBot="1">
+    <row r="290" spans="1:7" ht="28.2" thickBot="1">
       <c r="A290" s="2" t="s">
         <v>874</v>
       </c>
@@ -9092,14 +9092,14 @@
         <v>875</v>
       </c>
       <c r="E290" s="8">
-        <v>1692</v>
+        <v>1890</v>
       </c>
       <c r="F290" s="8">
         <v>183</v>
       </c>
       <c r="G290" s="2"/>
     </row>
-    <row r="291" spans="1:7" ht="15.75" thickBot="1">
+    <row r="291" spans="1:7" ht="15" thickBot="1">
       <c r="A291" s="2" t="s">
         <v>876</v>
       </c>
@@ -9111,14 +9111,14 @@
         <v>877</v>
       </c>
       <c r="E291" s="8">
-        <v>376</v>
+        <v>420</v>
       </c>
       <c r="F291" s="8">
         <v>40</v>
       </c>
       <c r="G291" s="2"/>
     </row>
-    <row r="292" spans="1:7" ht="27" thickBot="1">
+    <row r="292" spans="1:7" ht="28.2" thickBot="1">
       <c r="A292" s="2" t="s">
         <v>879</v>
       </c>
@@ -9130,14 +9130,14 @@
         <v>880</v>
       </c>
       <c r="E292" s="8">
-        <v>606</v>
+        <v>677</v>
       </c>
       <c r="F292" s="8">
         <v>65</v>
       </c>
       <c r="G292" s="2"/>
     </row>
-    <row r="293" spans="1:7" ht="27" thickBot="1">
+    <row r="293" spans="1:7" ht="28.2" thickBot="1">
       <c r="A293" s="2" t="s">
         <v>882</v>
       </c>
@@ -9149,14 +9149,14 @@
         <v>883</v>
       </c>
       <c r="E293" s="8">
-        <v>765</v>
+        <v>855</v>
       </c>
       <c r="F293" s="8">
         <v>82</v>
       </c>
       <c r="G293" s="2"/>
     </row>
-    <row r="294" spans="1:7" ht="27" thickBot="1">
+    <row r="294" spans="1:7" ht="28.2" thickBot="1">
       <c r="A294" s="2" t="s">
         <v>885</v>
       </c>
@@ -9168,14 +9168,14 @@
         <v>886</v>
       </c>
       <c r="E294" s="8">
-        <v>874</v>
+        <v>976</v>
       </c>
       <c r="F294" s="8">
         <v>94</v>
       </c>
       <c r="G294" s="2"/>
     </row>
-    <row r="295" spans="1:7" ht="27" thickBot="1">
+    <row r="295" spans="1:7" ht="28.2" thickBot="1">
       <c r="A295" s="2" t="s">
         <v>888</v>
       </c>
@@ -9187,14 +9187,14 @@
         <v>889</v>
       </c>
       <c r="E295" s="8">
-        <v>479</v>
+        <v>535</v>
       </c>
       <c r="F295" s="8">
         <v>51</v>
       </c>
       <c r="G295" s="2"/>
     </row>
-    <row r="296" spans="1:7" ht="27" thickBot="1">
+    <row r="296" spans="1:7" ht="28.2" thickBot="1">
       <c r="A296" s="2" t="s">
         <v>891</v>
       </c>
@@ -9206,14 +9206,14 @@
         <v>892</v>
       </c>
       <c r="E296" s="8">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="F296" s="8">
         <v>30</v>
       </c>
       <c r="G296" s="2"/>
     </row>
-    <row r="297" spans="1:7" ht="27" thickBot="1">
+    <row r="297" spans="1:7" ht="28.2" thickBot="1">
       <c r="A297" s="2" t="s">
         <v>894</v>
       </c>
@@ -9225,14 +9225,14 @@
         <v>895</v>
       </c>
       <c r="E297" s="8">
-        <v>1510</v>
+        <v>1687</v>
       </c>
       <c r="F297" s="8">
         <v>163</v>
       </c>
       <c r="G297" s="2"/>
     </row>
-    <row r="298" spans="1:7" ht="27" thickBot="1">
+    <row r="298" spans="1:7" ht="28.2" thickBot="1">
       <c r="A298" s="2" t="s">
         <v>897</v>
       </c>
@@ -9244,14 +9244,14 @@
         <v>898</v>
       </c>
       <c r="E298" s="8">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c r="F298" s="8">
         <v>31</v>
       </c>
       <c r="G298" s="2"/>
     </row>
-    <row r="299" spans="1:7" ht="27" thickBot="1">
+    <row r="299" spans="1:7" ht="28.2" thickBot="1">
       <c r="A299" s="2" t="s">
         <v>900</v>
       </c>
@@ -9263,14 +9263,14 @@
         <v>901</v>
       </c>
       <c r="E299" s="8">
-        <v>630</v>
+        <v>704</v>
       </c>
       <c r="F299" s="8">
         <v>68</v>
       </c>
       <c r="G299" s="2"/>
     </row>
-    <row r="300" spans="1:7" ht="27" thickBot="1">
+    <row r="300" spans="1:7" ht="28.2" thickBot="1">
       <c r="A300" s="2" t="s">
         <v>903</v>
       </c>
@@ -9282,14 +9282,14 @@
         <v>904</v>
       </c>
       <c r="E300" s="8">
-        <v>535</v>
+        <v>598</v>
       </c>
       <c r="F300" s="8">
         <v>58</v>
       </c>
       <c r="G300" s="2"/>
     </row>
-    <row r="301" spans="1:7" ht="27" thickBot="1">
+    <row r="301" spans="1:7" ht="28.2" thickBot="1">
       <c r="A301" s="2" t="s">
         <v>906</v>
       </c>
@@ -9301,14 +9301,14 @@
         <v>907</v>
       </c>
       <c r="E301" s="8">
-        <v>675</v>
+        <v>754</v>
       </c>
       <c r="F301" s="8">
         <v>73</v>
       </c>
       <c r="G301" s="2"/>
     </row>
-    <row r="302" spans="1:7" ht="27" thickBot="1">
+    <row r="302" spans="1:7" ht="28.2" thickBot="1">
       <c r="A302" s="2" t="s">
         <v>909</v>
       </c>
@@ -9320,14 +9320,14 @@
         <v>910</v>
       </c>
       <c r="E302" s="8">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F302" s="8">
         <v>11</v>
       </c>
       <c r="G302" s="2"/>
     </row>
-    <row r="303" spans="1:7" ht="27" thickBot="1">
+    <row r="303" spans="1:7" ht="28.2" thickBot="1">
       <c r="A303" s="2" t="s">
         <v>912</v>
       </c>
@@ -9339,14 +9339,14 @@
         <v>913</v>
       </c>
       <c r="E303" s="8">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F303" s="8">
         <v>8</v>
       </c>
       <c r="G303" s="2"/>
     </row>
-    <row r="304" spans="1:7" ht="27" thickBot="1">
+    <row r="304" spans="1:7" ht="28.2" thickBot="1">
       <c r="A304" s="2" t="s">
         <v>915</v>
       </c>
@@ -9358,14 +9358,14 @@
         <v>916</v>
       </c>
       <c r="E304" s="8">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="F304" s="8">
         <v>21</v>
       </c>
       <c r="G304" s="2"/>
     </row>
-    <row r="305" spans="1:7" ht="27" thickBot="1">
+    <row r="305" spans="1:7" ht="28.2" thickBot="1">
       <c r="A305" s="2" t="s">
         <v>918</v>
       </c>
@@ -9377,14 +9377,14 @@
         <v>919</v>
       </c>
       <c r="E305" s="8">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="F305" s="8">
         <v>12</v>
       </c>
       <c r="G305" s="2"/>
     </row>
-    <row r="306" spans="1:7" ht="27" thickBot="1">
+    <row r="306" spans="1:7" ht="28.2" thickBot="1">
       <c r="A306" s="2" t="s">
         <v>921</v>
       </c>
@@ -9396,14 +9396,14 @@
         <v>922</v>
       </c>
       <c r="E306" s="8">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="F306" s="8">
         <v>12</v>
       </c>
       <c r="G306" s="2"/>
     </row>
-    <row r="307" spans="1:7" ht="27" thickBot="1">
+    <row r="307" spans="1:7" ht="28.2" thickBot="1">
       <c r="A307" s="2" t="s">
         <v>924</v>
       </c>
@@ -9415,14 +9415,14 @@
         <v>925</v>
       </c>
       <c r="E307" s="8">
-        <v>795</v>
+        <v>888</v>
       </c>
       <c r="F307" s="8">
         <v>86</v>
       </c>
       <c r="G307" s="2"/>
     </row>
-    <row r="308" spans="1:7" ht="27" thickBot="1">
+    <row r="308" spans="1:7" ht="28.2" thickBot="1">
       <c r="A308" s="2" t="s">
         <v>927</v>
       </c>
@@ -9434,14 +9434,14 @@
         <v>928</v>
       </c>
       <c r="E308" s="8">
-        <v>922</v>
+        <v>1031</v>
       </c>
       <c r="F308" s="8">
         <v>100</v>
       </c>
       <c r="G308" s="2"/>
     </row>
-    <row r="309" spans="1:7" ht="27" thickBot="1">
+    <row r="309" spans="1:7" ht="28.2" thickBot="1">
       <c r="A309" s="2" t="s">
         <v>930</v>
       </c>
@@ -9453,14 +9453,14 @@
         <v>931</v>
       </c>
       <c r="E309" s="8">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="F309" s="8">
         <v>19</v>
       </c>
       <c r="G309" s="2"/>
     </row>
-    <row r="310" spans="1:7" ht="27" thickBot="1">
+    <row r="310" spans="1:7" ht="28.2" thickBot="1">
       <c r="A310" s="2" t="s">
         <v>933</v>
       </c>
@@ -9472,14 +9472,14 @@
         <v>934</v>
       </c>
       <c r="E310" s="8">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="F310" s="8">
         <v>29</v>
       </c>
       <c r="G310" s="2"/>
     </row>
-    <row r="311" spans="1:7" ht="27" thickBot="1">
+    <row r="311" spans="1:7" ht="28.2" thickBot="1">
       <c r="A311" s="2" t="s">
         <v>936</v>
       </c>
@@ -9491,14 +9491,14 @@
         <v>937</v>
       </c>
       <c r="E311" s="8">
-        <v>283</v>
+        <v>316</v>
       </c>
       <c r="F311" s="8">
         <v>30</v>
       </c>
       <c r="G311" s="2"/>
     </row>
-    <row r="312" spans="1:7" ht="27" thickBot="1">
+    <row r="312" spans="1:7" ht="28.2" thickBot="1">
       <c r="A312" s="2" t="s">
         <v>939</v>
       </c>
@@ -9510,14 +9510,14 @@
         <v>940</v>
       </c>
       <c r="E312" s="8">
-        <v>320</v>
+        <v>357</v>
       </c>
       <c r="F312" s="8">
         <v>34</v>
       </c>
       <c r="G312" s="2"/>
     </row>
-    <row r="313" spans="1:7" ht="27" thickBot="1">
+    <row r="313" spans="1:7" ht="28.2" thickBot="1">
       <c r="A313" s="2" t="s">
         <v>942</v>
       </c>
@@ -9529,14 +9529,14 @@
         <v>943</v>
       </c>
       <c r="E313" s="8">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="F313" s="8">
         <v>20</v>
       </c>
       <c r="G313" s="2"/>
     </row>
-    <row r="314" spans="1:7" ht="27" thickBot="1">
+    <row r="314" spans="1:7" ht="28.2" thickBot="1">
       <c r="A314" s="2" t="s">
         <v>945</v>
       </c>
@@ -9548,14 +9548,14 @@
         <v>946</v>
       </c>
       <c r="E314" s="8">
-        <v>1086</v>
+        <v>1214</v>
       </c>
       <c r="F314" s="8">
         <v>117</v>
       </c>
       <c r="G314" s="2"/>
     </row>
-    <row r="315" spans="1:7" ht="27" thickBot="1">
+    <row r="315" spans="1:7" ht="28.2" thickBot="1">
       <c r="A315" s="2" t="s">
         <v>948</v>
       </c>
@@ -9567,14 +9567,14 @@
         <v>949</v>
       </c>
       <c r="E315" s="8">
-        <v>808</v>
+        <v>902</v>
       </c>
       <c r="F315" s="8">
         <v>87</v>
       </c>
       <c r="G315" s="2"/>
     </row>
-    <row r="316" spans="1:7" ht="27" thickBot="1">
+    <row r="316" spans="1:7" ht="28.2" thickBot="1">
       <c r="A316" s="2" t="s">
         <v>951</v>
       </c>
@@ -9586,14 +9586,14 @@
         <v>952</v>
       </c>
       <c r="E316" s="8">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="F316" s="8">
         <v>36</v>
       </c>
       <c r="G316" s="2"/>
     </row>
-    <row r="317" spans="1:7" ht="27" thickBot="1">
+    <row r="317" spans="1:7" ht="28.2" thickBot="1">
       <c r="A317" s="2" t="s">
         <v>954</v>
       </c>
@@ -9605,14 +9605,14 @@
         <v>955</v>
       </c>
       <c r="E317" s="8">
-        <v>741</v>
+        <v>828</v>
       </c>
       <c r="F317" s="8">
         <v>80</v>
       </c>
       <c r="G317" s="2"/>
     </row>
-    <row r="318" spans="1:7" ht="27" thickBot="1">
+    <row r="318" spans="1:7" ht="28.2" thickBot="1">
       <c r="A318" s="2" t="s">
         <v>957</v>
       </c>
@@ -9624,14 +9624,14 @@
         <v>958</v>
       </c>
       <c r="E318" s="8">
-        <v>1443</v>
+        <v>1612</v>
       </c>
       <c r="F318" s="8">
         <v>156</v>
       </c>
       <c r="G318" s="2"/>
     </row>
-    <row r="319" spans="1:7" ht="27" thickBot="1">
+    <row r="319" spans="1:7" ht="28.2" thickBot="1">
       <c r="A319" s="2" t="s">
         <v>960</v>
       </c>
@@ -9643,14 +9643,14 @@
         <v>961</v>
       </c>
       <c r="E319" s="8">
-        <v>2152</v>
+        <v>2404</v>
       </c>
       <c r="F319" s="8">
         <v>233</v>
       </c>
       <c r="G319" s="2"/>
     </row>
-    <row r="320" spans="1:7" ht="15.75" thickBot="1">
+    <row r="320" spans="1:7" ht="15" thickBot="1">
       <c r="A320" s="2" t="s">
         <v>963</v>
       </c>
@@ -9662,14 +9662,14 @@
         <v>964</v>
       </c>
       <c r="E320" s="8">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="F320" s="8">
         <v>19</v>
       </c>
       <c r="G320" s="2"/>
     </row>
-    <row r="321" spans="1:7" ht="39.75" thickBot="1">
+    <row r="321" spans="1:7" ht="42" thickBot="1">
       <c r="A321" s="2" t="s">
         <v>966</v>
       </c>
@@ -9681,14 +9681,14 @@
         <v>967</v>
       </c>
       <c r="E321" s="8">
-        <v>3456</v>
+        <v>3862</v>
       </c>
       <c r="F321" s="8">
         <v>374</v>
       </c>
       <c r="G321" s="2"/>
     </row>
-    <row r="322" spans="1:7" ht="27" thickBot="1">
+    <row r="322" spans="1:7" ht="28.2" thickBot="1">
       <c r="A322" s="2" t="s">
         <v>969</v>
       </c>
@@ -9700,14 +9700,14 @@
         <v>970</v>
       </c>
       <c r="E322" s="8">
-        <v>727</v>
+        <v>812</v>
       </c>
       <c r="F322" s="8">
         <v>78</v>
       </c>
       <c r="G322" s="2"/>
     </row>
-    <row r="323" spans="1:7" ht="27" thickBot="1">
+    <row r="323" spans="1:7" ht="28.2" thickBot="1">
       <c r="A323" s="2" t="s">
         <v>972</v>
       </c>
@@ -9719,14 +9719,14 @@
         <v>973</v>
       </c>
       <c r="E323" s="8">
-        <v>1802</v>
+        <v>2014</v>
       </c>
       <c r="F323" s="8">
         <v>195</v>
       </c>
       <c r="G323" s="2"/>
     </row>
-    <row r="324" spans="1:7" ht="27" thickBot="1">
+    <row r="324" spans="1:7" ht="28.2" thickBot="1">
       <c r="A324" s="2" t="s">
         <v>975</v>
       </c>
@@ -9738,14 +9738,14 @@
         <v>976</v>
       </c>
       <c r="E324" s="8">
-        <v>445</v>
+        <v>497</v>
       </c>
       <c r="F324" s="8">
         <v>48</v>
       </c>
       <c r="G324" s="2"/>
     </row>
-    <row r="325" spans="1:7" ht="27" thickBot="1">
+    <row r="325" spans="1:7" ht="28.2" thickBot="1">
       <c r="A325" s="2" t="s">
         <v>978</v>
       </c>
@@ -9757,14 +9757,14 @@
         <v>979</v>
       </c>
       <c r="E325" s="8">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="F325" s="8">
         <v>25</v>
       </c>
       <c r="G325" s="2"/>
     </row>
-    <row r="326" spans="1:7" ht="52.5" thickBot="1">
+    <row r="326" spans="1:7" ht="55.8" thickBot="1">
       <c r="A326" s="2" t="s">
         <v>981</v>
       </c>
@@ -9778,14 +9778,14 @@
         <v>982</v>
       </c>
       <c r="E326" s="8">
-        <v>2549</v>
+        <v>2848</v>
       </c>
       <c r="F326" s="8">
         <v>276</v>
       </c>
       <c r="G326" s="2"/>
     </row>
-    <row r="327" spans="1:7" ht="27" thickBot="1">
+    <row r="327" spans="1:7" ht="28.2" thickBot="1">
       <c r="A327" s="2" t="s">
         <v>984</v>
       </c>
@@ -9797,14 +9797,14 @@
         <v>985</v>
       </c>
       <c r="E327" s="8">
-        <v>703</v>
+        <v>786</v>
       </c>
       <c r="F327" s="8">
         <v>76</v>
       </c>
       <c r="G327" s="2"/>
     </row>
-    <row r="328" spans="1:7" ht="15.75" thickBot="1">
+    <row r="328" spans="1:7" ht="15" thickBot="1">
       <c r="A328" s="2" t="s">
         <v>987</v>
       </c>
@@ -9816,14 +9816,14 @@
         <v>988</v>
       </c>
       <c r="E328" s="8">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F328" s="8">
         <v>9</v>
       </c>
       <c r="G328" s="2"/>
     </row>
-    <row r="329" spans="1:7" ht="15.75" thickBot="1">
+    <row r="329" spans="1:7" ht="15" thickBot="1">
       <c r="A329" s="2" t="s">
         <v>990</v>
       </c>
@@ -9835,14 +9835,14 @@
         <v>991</v>
       </c>
       <c r="E329" s="8">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F329" s="8">
         <v>3</v>
       </c>
       <c r="G329" s="2"/>
     </row>
-    <row r="330" spans="1:7" ht="15.75" thickBot="1">
+    <row r="330" spans="1:7" ht="15" thickBot="1">
       <c r="A330" s="2" t="s">
         <v>993</v>
       </c>
@@ -9854,14 +9854,14 @@
         <v>994</v>
       </c>
       <c r="E330" s="8">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="F330" s="8">
         <v>8</v>
       </c>
       <c r="G330" s="2"/>
     </row>
-    <row r="331" spans="1:7" ht="15.75" thickBot="1">
+    <row r="331" spans="1:7" ht="15" thickBot="1">
       <c r="A331" s="2" t="s">
         <v>996</v>
       </c>
@@ -9873,14 +9873,14 @@
         <v>997</v>
       </c>
       <c r="E331" s="8">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F331" s="8">
         <v>5</v>
       </c>
       <c r="G331" s="2"/>
     </row>
-    <row r="332" spans="1:7" ht="39.75" thickBot="1">
+    <row r="332" spans="1:7" ht="42" thickBot="1">
       <c r="A332" s="2" t="s">
         <v>999</v>
       </c>
@@ -9892,14 +9892,14 @@
         <v>1000</v>
       </c>
       <c r="E332" s="8">
-        <v>1296</v>
+        <v>1448</v>
       </c>
       <c r="F332" s="8">
         <v>140</v>
       </c>
       <c r="G332" s="2"/>
     </row>
-    <row r="333" spans="1:7" ht="15.75" thickBot="1">
+    <row r="333" spans="1:7" ht="15" thickBot="1">
       <c r="A333" s="2" t="s">
         <v>1002</v>
       </c>
@@ -9911,14 +9911,14 @@
         <v>1003</v>
       </c>
       <c r="E333" s="8">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F333" s="8">
         <v>2</v>
       </c>
       <c r="G333" s="2"/>
     </row>
-    <row r="334" spans="1:7" ht="15.75" thickBot="1">
+    <row r="334" spans="1:7" ht="15" thickBot="1">
       <c r="A334" s="2" t="s">
         <v>1005</v>
       </c>
@@ -9930,14 +9930,14 @@
         <v>1006</v>
       </c>
       <c r="E334" s="8">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F334" s="8">
         <v>9</v>
       </c>
       <c r="G334" s="2"/>
     </row>
-    <row r="335" spans="1:7" ht="15.75" thickBot="1">
+    <row r="335" spans="1:7" ht="15" thickBot="1">
       <c r="A335" s="2" t="s">
         <v>1008</v>
       </c>
@@ -9949,14 +9949,14 @@
         <v>1009</v>
       </c>
       <c r="E335" s="8">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F335" s="8">
         <v>4</v>
       </c>
       <c r="G335" s="2"/>
     </row>
-    <row r="336" spans="1:7" ht="27" thickBot="1">
+    <row r="336" spans="1:7" ht="28.2" thickBot="1">
       <c r="A336" s="2" t="s">
         <v>1011</v>
       </c>
@@ -9968,7 +9968,7 @@
         <v>1012</v>
       </c>
       <c r="E336" s="8">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="F336" s="8">
         <v>35</v>
